--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.8</v>
+        <v>0.19</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>0.19</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>2.96</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.96</v>
+        <v>3.48</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.4</v>
       </c>
-      <c r="V21" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.97</v>
+        <v>2.24</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.74</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N29" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>1.75</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,61 +4229,61 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M32" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
         <v>1.75</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
-        <v>0</v>
-      </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" t="n">
-        <v>0</v>
-      </c>
-      <c r="W32" t="n">
-        <v>0</v>
-      </c>
-      <c r="X32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB32" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M33" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N33" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="M29" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>2.18</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,61 +3991,61 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>2</v>
       </c>
       <c r="M30" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="N30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
         <v>1.75</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
-      <c r="T30" t="n">
-        <v>0</v>
-      </c>
-      <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>0</v>
-      </c>
-      <c r="W30" t="n">
-        <v>0</v>
-      </c>
-      <c r="X30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.45</v>
+        <v>2.1</v>
       </c>
       <c r="M31" t="n">
-        <v>5.6</v>
+        <v>3.65</v>
       </c>
       <c r="N31" t="n">
-        <v>5.4</v>
+        <v>3.3</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2</v>
+        <v>3.65</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N32" t="n">
-        <v>3.35</v>
+        <v>1.95</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
         <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="M33" t="n">
-        <v>3.65</v>
+        <v>4.5</v>
       </c>
       <c r="N33" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>4.1</v>
       </c>
       <c r="N34" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>1.75</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="M34" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="N34" t="n">
-        <v>1.75</v>
+        <v>2.35</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.53</v>
+        <v>2.03</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.45</v>
+        <v>1.8</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0.19</v>
+        <v>7.8</v>
       </c>
       <c r="M10" t="n">
-        <v>0.19</v>
+        <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N17" t="n">
         <v>2.4</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>3.96</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.9</v>
+        <v>5.7</v>
       </c>
       <c r="M19" t="n">
-        <v>3.3</v>
+        <v>3.95</v>
       </c>
       <c r="N19" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,10 +2840,10 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.1</v>
+        <v>3.35</v>
       </c>
       <c r="N28" t="n">
-        <v>1.75</v>
+        <v>2.8</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.45</v>
+        <v>0.38</v>
       </c>
       <c r="M29" t="n">
-        <v>5.6</v>
+        <v>0.26</v>
       </c>
       <c r="N29" t="n">
-        <v>5.4</v>
+        <v>0.35</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.18</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.7</v>
+        <v>1.62</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2</v>
+        <v>1.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.9</v>
+        <v>5.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.35</v>
+        <v>5.4</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="N31" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N34" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O17" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M18" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,55 +2682,55 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.57</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.8</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
-        <v>3.05</v>
+        <v>2.3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,16 +2840,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N21" t="n">
         <v>2.4</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N21" t="n">
-        <v>3</v>
-      </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>2.3</v>
+        <v>3.05</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.65</v>
+        <v>5.7</v>
       </c>
       <c r="M26" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N26" t="n">
-        <v>5.3</v>
+        <v>1.57</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,61 +3634,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC27" t="n">
         <v>2.35</v>
       </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>2.1</v>
       </c>
       <c r="M28" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="N28" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.65</v>
+        <v>3</v>
       </c>
       <c r="M32" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.95</v>
+        <v>2.35</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB32" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="M33" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N33" t="n">
-        <v>5.2</v>
+        <v>1.95</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.1</v>
+        <v>2.45</v>
       </c>
       <c r="M34" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="N34" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.96</v>
+        <v>5.7</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.24</v>
+        <v>1.9</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.8</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>1.63</v>
       </c>
       <c r="M17" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="N17" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.63</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.57</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="M19" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.25</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="N20" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.13</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="N21" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.95</v>
+        <v>2.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N23" t="n">
         <v>2.4</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N23" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>5.3</v>
+        <v>3.05</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.7</v>
+        <v>2.9</v>
       </c>
       <c r="M26" t="n">
-        <v>3.95</v>
+        <v>3.3</v>
       </c>
       <c r="N26" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M34" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N34" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.7</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.95</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.57</v>
+        <v>3.05</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="M17" t="n">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.9</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
       <c r="M18" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>1.8</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.57</v>
+        <v>1.9</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.75</v>
+        <v>3.35</v>
       </c>
       <c r="N20" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.9</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.96</v>
+        <v>1.63</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>3.95</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.24</v>
+        <v>1.8</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>1.9</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N24" t="n">
         <v>2.4</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N24" t="n">
-        <v>3.05</v>
-      </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.65</v>
+        <v>5.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N25" t="n">
-        <v>5.3</v>
+        <v>1.57</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="N26" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="O26" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>5.2</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.1</v>
+        <v>3</v>
       </c>
       <c r="M28" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB28" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>0.38</v>
+        <v>4.2</v>
       </c>
       <c r="M29" t="n">
-        <v>0.26</v>
+        <v>4.1</v>
       </c>
       <c r="N29" t="n">
-        <v>0.35</v>
+        <v>1.75</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,61 +4110,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.2</v>
+        <v>0.38</v>
       </c>
       <c r="M31" t="n">
-        <v>4.1</v>
+        <v>0.26</v>
       </c>
       <c r="N31" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="n">
+        <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
         <v>1.75</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="n">
-        <v>0</v>
-      </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
-      <c r="W31" t="n">
-        <v>0</v>
-      </c>
-      <c r="X31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="N32" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.03</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.65</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="N33" t="n">
-        <v>1.95</v>
+        <v>2.8</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.57</v>
+        <v>3.65</v>
       </c>
       <c r="M34" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="N34" t="n">
-        <v>5.2</v>
+        <v>1.95</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>7.8</v>
+        <v>4.7</v>
       </c>
       <c r="M10" t="n">
         <v>4.6</v>
       </c>
       <c r="N10" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="M15" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.52</v>
+        <v>1.39</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2257,10 +2257,10 @@
         <v>2.9</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.13</v>
+        <v>1.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.4</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>3.05</v>
+        <v>1.61</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2364,16 +2364,16 @@
         <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.65</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.75</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>5.3</v>
+        <v>3.06</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.8</v>
+        <v>3.16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.75</v>
+        <v>3.16</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.8</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.9</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.3</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.63</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.95</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.7</v>
+        <v>3.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.95</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1.57</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.9</v>
+        <v>2.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="M27" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
         <v>5.2</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.61</v>
       </c>
       <c r="N28" t="n">
-        <v>2.35</v>
+        <v>1.84</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.03</v>
+        <v>1.82</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4.2</v>
+        <v>2.47</v>
       </c>
       <c r="M29" t="n">
-        <v>4.1</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>1.75</v>
+        <v>2.67</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.45</v>
+        <v>2.62</v>
       </c>
       <c r="M30" t="n">
-        <v>5.6</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>5.4</v>
+        <v>2.59</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>0.38</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>0.26</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>0.35</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.65</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>3.3</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>3.35</v>
+        <v>3.52</v>
       </c>
       <c r="N33" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.65</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>1.95</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.4</v>
+        <v>3.16</v>
       </c>
       <c r="M16" t="n">
-        <v>3.83</v>
+        <v>3.16</v>
       </c>
       <c r="N16" t="n">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.91</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.83</v>
+      </c>
+      <c r="N20" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB20" t="n">
         <v>1.83</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>3.96</v>
       </c>
       <c r="P25" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
         <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="T25" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.33</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.61</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>1.84</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>2.67</v>
+        <v>1.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>8.9</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>3.97</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.16</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.83</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N19" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB19" t="n">
+      <c r="AF19" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>0</v>
-      </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.83</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>2.44</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>3.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>2.23</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.44</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.23</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.25</v>
       </c>
-      <c r="N23" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="n">
-        <v>0</v>
-      </c>
-      <c r="T23" t="n">
-        <v>0</v>
-      </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="n">
-        <v>0</v>
-      </c>
-      <c r="X23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>0</v>
-      </c>
       <c r="AA23" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M24" t="n">
         <v>3.25</v>
       </c>
-      <c r="M24" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="N25" t="n">
         <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.42</v>
+        <v>3.97</v>
       </c>
       <c r="M27" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>1.78</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>2.47</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>1.84</v>
+        <v>2.67</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>8.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>8.9</v>
+        <v>2.69</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.97</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>2.59</v>
+        <v>1.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.4</v>
+        <v>1.66</v>
       </c>
       <c r="M16" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="N16" t="n">
-        <v>1.61</v>
+        <v>4.9</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.55</v>
       </c>
       <c r="N18" t="n">
-        <v>3.06</v>
+        <v>4.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.25</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>5.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N22" t="n">
-        <v>4.9</v>
+        <v>1.61</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.97</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.92</v>
+        <v>3.61</v>
       </c>
       <c r="N27" t="n">
-        <v>1.78</v>
+        <v>1.84</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.53</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.45</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="N30" t="n">
-        <v>8.9</v>
+        <v>5.2</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.36</v>
+        <v>1.58</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.1</v>
+        <v>2.38</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>1.6</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>3.92</v>
       </c>
       <c r="N33" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>5.2</v>
+        <v>2.59</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="N16" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>3.01</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N21" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>5.4</v>
+        <v>3.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.83</v>
+        <v>3.16</v>
       </c>
       <c r="N22" t="n">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V23" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.4</v>
       </c>
-      <c r="V23" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.27</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.55</v>
+        <v>4.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.11</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.16</v>
+        <v>3.83</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M27" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="N27" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N29" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>5.2</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>1.84</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>3.01</v>
       </c>
       <c r="O16" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>5.4</v>
       </c>
       <c r="M17" t="n">
-        <v>3.65</v>
+        <v>3.83</v>
       </c>
       <c r="N17" t="n">
-        <v>5.1</v>
+        <v>1.61</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="M18" t="n">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="N18" t="n">
-        <v>4.1</v>
+        <v>3.06</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2602,16 +2602,16 @@
         <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>3.01</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.13</v>
+        <v>2.24</v>
       </c>
       <c r="AB22" t="n">
         <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>3.16</v>
       </c>
       <c r="M25" t="n">
-        <v>3.83</v>
+        <v>3.16</v>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="N27" t="n">
-        <v>2.69</v>
+        <v>1.84</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N31" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>2.67</v>
+        <v>8.9</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.59</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>5.4</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>1.61</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.83</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>2.93</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.4</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2678,77 +2678,77 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.83</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>3.03</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="N24" t="n">
-        <v>4.1</v>
+        <v>3.06</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.16</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
         <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.13</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>3.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>2.29</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="M27" t="n">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="N27" t="n">
-        <v>1.84</v>
+        <v>8.9</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.97</v>
+        <v>2.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>1.78</v>
+        <v>2.59</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.61</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>1.84</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,10 +4274,10 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>5.2</v>
+        <v>2.69</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>1.61</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,10 +2370,10 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M18" t="n">
         <v>3.25</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>3.03</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>3.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>0</v>
-      </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>3.03</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
       <c r="M24" t="n">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="N24" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3316,16 +3316,16 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3392,77 +3392,77 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>3.01</v>
       </c>
       <c r="O25" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>2.23</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>1.58</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.16</v>
+        <v>1.67</v>
       </c>
       <c r="M26" t="n">
-        <v>3.16</v>
+        <v>3.65</v>
       </c>
       <c r="N26" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N27" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,16 +3679,16 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.59</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="N30" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>2.62</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>2.59</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>2.67</v>
+        <v>1.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>3.97</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>1.78</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI34"/>
+  <dimension ref="A1:AI35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1561,7 +1561,7 @@
         <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46042.50347222222</v>
+        <v>46042.5</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,16 +1656,16 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
         <v>0</v>
@@ -1680,7 +1680,7 @@
         <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46042.52083333334</v>
+        <v>46042.50347222222</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1775,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE11" t="n">
         <v>0</v>
@@ -1799,7 +1799,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46042.60416666666</v>
+        <v>46042.52083333334</v>
       </c>
     </row>
     <row r="12">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.53</v>
+        <v>1.5</v>
       </c>
       <c r="M13" t="n">
-        <v>2.6</v>
+        <v>3.62</v>
       </c>
       <c r="N13" t="n">
-        <v>3.13</v>
+        <v>6.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.9</v>
+        <v>2.53</v>
       </c>
       <c r="M15" t="n">
-        <v>5.6</v>
+        <v>2.6</v>
       </c>
       <c r="N15" t="n">
-        <v>1.39</v>
+        <v>3.13</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,16 +2251,16 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46042.61458333334</v>
+        <v>46042.60416666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,13 +2325,13 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="M16" t="n">
-        <v>3.83</v>
+        <v>5.6</v>
       </c>
       <c r="N16" t="n">
-        <v>1.61</v>
+        <v>1.39</v>
       </c>
       <c r="O16" t="n">
         <v>0</v>
@@ -2370,16 +2370,16 @@
         <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.83</v>
+        <v>2.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
@@ -2394,7 +2394,7 @@
         <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46042.69791666666</v>
+        <v>46042.61458333334</v>
       </c>
     </row>
     <row r="17">
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>3.16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3154,77 +3154,77 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N25" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.67</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>5.1</v>
+        <v>3.03</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.47</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.41</v>
+        <v>3.83</v>
       </c>
       <c r="N27" t="n">
-        <v>2.67</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3703,7 +3703,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46042.70833333334</v>
+        <v>46042.69791666666</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2</v>
+        <v>2.67</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.59</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>3.97</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.92</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.97</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>1.78</v>
+        <v>2.69</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4536,6 +4536,125 @@
         <v>0</v>
       </c>
       <c r="AI34" s="3" t="n">
+        <v>46042.70833333334</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>17:00</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>England Championship</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Wrexham</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Leicester City</t>
+        </is>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M35" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N35" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>0</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" s="3" t="n">
         <v>46042.70833333334</v>
       </c>
     </row>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>3.62</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>6.4</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="N19" t="n">
         <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.16</v>
+        <v>2.49</v>
       </c>
       <c r="M21" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>2.32</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.59</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>2.67</v>
+        <v>1.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>8.9</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="M31" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>2.67</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.97</v>
+        <v>2.42</v>
       </c>
       <c r="M32" t="n">
-        <v>3.92</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>2.69</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>3.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>1.78</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>2.93</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.66</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>1.76</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N24" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>3.83</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="M27" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>3.03</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>2.67</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB31" t="n">
         <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.42</v>
+        <v>2.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>2.59</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.59</v>
+        <v>5.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.45</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>2.8</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.16</v>
+        <v>2.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.16</v>
+        <v>2.93</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC20" t="n">
         <v>3.55</v>
       </c>
-      <c r="N20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
-      <c r="U20" t="n">
-        <v>0</v>
-      </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>0</v>
-      </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>3.01</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.49</v>
+        <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>2.93</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>3.06</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3078,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.25</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.24</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>1.83</v>
       </c>
       <c r="M25" t="n">
-        <v>3.83</v>
+        <v>3.55</v>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>4.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.91</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.32</v>
+        <v>3.16</v>
       </c>
       <c r="M27" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N27" t="n">
-        <v>3.03</v>
+        <v>2.29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.84</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>2.69</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.62</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.32</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.59</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC32" t="n">
         <v>1.87</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AD32" t="n">
         <v>1.87</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>5.2</v>
+        <v>2.59</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N34" t="n">
-        <v>8.9</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="M35" t="n">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>3.06</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.92</v>
+        <v>2.4</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.4</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>3.03</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>2.02</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.24</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>3.01</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>3.16</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.16</v>
+        <v>3.83</v>
       </c>
       <c r="N27" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N35" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>3.03</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.02</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.25</v>
+        <v>1.83</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>4.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.24</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="M25" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>4.1</v>
+        <v>3.03</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="N26" t="n">
         <v>2.29</v>
       </c>
       <c r="O26" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="M27" t="n">
-        <v>3.83</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N30" t="n">
-        <v>8.9</v>
+        <v>1.84</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N33" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="M35" t="n">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,16 +1888,16 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2126,10 +2126,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>3.06</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2483,16 +2483,16 @@
         <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>3.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="N19" t="n">
         <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>3.96</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
         <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD20" t="n">
         <v>1.33</v>
       </c>
-      <c r="V20" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.83</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N22" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB22" t="n">
+      <c r="AF22" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>0</v>
-      </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.83</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N25" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.16</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>3.97</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>3.92</v>
       </c>
       <c r="N28" t="n">
-        <v>2.59</v>
+        <v>1.78</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>4.3</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>5.2</v>
+        <v>1.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N33" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.75</v>
+        <v>1.36</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.62</v>
+        <v>1.87</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>3.15</v>
       </c>
       <c r="N35" t="n">
-        <v>2.67</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2013,10 +2013,10 @@
         <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>2.24</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>3.01</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.16</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>2.49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.13</v>
+        <v>2.93</v>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>5.1</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AB22" t="n">
         <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.83</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>3.01</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>2.23</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.58</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3435,16 +3435,16 @@
         <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="N30" t="n">
-        <v>2.59</v>
+        <v>1.84</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.67</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>2.69</v>
+        <v>5.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="M34" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="N34" t="n">
-        <v>8.9</v>
+        <v>2.98</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB34" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M35" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1888,10 +1888,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,16 +2007,16 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>3.96</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
         <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.33</v>
       </c>
-      <c r="V17" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>3.16</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N19" t="n">
-        <v>3.03</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>2.13</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="M20" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,16 +2840,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.16</v>
+        <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA25" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N26" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>2.49</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>2.93</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>3.06</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3673,16 +3673,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>2.67</v>
+        <v>8.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>1.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>3.97</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>1.78</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>1.55</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>2.69</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>5.2</v>
+        <v>2.67</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4431,7 +4431,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="M34" t="n">
-        <v>3.15</v>
+        <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>2.98</v>
+        <v>2.59</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>2.02</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.7</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N35" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.16</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.16</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.13</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>2.93</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,16 +2840,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O22" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="P22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3.25</v>
       </c>
-      <c r="N22" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
-      <c r="V22" t="n">
-        <v>0</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0</v>
-      </c>
-      <c r="X22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>0</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="M25" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>3.01</v>
       </c>
       <c r="O25" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.66</v>
+        <v>3.16</v>
       </c>
       <c r="M26" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="N26" t="n">
-        <v>4.9</v>
+        <v>2.29</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.82</v>
+        <v>2.13</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.49</v>
+        <v>1.67</v>
       </c>
       <c r="M27" t="n">
-        <v>2.93</v>
+        <v>3.65</v>
       </c>
       <c r="N27" t="n">
-        <v>3.06</v>
+        <v>5.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3673,16 +3673,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.97</v>
+        <v>1.26</v>
       </c>
       <c r="M29" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N29" t="n">
-        <v>1.78</v>
+        <v>8.9</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.61</v>
+        <v>3.15</v>
       </c>
       <c r="N30" t="n">
-        <v>1.84</v>
+        <v>2.98</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.82</v>
+        <v>2.02</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>4.3</v>
+        <v>3.61</v>
       </c>
       <c r="N31" t="n">
-        <v>5.2</v>
+        <v>1.84</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>5.2</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="M34" t="n">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="N34" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.4</v>
+        <v>3.97</v>
       </c>
       <c r="M35" t="n">
-        <v>3.15</v>
+        <v>3.92</v>
       </c>
       <c r="N35" t="n">
-        <v>2.98</v>
+        <v>1.78</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>1.53</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1373,73 +1373,73 @@
         </is>
       </c>
       <c r="L8" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,13 +1849,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1894,10 +1894,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.83</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="N17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB17" t="n">
+      <c r="AF17" t="n">
         <v>1.91</v>
       </c>
-      <c r="AC17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>0</v>
-      </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.4</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N19" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2721,16 +2721,16 @@
         <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.49</v>
+        <v>2.44</v>
       </c>
       <c r="M20" t="n">
-        <v>2.93</v>
+        <v>3.05</v>
       </c>
       <c r="N20" t="n">
-        <v>3.06</v>
+        <v>3.01</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2840,16 +2840,16 @@
         <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>5.4</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.83</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2965,10 +2965,10 @@
         <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.76</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.25</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>2.8</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.44</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>3.01</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.23</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.58</v>
+        <v>1.76</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="M26" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="N26" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.67</v>
+        <v>3.16</v>
       </c>
       <c r="M27" t="n">
-        <v>3.65</v>
+        <v>3.16</v>
       </c>
       <c r="N27" t="n">
-        <v>5.1</v>
+        <v>2.29</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2</v>
+        <v>2.13</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N28" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,10 +3798,10 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>8.9</v>
+        <v>1.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>3.61</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.82</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.92</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>5.2</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.52</v>
       </c>
       <c r="N33" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.69</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="M35" t="n">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.89</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>3.89</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,13 +2206,13 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -2245,10 +2245,10 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M18" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N18" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.44</v>
+        <v>1.83</v>
       </c>
       <c r="M20" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N20" t="n">
-        <v>3.01</v>
+        <v>4.1</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.23</v>
+        <v>1.83</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,13 +2920,13 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.4</v>
+        <v>2.49</v>
       </c>
       <c r="M21" t="n">
-        <v>3.83</v>
+        <v>2.93</v>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2959,16 +2959,16 @@
         <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,13 +3039,13 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.23</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>1.66</v>
       </c>
       <c r="M23" t="n">
-        <v>3.45</v>
+        <v>3.8</v>
       </c>
       <c r="N23" t="n">
-        <v>2.8</v>
+        <v>4.9</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>3.83</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V25" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.83</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>4.1</v>
+        <v>3.03</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3560,10 +3560,10 @@
         <v>0</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.91</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.62</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.32</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.59</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.87</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M30" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,10 +4036,10 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>1.78</v>
+        <v>8.9</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>2.98</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.42</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.52</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>2.69</v>
+        <v>1.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="N34" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
         <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="M9" t="n">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="N9" t="n">
         <v>2.02</v>
       </c>
       <c r="O9" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="R9" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="S9" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="T9" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="V9" t="n">
-        <v>8.5</v>
+        <v>7.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.18</v>
+        <v>2.07</v>
       </c>
       <c r="AB9" t="n">
         <v>1.7</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.89</v>
+        <v>3.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AF9" t="n">
         <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1620,64 +1620,64 @@
         <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.50347222222</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -2007,10 +2007,10 @@
         <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
@@ -2096,40 +2096,40 @@
         <v>6.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA14" t="n">
         <v>2.35</v>
@@ -2138,22 +2138,22 @@
         <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.24</v>
+        <v>2.13</v>
       </c>
       <c r="AB17" t="n">
         <v>1.64</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,13 +2563,13 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.67</v>
+        <v>2.44</v>
       </c>
       <c r="M18" t="n">
-        <v>3.65</v>
+        <v>3.05</v>
       </c>
       <c r="N18" t="n">
-        <v>5.1</v>
+        <v>3.01</v>
       </c>
       <c r="O18" t="n">
         <v>0</v>
@@ -2608,10 +2608,10 @@
         <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2</v>
+        <v>2.23</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>1.66</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O19" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,13 +2801,13 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.83</v>
+        <v>2.3</v>
       </c>
       <c r="M20" t="n">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="N20" t="n">
-        <v>4.1</v>
+        <v>2.8</v>
       </c>
       <c r="O20" t="n">
         <v>0</v>
@@ -2846,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.49</v>
+        <v>2.75</v>
       </c>
       <c r="M21" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>2.25</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,13 +3158,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M23" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N23" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3203,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="M24" t="n">
-        <v>3.45</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>2.8</v>
+        <v>3.03</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,13 +3515,13 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>2.49</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>2.93</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>3.06</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -3554,16 +3554,16 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,13 +3634,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="M27" t="n">
-        <v>3.16</v>
+        <v>3.55</v>
       </c>
       <c r="N27" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3679,10 +3679,10 @@
         <v>0</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.64</v>
+        <v>1.91</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.62</v>
+        <v>4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.61</v>
       </c>
       <c r="N29" t="n">
-        <v>2.59</v>
+        <v>1.84</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,10 +3917,10 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M32" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N32" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.84</v>
+        <v>5.2</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>3.97</v>
+        <v>2.62</v>
       </c>
       <c r="M34" t="n">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="N34" t="n">
-        <v>1.78</v>
+        <v>2.59</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="N35" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB35" t="n">
         <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1739,40 +1739,40 @@
         <v>1.57</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57</v>
@@ -1787,16 +1787,16 @@
         <v>1.75</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.52083333334</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2334,40 +2334,40 @@
         <v>1.39</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>4.61</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA16" t="n">
         <v>1.4</v>
@@ -2382,16 +2382,16 @@
         <v>1.87</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.61458333334</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,13 +2444,13 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
         <v>0</v>
@@ -2489,10 +2489,10 @@
         <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,13 +2682,13 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.66</v>
+        <v>2.3</v>
       </c>
       <c r="M19" t="n">
-        <v>3.8</v>
+        <v>3.45</v>
       </c>
       <c r="N19" t="n">
-        <v>4.9</v>
+        <v>2.8</v>
       </c>
       <c r="O19" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="N20" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.75</v>
+        <v>3.16</v>
       </c>
       <c r="M21" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="N21" t="n">
         <v>2.29</v>
       </c>
       <c r="O21" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.94</v>
+        <v>2.13</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.76</v>
+        <v>1.64</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M22" t="n">
         <v>3.25</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N22" t="n">
-        <v>2.25</v>
+        <v>3.03</v>
       </c>
       <c r="O22" t="n">
-        <v>3.48</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.09</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.24</v>
+        <v>2.02</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="M23" t="n">
-        <v>3.65</v>
+        <v>3.15</v>
       </c>
       <c r="N23" t="n">
-        <v>5.1</v>
+        <v>2.25</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA23" t="n">
-        <v>2</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,13 +3277,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.32</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>3.03</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3322,10 +3322,10 @@
         <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB32" t="n">
         <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="M35" t="n">
-        <v>3.41</v>
+        <v>3.52</v>
       </c>
       <c r="N35" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AB35" t="n">
         <v>2</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,73 +1492,73 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.5</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>3.1</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.14</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>2.32</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.82</v>
+        <v>2.19</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.92</v>
+        <v>1.65</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.44</v>
+        <v>3.25</v>
       </c>
       <c r="M18" t="n">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="N18" t="n">
-        <v>3.01</v>
+        <v>2.25</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.48</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M19" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N19" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.13</v>
+        <v>3.04</v>
       </c>
       <c r="N20" t="n">
+        <v>3</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V20" t="n">
+        <v>8</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA20" t="n">
         <v>2.29</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.96</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB20" t="n">
-        <v>1.76</v>
+        <v>1.6</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.76</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.11</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.16</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.16</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.29</v>
+        <v>1.6</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>5.68</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.13</v>
+        <v>1.93</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.64</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.32</v>
+        <v>1.69</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.52</v>
       </c>
       <c r="N22" t="n">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.42</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>3.25</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.15</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>3.96</v>
       </c>
       <c r="P23" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.02</v>
+        <v>2.75</v>
       </c>
       <c r="R23" t="n">
         <v>1.4</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.97</v>
       </c>
       <c r="T23" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.33</v>
       </c>
-      <c r="V23" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.19</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>2.11</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.94</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,13 +3396,13 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>2.3</v>
       </c>
       <c r="M25" t="n">
-        <v>3.83</v>
+        <v>3.45</v>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>2.8</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
@@ -3441,10 +3441,10 @@
         <v>0</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="N26" t="n">
-        <v>3.06</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB26" t="n">
         <v>1.5</v>
       </c>
-      <c r="Z26" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="M27" t="n">
-        <v>3.55</v>
+        <v>3.62</v>
       </c>
       <c r="N27" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA27" t="n">
         <v>1.83</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,13 +3872,13 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>3.61</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
-        <v>1.84</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -3917,16 +3917,16 @@
         <v>0</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.82</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AE29" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.97</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.92</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>8.9</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>1.87</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>2.62</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>3.32</v>
       </c>
       <c r="N31" t="n">
-        <v>8.9</v>
+        <v>2.59</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.87</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.1</v>
+        <v>1.87</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M32" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N32" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB32" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>5.2</v>
+        <v>1.84</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,16 +4393,16 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="M34" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N34" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,10 +4512,10 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB34" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.42</v>
+        <v>2.27</v>
       </c>
       <c r="M35" t="n">
-        <v>3.52</v>
+        <v>3.22</v>
       </c>
       <c r="N35" t="n">
-        <v>2.69</v>
+        <v>3.04</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,16 +4631,16 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.75</v>
+        <v>2.02</v>
       </c>
       <c r="AB35" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AC35" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>4.32</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="M17" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="N17" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.96</v>
       </c>
       <c r="P17" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="R17" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="S17" t="n">
-        <v>2.5</v>
+        <v>2.97</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="V17" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X17" t="n">
         <v>1.04</v>
       </c>
-      <c r="X17" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y17" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.76</v>
+        <v>3.25</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.19</v>
+        <v>1.94</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.76</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.78</v>
+        <v>3.55</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.83</v>
+        <v>1.76</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.25</v>
+        <v>2.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.15</v>
+        <v>3.04</v>
       </c>
       <c r="N18" t="n">
-        <v>2.25</v>
+        <v>3</v>
       </c>
       <c r="O18" t="n">
-        <v>3.48</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>2.09</v>
+        <v>2.05</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.02</v>
+        <v>3.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="T18" t="n">
-        <v>2.95</v>
+        <v>3.34</v>
       </c>
       <c r="U18" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V18" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.24</v>
+        <v>2.29</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.05</v>
+        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
         <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.36</v>
+        <v>1.52</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.25</v>
+        <v>1.65</v>
       </c>
       <c r="M19" t="n">
-        <v>3.23</v>
+        <v>3.7</v>
       </c>
       <c r="N19" t="n">
-        <v>3.02</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.96</v>
+        <v>2.17</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.78</v>
+        <v>5.25</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.05</v>
+        <v>1.84</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.74</v>
+        <v>1.94</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>2.2</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.4</v>
+        <v>3.25</v>
       </c>
       <c r="M20" t="n">
-        <v>3.04</v>
+        <v>3.15</v>
       </c>
       <c r="N20" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="O20" t="n">
-        <v>3</v>
+        <v>3.48</v>
       </c>
       <c r="P20" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.78</v>
+        <v>3.02</v>
       </c>
       <c r="R20" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.44</v>
+        <v>2.62</v>
       </c>
       <c r="T20" t="n">
-        <v>3.34</v>
+        <v>2.95</v>
       </c>
       <c r="U20" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.2</v>
+        <v>4.05</v>
       </c>
       <c r="AD20" t="n">
         <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.79</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.52</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.5</v>
+        <v>1.82</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.62</v>
       </c>
       <c r="N21" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="O21" t="n">
-        <v>5.68</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>2.32</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.12</v>
+        <v>4.78</v>
       </c>
       <c r="R21" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W21" t="n">
         <v>1.05</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.5</v>
+        <v>2.94</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>2.01</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.69</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.52</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>4.92</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="O23" t="n">
-        <v>3.96</v>
+        <v>3.6</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S23" t="n">
-        <v>2.97</v>
+        <v>2.5</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="U23" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
         <v>1.08</v>
       </c>
-      <c r="X23" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y23" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.25</v>
+        <v>2.76</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.55</v>
+        <v>3.78</v>
       </c>
       <c r="AD23" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG23" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AH23" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="M24" t="n">
-        <v>3.7</v>
+        <v>3.52</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="O24" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
         <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.25</v>
+        <v>5.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>6.95</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.84</v>
+        <v>2.03</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.94</v>
+        <v>1.76</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.9</v>
+        <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.45</v>
+        <v>3.23</v>
       </c>
       <c r="N25" t="n">
-        <v>2.8</v>
+        <v>3.02</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>5.5</v>
       </c>
       <c r="M26" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="N26" t="n">
-        <v>3.1</v>
+        <v>1.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3.15</v>
+        <v>5.68</v>
       </c>
       <c r="P26" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.75</v>
+        <v>2.12</v>
       </c>
       <c r="R26" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S26" t="n">
-        <v>2.31</v>
+        <v>2.77</v>
       </c>
       <c r="T26" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V26" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z26" t="n">
         <v>3.5</v>
       </c>
-      <c r="U26" t="n">
+      <c r="AA26" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.24</v>
       </c>
-      <c r="V26" t="n">
-        <v>9</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.82</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.62</v>
+        <v>3</v>
       </c>
       <c r="N27" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O27" t="n">
-        <v>2.38</v>
+        <v>3.15</v>
       </c>
       <c r="P27" t="n">
-        <v>2.32</v>
+        <v>1.87</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.78</v>
+        <v>3.75</v>
       </c>
       <c r="R27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V27" t="n">
+        <v>9</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.36</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,13 +3753,13 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>6</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>8.9</v>
       </c>
       <c r="O28" t="n">
         <v>0</v>
@@ -3798,16 +3798,16 @@
         <v>0</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>1.36</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>3.1</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.6</v>
+        <v>1.87</v>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,13 +3991,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M30" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4036,16 +4036,16 @@
         <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,13 +4110,13 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.62</v>
+        <v>3.97</v>
       </c>
       <c r="M31" t="n">
-        <v>3.32</v>
+        <v>3.92</v>
       </c>
       <c r="N31" t="n">
-        <v>2.59</v>
+        <v>1.78</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -4155,16 +4155,16 @@
         <v>0</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.87</v>
+        <v>1.53</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.87</v>
+        <v>2.45</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,13 +4229,13 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.97</v>
+        <v>2.27</v>
       </c>
       <c r="M32" t="n">
-        <v>3.92</v>
+        <v>3.22</v>
       </c>
       <c r="N32" t="n">
-        <v>1.78</v>
+        <v>3.04</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -4274,16 +4274,16 @@
         <v>0</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.53</v>
+        <v>2.02</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,13 +4348,13 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>2.62</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>3.32</v>
       </c>
       <c r="N33" t="n">
-        <v>1.84</v>
+        <v>2.59</v>
       </c>
       <c r="O33" t="n">
         <v>0</v>
@@ -4393,10 +4393,10 @@
         <v>0</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.92</v>
+        <v>1.87</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="M34" t="n">
-        <v>3.41</v>
+        <v>4.3</v>
       </c>
       <c r="N34" t="n">
-        <v>2.67</v>
+        <v>5.2</v>
       </c>
       <c r="O34" t="n">
         <v>0</v>
@@ -4512,16 +4512,16 @@
         <v>0</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.8</v>
+        <v>1.58</v>
       </c>
       <c r="AB34" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD34" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,13 +4586,13 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>2.27</v>
+        <v>4</v>
       </c>
       <c r="M35" t="n">
-        <v>3.22</v>
+        <v>3.61</v>
       </c>
       <c r="N35" t="n">
-        <v>3.04</v>
+        <v>1.84</v>
       </c>
       <c r="O35" t="n">
         <v>0</v>
@@ -4631,10 +4631,10 @@
         <v>0</v>
       </c>
       <c r="AA35" t="n">
-        <v>2.02</v>
+        <v>1.82</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.7</v>
+        <v>1.92</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -871,12 +871,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Stade Tunisien</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Stade Tunisien</t>
+          <t>Zarzis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1751,16 +1751,16 @@
         <v>1.23</v>
       </c>
       <c r="S11" t="n">
-        <v>3.65</v>
+        <v>3.94</v>
       </c>
       <c r="T11" t="n">
-        <v>2.49</v>
+        <v>2.36</v>
       </c>
       <c r="U11" t="n">
         <v>1.61</v>
       </c>
       <c r="V11" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="W11" t="n">
         <v>1.13</v>
@@ -1769,10 +1769,10 @@
         <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA11" t="n">
         <v>1.57</v>
@@ -1790,10 +1790,10 @@
         <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.22</v>
+        <v>1.19</v>
       </c>
       <c r="AH11" t="n">
         <v>1.15</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,73 +2087,73 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.32</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2334,25 +2334,25 @@
         <v>1.39</v>
       </c>
       <c r="O16" t="n">
-        <v>4.61</v>
+        <v>5.5</v>
       </c>
       <c r="P16" t="n">
         <v>3</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="R16" t="n">
         <v>1.16</v>
       </c>
       <c r="S16" t="n">
-        <v>4.2</v>
+        <v>4.85</v>
       </c>
       <c r="T16" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="U16" t="n">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="V16" t="n">
         <v>3.75</v>
@@ -2385,7 +2385,7 @@
         <v>1.5</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AG16" t="n">
         <v>1.15</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="N17" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.96</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.4</v>
+        <v>3.16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.04</v>
+        <v>3.16</v>
       </c>
       <c r="N18" t="n">
-        <v>3</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.05</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC18" t="n">
         <v>3.78</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="T18" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V18" t="n">
-        <v>8</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.2</v>
       </c>
       <c r="AD18" t="n">
         <v>1.19</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>1.83</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.79</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.65</v>
+        <v>2.44</v>
       </c>
       <c r="M19" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>3.01</v>
       </c>
       <c r="O19" t="n">
-        <v>2.17</v>
+        <v>3.2</v>
       </c>
       <c r="P19" t="n">
-        <v>2.15</v>
+        <v>1.91</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.25</v>
+        <v>3.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="T19" t="n">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="U19" t="n">
-        <v>1.45</v>
+        <v>1.28</v>
       </c>
       <c r="V19" t="n">
-        <v>6.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.23</v>
+        <v>1.4</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.6</v>
+        <v>2.68</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.94</v>
+        <v>1.58</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.36</v>
+        <v>1.16</v>
       </c>
       <c r="AE19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF19" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.35</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.2</v>
+        <v>1.52</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.25</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.15</v>
+        <v>3.65</v>
       </c>
       <c r="N20" t="n">
-        <v>2.25</v>
+        <v>5.1</v>
       </c>
       <c r="O20" t="n">
-        <v>3.48</v>
+        <v>2.3</v>
       </c>
       <c r="P20" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.02</v>
+        <v>5.42</v>
       </c>
       <c r="R20" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V20" t="n">
-        <v>8.5</v>
+        <v>6.95</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.92</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.05</v>
+        <v>3.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.26</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>2.06</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.82</v>
+        <v>3.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.62</v>
+        <v>3.15</v>
       </c>
       <c r="N21" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="O21" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P21" t="n">
-        <v>2.32</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>4.78</v>
+        <v>2.8</v>
       </c>
       <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.36</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
+      <c r="Z21" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.28</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>1.94</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M22" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N22" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O22" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P22" t="n">
         <v>2.3</v>
       </c>
-      <c r="M22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N22" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="M23" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N23" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O23" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V23" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z23" t="n">
         <v>3.1</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="O23" t="n">
+      <c r="AA23" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.6</v>
       </c>
-      <c r="P23" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.78</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.83</v>
+        <v>2.06</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.69</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.52</v>
+        <v>3.83</v>
       </c>
       <c r="N24" t="n">
-        <v>4.92</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>5.68</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.42</v>
+        <v>2.18</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.77</v>
       </c>
       <c r="T24" t="n">
-        <v>2.94</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="V24" t="n">
-        <v>6.95</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.76</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AF24" t="n">
         <v>1.77</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.06</v>
+        <v>1.13</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.25</v>
+        <v>2.49</v>
       </c>
       <c r="M25" t="n">
-        <v>3.23</v>
+        <v>2.93</v>
       </c>
       <c r="N25" t="n">
-        <v>3.02</v>
+        <v>3.06</v>
       </c>
       <c r="O25" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.57</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>2.31</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>3.5</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>2.4</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE25" t="n">
         <v>2.05</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>1.73</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>5.5</v>
+        <v>2.32</v>
       </c>
       <c r="M26" t="n">
-        <v>3.9</v>
+        <v>3.25</v>
       </c>
       <c r="N26" t="n">
-        <v>1.6</v>
+        <v>3.03</v>
       </c>
       <c r="O26" t="n">
-        <v>5.68</v>
+        <v>2.9</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="R26" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T26" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X26" t="n">
         <v>1.05</v>
       </c>
-      <c r="X26" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y26" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF26" t="n">
         <v>1.93</v>
       </c>
-      <c r="AB26" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>1.79</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>1.66</v>
       </c>
       <c r="M27" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="N27" t="n">
-        <v>3.1</v>
+        <v>4.9</v>
       </c>
       <c r="O27" t="n">
-        <v>3.15</v>
+        <v>2.17</v>
       </c>
       <c r="P27" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="U27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V27" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.24</v>
       </c>
-      <c r="V27" t="n">
-        <v>9</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="M28" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="N28" t="n">
-        <v>8.9</v>
+        <v>2.98</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB28" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC28" t="n">
-        <v>1.87</v>
+        <v>3.54</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3881,40 +3881,40 @@
         <v>2.69</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.54</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
         <v>1.75</v>
@@ -3929,16 +3929,16 @@
         <v>1.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4000,40 +4000,40 @@
         <v>2.67</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>6.45</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AA30" t="n">
         <v>1.8</v>
@@ -4042,22 +4042,22 @@
         <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4119,40 +4119,40 @@
         <v>1.78</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AA31" t="n">
         <v>1.53</v>
@@ -4167,16 +4167,16 @@
         <v>1.65</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.27</v>
+        <v>1.55</v>
       </c>
       <c r="M32" t="n">
-        <v>3.22</v>
+        <v>4.3</v>
       </c>
       <c r="N32" t="n">
-        <v>3.04</v>
+        <v>5.2</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AA32" t="n">
-        <v>2.02</v>
+        <v>1.58</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.7</v>
+        <v>2.38</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4357,40 +4357,40 @@
         <v>2.59</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AA33" t="n">
         <v>1.87</v>
@@ -4399,22 +4399,22 @@
         <v>1.87</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4441,12 +4441,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -4467,73 +4467,73 @@
         </is>
       </c>
       <c r="L34" t="n">
-        <v>1.55</v>
+        <v>4</v>
       </c>
       <c r="M34" t="n">
-        <v>4.3</v>
+        <v>3.61</v>
       </c>
       <c r="N34" t="n">
-        <v>5.2</v>
+        <v>1.84</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S34" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="U34" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="V34" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W34" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y34" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA34" t="n">
-        <v>1.58</v>
+        <v>1.82</v>
       </c>
       <c r="AB34" t="n">
-        <v>2.38</v>
+        <v>1.92</v>
       </c>
       <c r="AC34" t="n">
-        <v>2.35</v>
+        <v>3.3</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.6</v>
+        <v>1.33</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG34" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH34" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI34" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4560,12 +4560,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -4586,73 +4586,73 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>4</v>
+        <v>1.26</v>
       </c>
       <c r="M35" t="n">
-        <v>3.61</v>
+        <v>6</v>
       </c>
       <c r="N35" t="n">
-        <v>1.84</v>
+        <v>8.9</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="S35" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y35" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AA35" t="n">
-        <v>1.82</v>
+        <v>1.36</v>
       </c>
       <c r="AB35" t="n">
-        <v>1.92</v>
+        <v>3.1</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD35" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE35" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF35" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG35" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AH35" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AI35" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI35"/>
+  <dimension ref="A1:AI33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -975,12 +975,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zarzis</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,76 +1016,76 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
-        <v>46042.41666666666</v>
+        <v>46042.5</v>
       </c>
     </row>
     <row r="6">
@@ -1094,12 +1094,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1204,7 +1204,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
-        <v>46042.41666666666</v>
+        <v>46042.5</v>
       </c>
     </row>
     <row r="7">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Al Najma</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1382,67 +1382,67 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AI8" s="3" t="n">
-        <v>46042.5</v>
+        <v>46042.50347222222</v>
       </c>
     </row>
     <row r="9">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Club Brugge</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1492,76 +1492,76 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.94</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AI9" s="3" t="n">
-        <v>46042.5</v>
+        <v>46042.52083333334</v>
       </c>
     </row>
     <row r="10">
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Najma</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,76 +1611,76 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.45</v>
+        <v>6.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>2.62</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>2.8</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>6.75</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
         <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.08</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.76</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.28</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.24</v>
+        <v>2.45</v>
       </c>
       <c r="AI10" s="3" t="n">
-        <v>46042.50347222222</v>
+        <v>46042.60416666666</v>
       </c>
     </row>
     <row r="11">
@@ -1689,12 +1689,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Club Brugge</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,76 +1730,76 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>1.57</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>5.2</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.1</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>3.94</v>
+        <v>2.07</v>
       </c>
       <c r="T11" t="n">
-        <v>2.36</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.61</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
-        <v>5.5</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>1.13</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.18</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>4.33</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.57</v>
+        <v>3.03</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.25</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.1</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.75</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.19</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
-        <v>46042.52083333334</v>
+        <v>46042.60416666666</v>
       </c>
     </row>
     <row r="12">
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2046,12 +2046,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>FK Bodo - Glimt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2087,76 +2087,76 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>4.85</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" s="3" t="n">
-        <v>46042.60416666666</v>
+        <v>46042.61458333334</v>
       </c>
     </row>
     <row r="15">
@@ -2165,12 +2165,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,76 +2206,76 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.5</v>
+        <v>3.13</v>
       </c>
       <c r="N15" t="n">
-        <v>6.7</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>6.5</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.41</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>3.25</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>9.1</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.63</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.35</v>
+        <v>1.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.25</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.57</v>
+        <v>2.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.45</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
-        <v>46042.60416666666</v>
+        <v>46042.69791666666</v>
       </c>
     </row>
     <row r="16">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FK Bodo - Glimt</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,76 +2325,76 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.9</v>
+        <v>2.44</v>
       </c>
       <c r="M16" t="n">
-        <v>5.6</v>
+        <v>3.05</v>
       </c>
       <c r="N16" t="n">
-        <v>1.39</v>
+        <v>3.01</v>
       </c>
       <c r="O16" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V16" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.8</v>
       </c>
-      <c r="R16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="S16" t="n">
-        <v>4.85</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V16" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>7</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AG16" t="n">
-        <v>1.15</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.13</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" s="3" t="n">
-        <v>46042.61458333334</v>
+        <v>46042.69791666666</v>
       </c>
     </row>
     <row r="17">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="M19" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="O19" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P19" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="R19" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S19" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T19" t="n">
-        <v>3.34</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.65</v>
+        <v>2.93</v>
       </c>
       <c r="N20" t="n">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.42</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="T20" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="V20" t="n">
-        <v>6.95</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,25 +3039,25 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="O22" t="n">
-        <v>2.38</v>
+        <v>2.17</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.78</v>
+        <v>5.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S22" t="n">
         <v>2.89</v>
@@ -3069,43 +3069,43 @@
         <v>1.42</v>
       </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>6.1</v>
       </c>
       <c r="W22" t="n">
         <v>1.06</v>
       </c>
       <c r="X22" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="Z22" t="n">
         <v>3.85</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AC22" t="n">
         <v>2.89</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.01</v>
+        <v>1.9</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.94</v>
+        <v>2.19</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.3</v>
+        <v>2.38</v>
       </c>
       <c r="P23" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.78</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AF23" t="n">
         <v>2.01</v>
       </c>
-      <c r="Q23" t="n">
-        <v>3</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T23" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V23" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA23" t="n">
+      <c r="AG23" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH23" t="n">
         <v>1.94</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AG23" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH23" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.83</v>
+        <v>3.65</v>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>5.1</v>
       </c>
       <c r="O24" t="n">
-        <v>5.68</v>
+        <v>2.3</v>
       </c>
       <c r="P24" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.18</v>
+        <v>5.42</v>
       </c>
       <c r="R24" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="U24" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6.95</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.13</v>
+        <v>2.06</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.49</v>
+        <v>5.4</v>
       </c>
       <c r="M25" t="n">
-        <v>2.93</v>
+        <v>3.83</v>
       </c>
       <c r="N25" t="n">
-        <v>3.06</v>
+        <v>1.61</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>5.68</v>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>2.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="R25" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="S25" t="n">
-        <v>2.31</v>
+        <v>2.77</v>
       </c>
       <c r="T25" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.5</v>
       </c>
-      <c r="U25" t="n">
+      <c r="AA25" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AG25" t="n">
         <v>1.24</v>
       </c>
-      <c r="V25" t="n">
-        <v>9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG25" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,76 +3515,76 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.32</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>3.25</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>3.03</v>
+        <v>8.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.9</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.03</v>
+        <v>2.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.45</v>
+        <v>7.5</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>2.69</v>
+        <v>4.45</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>1.97</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="V26" t="n">
-        <v>7.9</v>
+        <v>3.84</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.33</v>
+        <v>1.09</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>6.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.54</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.31</v>
+        <v>1.13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>3.6</v>
       </c>
       <c r="AI26" s="3" t="n">
-        <v>46042.69791666666</v>
+        <v>46042.70833333334</v>
       </c>
     </row>
     <row r="27">
@@ -3593,12 +3593,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,49 +3634,49 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.66</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.8</v>
+        <v>3.61</v>
       </c>
       <c r="N27" t="n">
-        <v>4.9</v>
+        <v>1.84</v>
       </c>
       <c r="O27" t="n">
-        <v>2.17</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.35</v>
+        <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.1</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="S27" t="n">
         <v>2.89</v>
       </c>
       <c r="T27" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V27" t="n">
-        <v>6.1</v>
+        <v>6.75</v>
       </c>
       <c r="W27" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.85</v>
+        <v>3.4</v>
       </c>
       <c r="AA27" t="n">
         <v>1.82</v>
@@ -3685,25 +3685,25 @@
         <v>1.92</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF27" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.19</v>
+        <v>1.26</v>
       </c>
       <c r="AI27" s="3" t="n">
-        <v>46042.69791666666</v>
+        <v>46042.70833333334</v>
       </c>
     </row>
     <row r="28">
@@ -3717,7 +3717,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M28" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="R28" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="T28" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="U28" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="V28" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="W28" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X28" t="n">
         <v>1.02</v>
       </c>
-      <c r="X28" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y28" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.54</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF28" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>3.97</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>3.92</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>1.78</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.32</v>
+        <v>2.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="S29" t="n">
-        <v>3.24</v>
+        <v>3.5</v>
       </c>
       <c r="T29" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="U29" t="n">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.14</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG29" t="n">
         <v>2</v>
       </c>
-      <c r="AC29" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>4.3</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>5.2</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="T30" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V30" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF30" t="n">
         <v>2.5</v>
       </c>
-      <c r="U30" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V30" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC30" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF30" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.97</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.92</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="O31" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.78</v>
       </c>
-      <c r="O31" t="n">
-        <v>4</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF31" t="n">
-        <v>2.35</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>2</v>
+        <v>1.32</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>1.58</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="M32" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>5.2</v>
+        <v>2.59</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>5.05</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3.94</v>
+        <v>3.02</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="U32" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="V32" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,67 +4348,67 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
       <c r="M33" t="n">
-        <v>3.32</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>2.59</v>
+        <v>2.67</v>
       </c>
       <c r="O33" t="n">
-        <v>3.28</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="Q33" t="n">
         <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="S33" t="n">
-        <v>3.02</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.44</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
-        <v>7.2</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
         <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.14</v>
+        <v>2.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.68</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
         <v>1.3</v>
@@ -4417,244 +4417,6 @@
         <v>1.5</v>
       </c>
       <c r="AI33" s="3" t="n">
-        <v>46042.70833333334</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="n">
-        <v>46042</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>København</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Napoli</t>
-        </is>
-      </c>
-      <c r="G34" t="n">
-        <v>0</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>4</v>
-      </c>
-      <c r="M34" t="n">
-        <v>3.61</v>
-      </c>
-      <c r="N34" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="O34" t="n">
-        <v>4</v>
-      </c>
-      <c r="P34" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="R34" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S34" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T34" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U34" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V34" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W34" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X34" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y34" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z34" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA34" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC34" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AD34" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE34" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF34" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG34" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH34" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI34" s="3" t="n">
-        <v>46042.70833333334</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="n">
-        <v>46042</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Europe UEFA Champions League</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Real Madrid</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Monaco</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="M35" t="n">
-        <v>6</v>
-      </c>
-      <c r="N35" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P35" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q35" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R35" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S35" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T35" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U35" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V35" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AI35" s="3" t="n">
         <v>46042.70833333334</v>
       </c>
     </row>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.75</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.13</v>
+        <v>3.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>2.8</v>
       </c>
       <c r="O15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="P16" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.88</v>
+        <v>3.45</v>
       </c>
       <c r="R16" t="n">
-        <v>1.49</v>
+        <v>1.41</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="T16" t="n">
-        <v>3.34</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>9.199999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.68</v>
+        <v>3.08</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.23</v>
+        <v>2.02</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.2</v>
+        <v>3.54</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.16</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.52</v>
+        <v>1.57</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="N17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="M18" t="n">
-        <v>3.16</v>
+        <v>3.83</v>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>5.68</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="T18" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,28 +2682,28 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.32</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>3.03</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S19" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
         <v>2.99</v>
@@ -2718,37 +2718,37 @@
         <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.7</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.49</v>
+        <v>3.16</v>
       </c>
       <c r="M20" t="n">
-        <v>2.93</v>
+        <v>3.16</v>
       </c>
       <c r="N20" t="n">
-        <v>3.06</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="P20" t="n">
-        <v>1.87</v>
+        <v>1.97</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.75</v>
+        <v>2.97</v>
       </c>
       <c r="R20" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="S20" t="n">
-        <v>2.31</v>
+        <v>2.5</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="U20" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.4</v>
+        <v>2.76</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.44</v>
+        <v>2.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.4</v>
+        <v>3.78</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.14</v>
+        <v>1.19</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.25</v>
+        <v>1.66</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.8</v>
       </c>
       <c r="N21" t="n">
-        <v>2.25</v>
+        <v>4.9</v>
       </c>
       <c r="O21" t="n">
-        <v>3.75</v>
+        <v>2.17</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.35</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="R21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="U21" t="n">
         <v>1.42</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.33</v>
-      </c>
       <c r="V21" t="n">
-        <v>8.5</v>
+        <v>6.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y21" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD21" t="n">
         <v>1.36</v>
       </c>
-      <c r="Z21" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.2</v>
-      </c>
       <c r="AE21" t="n">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>2.19</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="N22" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="O22" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="P22" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.1</v>
+        <v>5.42</v>
       </c>
       <c r="R22" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>6.1</v>
+        <v>6.95</v>
       </c>
       <c r="W22" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.85</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.92</v>
+        <v>1.72</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.89</v>
+        <v>3.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.9</v>
+        <v>1.79</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.19</v>
+        <v>2.06</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>2.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>3.01</v>
       </c>
       <c r="O23" t="n">
-        <v>2.38</v>
+        <v>3.2</v>
       </c>
       <c r="P23" t="n">
-        <v>2.3</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.78</v>
+        <v>3.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.89</v>
+        <v>2.44</v>
       </c>
       <c r="T23" t="n">
-        <v>2.65</v>
+        <v>3.34</v>
       </c>
       <c r="U23" t="n">
-        <v>1.42</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.24</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.85</v>
+        <v>2.68</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>2.23</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.89</v>
+        <v>4.2</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.32</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.71</v>
+        <v>1.9</v>
       </c>
       <c r="AF23" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.94</v>
+        <v>1.52</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>2.49</v>
       </c>
       <c r="M24" t="n">
-        <v>3.65</v>
+        <v>2.93</v>
       </c>
       <c r="N24" t="n">
-        <v>5.1</v>
+        <v>3.06</v>
       </c>
       <c r="O24" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.42</v>
+        <v>3.75</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.57</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>2.31</v>
       </c>
       <c r="T24" t="n">
-        <v>2.94</v>
+        <v>3.5</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="V24" t="n">
-        <v>6.95</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="AA24" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.72</v>
+        <v>1.44</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.7</v>
+        <v>5.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.26</v>
+        <v>1.14</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.06</v>
+        <v>1.5</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.4</v>
+        <v>3.25</v>
       </c>
       <c r="M25" t="n">
-        <v>3.83</v>
+        <v>3.15</v>
       </c>
       <c r="N25" t="n">
-        <v>1.61</v>
+        <v>2.25</v>
       </c>
       <c r="O25" t="n">
-        <v>5.68</v>
+        <v>3.75</v>
       </c>
       <c r="P25" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="R25" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.77</v>
+        <v>2.63</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="U25" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>2.85</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.83</v>
+        <v>1.6</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.5</v>
+        <v>4.05</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>8.9</v>
+        <v>2.98</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>2.96</v>
       </c>
       <c r="P26" t="n">
-        <v>2.8</v>
+        <v>2.01</v>
       </c>
       <c r="Q26" t="n">
-        <v>7.5</v>
+        <v>3.85</v>
       </c>
       <c r="R26" t="n">
-        <v>1.19</v>
+        <v>1.42</v>
       </c>
       <c r="S26" t="n">
-        <v>4.45</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>1.97</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.8</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>3.84</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.24</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.09</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.2</v>
+        <v>3.05</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.36</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.1</v>
+        <v>1.7</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>3.54</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.87</v>
+        <v>1.22</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>3.97</v>
       </c>
       <c r="M27" t="n">
-        <v>3.61</v>
+        <v>3.92</v>
       </c>
       <c r="N27" t="n">
-        <v>1.84</v>
+        <v>1.78</v>
       </c>
       <c r="O27" t="n">
         <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V27" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB27" t="n">
         <v>2.45</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S27" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V27" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AC27" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.33</v>
+        <v>1.65</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="AF27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG27" t="n">
         <v>2</v>
       </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.42</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.32</v>
+        <v>5.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.24</v>
+        <v>3.94</v>
       </c>
       <c r="T28" t="n">
-        <v>2.54</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.51</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>4</v>
+        <v>5.45</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.97</v>
+        <v>2.62</v>
       </c>
       <c r="M29" t="n">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="N29" t="n">
-        <v>1.78</v>
+        <v>2.59</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P29" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="U29" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="V29" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
         <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.55</v>
+        <v>2.47</v>
       </c>
       <c r="M30" t="n">
-        <v>4.3</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>5.2</v>
+        <v>2.67</v>
       </c>
       <c r="O30" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V30" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>5.05</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V30" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA30" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.5</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.98</v>
+        <v>8.9</v>
       </c>
       <c r="O31" t="n">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.85</v>
+        <v>7.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>4.45</v>
       </c>
       <c r="T31" t="n">
-        <v>2.99</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="V31" t="n">
-        <v>7.9</v>
+        <v>3.84</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.32</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.05</v>
+        <v>6.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.54</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.22</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.32</v>
+        <v>1.13</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,67 +4229,67 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.62</v>
+        <v>2.42</v>
       </c>
       <c r="M32" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N32" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O32" t="n">
+        <v>3</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q32" t="n">
         <v>3.32</v>
       </c>
-      <c r="N32" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="P32" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.2</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="S32" t="n">
-        <v>3.02</v>
+        <v>3.24</v>
       </c>
       <c r="T32" t="n">
-        <v>2.77</v>
+        <v>2.54</v>
       </c>
       <c r="U32" t="n">
-        <v>1.44</v>
+        <v>1.51</v>
       </c>
       <c r="V32" t="n">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X32" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.14</v>
+        <v>2.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.35</v>
+        <v>1.62</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.47</v>
+        <v>4</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.61</v>
       </c>
       <c r="N33" t="n">
-        <v>2.67</v>
+        <v>1.84</v>
       </c>
       <c r="O33" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
-        <v>2.13</v>
+        <v>2.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="R33" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="S33" t="n">
-        <v>3.2</v>
+        <v>2.89</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.81</v>
       </c>
       <c r="U33" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="V33" t="n">
-        <v>6.45</v>
+        <v>6.75</v>
       </c>
       <c r="W33" t="n">
         <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AB33" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF33" t="n">
         <v>2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
         <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.5</v>
+        <v>1.26</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1382,46 +1382,46 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="P8" t="n">
-        <v>2.11</v>
+        <v>2.15</v>
       </c>
       <c r="Q8" t="n">
         <v>6.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T8" t="n">
         <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V8" t="n">
         <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="AC8" t="n">
         <v>3.28</v>
@@ -1430,7 +1430,7 @@
         <v>1.28</v>
       </c>
       <c r="AE8" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="AF8" t="n">
         <v>1.72</v>
@@ -1439,7 +1439,7 @@
         <v>1.2</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.50347222222</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.5</v>
+        <v>2.7</v>
       </c>
       <c r="N10" t="n">
-        <v>6.7</v>
+        <v>3.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q10" t="n">
-        <v>6.5</v>
+        <v>3.8</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.67</v>
       </c>
       <c r="S10" t="n">
-        <v>2.41</v>
+        <v>2.07</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>4.05</v>
       </c>
       <c r="U10" t="n">
-        <v>1.27</v>
+        <v>1.16</v>
       </c>
       <c r="V10" t="n">
-        <v>9.1</v>
+        <v>13</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.38</v>
+        <v>1.62</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.63</v>
+        <v>2.15</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.35</v>
+        <v>3.03</v>
       </c>
       <c r="AB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF10" t="n">
         <v>1.53</v>
       </c>
-      <c r="AC10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.45</v>
+        <v>1.44</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M15" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="N15" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>1.83</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>3.03</v>
+        <v>4.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.9</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.45</v>
+        <v>4.78</v>
       </c>
       <c r="R16" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>2.65</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.08</v>
+        <v>3.85</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.7</v>
+        <v>1.91</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.78</v>
+        <v>1.71</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.57</v>
+        <v>1.94</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>3.25</v>
       </c>
       <c r="M17" t="n">
-        <v>3.55</v>
+        <v>3.15</v>
       </c>
       <c r="N17" t="n">
-        <v>4.1</v>
+        <v>2.25</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.06</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.78</v>
+        <v>2.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="T17" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="W17" t="n">
         <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>2.17</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.89</v>
+        <v>4.05</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF17" t="n">
-        <v>2.01</v>
+        <v>1.8</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.94</v>
+        <v>1.28</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.4</v>
+        <v>3.16</v>
       </c>
       <c r="M18" t="n">
-        <v>3.83</v>
+        <v>3.16</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
-        <v>5.68</v>
+        <v>3.6</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>2.97</v>
       </c>
       <c r="R18" t="n">
-        <v>1.39</v>
+        <v>1.47</v>
       </c>
       <c r="S18" t="n">
-        <v>2.77</v>
+        <v>2.5</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>3.15</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>2.76</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.91</v>
+        <v>2.13</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.83</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AF18" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,22 +2682,22 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.65</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>5.1</v>
       </c>
       <c r="O19" t="n">
-        <v>3.3</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>5.42</v>
       </c>
       <c r="R19" t="n">
         <v>1.42</v>
@@ -2706,49 +2706,49 @@
         <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>6.95</v>
       </c>
       <c r="W19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.02</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
         <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AF19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AH19" t="n">
         <v>2.06</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.36</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.16</v>
+        <v>5.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.16</v>
+        <v>3.83</v>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>1.61</v>
       </c>
       <c r="O20" t="n">
-        <v>3.6</v>
+        <v>5.68</v>
       </c>
       <c r="P20" t="n">
-        <v>1.97</v>
+        <v>2.28</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.97</v>
+        <v>2.18</v>
       </c>
       <c r="R20" t="n">
-        <v>1.47</v>
+        <v>1.39</v>
       </c>
       <c r="S20" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="T20" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="U20" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.33</v>
+        <v>1.13</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.66</v>
+        <v>2.49</v>
       </c>
       <c r="M21" t="n">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="N21" t="n">
-        <v>4.9</v>
+        <v>3.06</v>
       </c>
       <c r="O21" t="n">
-        <v>2.17</v>
+        <v>3.1</v>
       </c>
       <c r="P21" t="n">
-        <v>2.35</v>
+        <v>1.87</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.1</v>
+        <v>3.75</v>
       </c>
       <c r="R21" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V21" t="n">
+        <v>9</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG21" t="n">
         <v>1.36</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="AH21" t="n">
-        <v>2.19</v>
+        <v>1.5</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.67</v>
+        <v>2.3</v>
       </c>
       <c r="M22" t="n">
-        <v>3.65</v>
+        <v>3.45</v>
       </c>
       <c r="N22" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="O22" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.42</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>6.95</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.49</v>
+        <v>1.66</v>
       </c>
       <c r="M24" t="n">
-        <v>2.93</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>3.06</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
-        <v>3.1</v>
+        <v>2.17</v>
       </c>
       <c r="P24" t="n">
-        <v>1.87</v>
+        <v>2.35</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.31</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V24" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG24" t="n">
         <v>1.24</v>
       </c>
-      <c r="V24" t="n">
-        <v>9</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z24" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA24" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB24" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF24" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AH24" t="n">
-        <v>1.5</v>
+        <v>2.19</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="M25" t="n">
         <v>3.25</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.15</v>
-      </c>
       <c r="N25" t="n">
-        <v>2.25</v>
+        <v>3.03</v>
       </c>
       <c r="O25" t="n">
-        <v>3.75</v>
+        <v>2.9</v>
       </c>
       <c r="P25" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.8</v>
+        <v>3.45</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S25" t="n">
-        <v>2.63</v>
+        <v>2.69</v>
       </c>
       <c r="T25" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V25" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
         <v>1.33</v>
       </c>
-      <c r="V25" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.36</v>
-      </c>
       <c r="Z25" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.17</v>
+        <v>2.02</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.05</v>
+        <v>3.54</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>2.47</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>3.41</v>
       </c>
       <c r="N26" t="n">
-        <v>2.98</v>
+        <v>2.67</v>
       </c>
       <c r="O26" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="P26" t="n">
-        <v>2.01</v>
+        <v>2.13</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.85</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="S26" t="n">
-        <v>2.65</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.34</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>7.9</v>
+        <v>6.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.54</v>
+        <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.78</v>
+        <v>1.62</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.97</v>
+        <v>1.55</v>
       </c>
       <c r="M27" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="N27" t="n">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
         <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>5.05</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>2.02</v>
       </c>
       <c r="U27" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>4.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>5.45</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.53</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.57</v>
-      </c>
       <c r="AF27" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="AG27" t="n">
-        <v>2</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P28" t="n">
         <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.05</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V28" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="M29" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="N29" t="n">
-        <v>2.59</v>
+        <v>2.98</v>
       </c>
       <c r="O29" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3.85</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S29" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="T29" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U29" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V29" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.87</v>
+        <v>1.7</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.14</v>
+        <v>3.54</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>1.93</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,67 +3991,67 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>3.32</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="P30" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q30" t="n">
         <v>3.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3.02</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>7.2</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X30" t="n">
         <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.9</v>
+        <v>3.14</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V31" t="n">
         <v>6</v>
       </c>
-      <c r="N31" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R31" t="n">
+      <c r="W31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
         <v>1.19</v>
       </c>
-      <c r="S31" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V31" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Z31" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.42</v>
+        <v>1.26</v>
       </c>
       <c r="M32" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N32" t="n">
-        <v>2.69</v>
+        <v>8.9</v>
       </c>
       <c r="O32" t="n">
-        <v>3</v>
+        <v>1.65</v>
       </c>
       <c r="P32" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4.45</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="V32" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V32" t="n">
-        <v>6</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.28</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1391,22 +1391,22 @@
         <v>6.35</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="S8" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T8" t="n">
         <v>2.8</v>
       </c>
       <c r="U8" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V8" t="n">
         <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X8" t="n">
         <v>1.06</v>
@@ -1415,13 +1415,13 @@
         <v>1.33</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.25</v>
+        <v>3.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="AC8" t="n">
         <v>3.28</v>
@@ -1433,7 +1433,7 @@
         <v>1.98</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AG8" t="n">
         <v>1.2</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>3.03</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N15" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O15" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="S15" t="n">
         <v>2.75</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.13</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>3</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.65</v>
-      </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>7.9</v>
+        <v>7</v>
       </c>
       <c r="W15" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.76</v>
+        <v>1.84</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.66</v>
+        <v>1.92</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.06</v>
+        <v>1.79</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.83</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
         <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>4.1</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.25</v>
+        <v>2.44</v>
       </c>
       <c r="M17" t="n">
-        <v>3.15</v>
+        <v>2.97</v>
       </c>
       <c r="N17" t="n">
-        <v>2.25</v>
+        <v>3.07</v>
       </c>
       <c r="O17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q17" t="n">
         <v>3.75</v>
       </c>
-      <c r="P17" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>2.8</v>
-      </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S17" t="n">
-        <v>2.63</v>
+        <v>2.3</v>
       </c>
       <c r="T17" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>9</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.05</v>
+        <v>5</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.88</v>
+        <v>2.05</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.28</v>
+        <v>1.5</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.16</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>3.16</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>3.6</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.97</v>
+        <v>4.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.47</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>3.15</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.31</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.76</v>
+        <v>3.54</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.13</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.64</v>
+        <v>1.93</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.78</v>
+        <v>2.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.33</v>
+        <v>1.94</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2682,16 +2682,16 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="M19" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="N19" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="P19" t="n">
         <v>2.15</v>
@@ -2727,28 +2727,28 @@
         <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.7</v>
+        <v>3.38</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AE19" t="n">
         <v>1.95</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>5.4</v>
+        <v>2.33</v>
       </c>
       <c r="M20" t="n">
-        <v>3.83</v>
+        <v>3.3</v>
       </c>
       <c r="N20" t="n">
-        <v>1.61</v>
+        <v>3.2</v>
       </c>
       <c r="O20" t="n">
-        <v>5.68</v>
+        <v>2.9</v>
       </c>
       <c r="P20" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.18</v>
+        <v>3.45</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S20" t="n">
-        <v>2.77</v>
+        <v>2.69</v>
       </c>
       <c r="T20" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
         <v>1.38</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W20" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.05</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.83</v>
+        <v>1.74</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF20" t="n">
         <v>1.92</v>
       </c>
-      <c r="AF20" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AG20" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.49</v>
+        <v>3.09</v>
       </c>
       <c r="M21" t="n">
-        <v>2.93</v>
+        <v>3.14</v>
       </c>
       <c r="N21" t="n">
-        <v>3.06</v>
+        <v>2.38</v>
       </c>
       <c r="O21" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V21" t="n">
+        <v>7</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE21" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q21" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="T21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V21" t="n">
-        <v>9</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>2.05</v>
-      </c>
       <c r="AF21" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="M22" t="n">
-        <v>3.45</v>
+        <v>3.13</v>
       </c>
       <c r="N22" t="n">
-        <v>2.8</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3158,16 +3158,16 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="M23" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="N23" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="O23" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P23" t="n">
         <v>1.91</v>
@@ -3176,19 +3176,19 @@
         <v>3.88</v>
       </c>
       <c r="R23" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
         <v>2.44</v>
       </c>
       <c r="T23" t="n">
-        <v>3.34</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
         <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
         <v>1</v>
@@ -3200,25 +3200,25 @@
         <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.68</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="AB23" t="n">
         <v>1.58</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG23" t="n">
         <v>1.35</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.66</v>
+        <v>2.96</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.17</v>
+        <v>3.75</v>
       </c>
       <c r="P24" t="n">
-        <v>2.35</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.1</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.63</v>
       </c>
       <c r="T24" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.23</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.85</v>
+        <v>2.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.82</v>
+        <v>2.17</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.89</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AF24" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF24" t="n">
-        <v>1.9</v>
-      </c>
       <c r="AG24" t="n">
-        <v>1.24</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.19</v>
+        <v>1.28</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.32</v>
+        <v>1.66</v>
       </c>
       <c r="M25" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N25" t="n">
-        <v>3.03</v>
+        <v>4.92</v>
       </c>
       <c r="O25" t="n">
-        <v>2.9</v>
+        <v>2.19</v>
       </c>
       <c r="P25" t="n">
-        <v>2.03</v>
+        <v>2.21</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.45</v>
+        <v>5.25</v>
       </c>
       <c r="R25" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.69</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="U25" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="V25" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.33</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.08</v>
+        <v>3.44</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.02</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.94</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.54</v>
+        <v>2.89</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M26" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N26" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O26" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="V26" t="n">
-        <v>6.45</v>
+        <v>5.5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
       </c>
       <c r="Y26" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH26" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.55</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>4.3</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>5.2</v>
+        <v>2.59</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>5.05</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3.94</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.58</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.38</v>
+        <v>1.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.35</v>
+        <v>3.14</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.6</v>
+        <v>1.35</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.68</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.5</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.97</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>3.92</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>1.78</v>
+        <v>2.67</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P28" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="W28" t="n">
-        <v>1.14</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
         <v>1.04</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.53</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AG28" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="M29" t="n">
-        <v>3.15</v>
+        <v>3.52</v>
       </c>
       <c r="N29" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="O29" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.85</v>
+        <v>3.32</v>
       </c>
       <c r="R29" t="n">
-        <v>1.42</v>
+        <v>1.34</v>
       </c>
       <c r="S29" t="n">
-        <v>2.65</v>
+        <v>3.24</v>
       </c>
       <c r="T29" t="n">
-        <v>2.99</v>
+        <v>2.54</v>
       </c>
       <c r="U29" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="V29" t="n">
-        <v>7.9</v>
+        <v>6</v>
       </c>
       <c r="W29" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X29" t="n">
         <v>1.02</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y29" t="n">
-        <v>1.32</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.05</v>
+        <v>4</v>
       </c>
       <c r="AA29" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.54</v>
+        <v>2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.22</v>
+        <v>1.62</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.62</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.32</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.59</v>
+        <v>8.9</v>
       </c>
       <c r="O30" t="n">
-        <v>3.28</v>
+        <v>1.65</v>
       </c>
       <c r="P30" t="n">
-        <v>2.14</v>
+        <v>2.8</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.2</v>
+        <v>7.5</v>
       </c>
       <c r="R30" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>3.02</v>
+        <v>4.45</v>
       </c>
       <c r="T30" t="n">
-        <v>2.77</v>
+        <v>1.97</v>
       </c>
       <c r="U30" t="n">
-        <v>1.44</v>
+        <v>1.8</v>
       </c>
       <c r="V30" t="n">
-        <v>7.2</v>
+        <v>3.84</v>
       </c>
       <c r="W30" t="n">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.3</v>
+        <v>1.09</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.55</v>
+        <v>6.2</v>
       </c>
       <c r="AA30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AC30" t="n">
         <v>1.87</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AD30" t="n">
         <v>1.87</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.35</v>
-      </c>
       <c r="AE30" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.3</v>
       </c>
       <c r="N31" t="n">
-        <v>2.69</v>
+        <v>2.85</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P31" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.32</v>
+        <v>3.85</v>
       </c>
       <c r="R31" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U31" t="n">
         <v>1.34</v>
       </c>
-      <c r="S31" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V31" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="W31" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z31" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AA31" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB31" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB31" t="n">
-        <v>2</v>
-      </c>
       <c r="AC31" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.62</v>
+        <v>1.28</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.26</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>6</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>8.9</v>
+        <v>1.84</v>
       </c>
       <c r="O32" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P32" t="n">
-        <v>2.8</v>
+        <v>2.28</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.5</v>
+        <v>2.45</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S32" t="n">
-        <v>4.45</v>
+        <v>2.89</v>
       </c>
       <c r="T32" t="n">
-        <v>1.97</v>
+        <v>2.81</v>
       </c>
       <c r="U32" t="n">
-        <v>1.8</v>
+        <v>1.43</v>
       </c>
       <c r="V32" t="n">
-        <v>3.84</v>
+        <v>6.75</v>
       </c>
       <c r="W32" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.09</v>
+        <v>1.28</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.2</v>
+        <v>3.4</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.36</v>
+        <v>1.82</v>
       </c>
       <c r="AB32" t="n">
-        <v>3.1</v>
+        <v>1.92</v>
       </c>
       <c r="AC32" t="n">
-        <v>1.87</v>
+        <v>3.3</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.87</v>
+        <v>1.33</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.6</v>
+        <v>1.26</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>4</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.61</v>
+        <v>4.3</v>
       </c>
       <c r="N33" t="n">
-        <v>1.84</v>
+        <v>5.2</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P33" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.45</v>
+        <v>5.05</v>
       </c>
       <c r="R33" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S33" t="n">
-        <v>2.89</v>
+        <v>3.94</v>
       </c>
       <c r="T33" t="n">
-        <v>2.81</v>
+        <v>2.02</v>
       </c>
       <c r="U33" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="V33" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.82</v>
+        <v>1.58</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.92</v>
+        <v>2.38</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.3</v>
+        <v>2.35</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>6.7</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>5.25</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>1.61</v>
+        <v>3.03</v>
       </c>
       <c r="O15" t="n">
-        <v>5.25</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.17</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.18</v>
+        <v>3.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
         <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
         <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.13</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.78</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.44</v>
+        <v>2.96</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>2.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.07</v>
+        <v>2.4</v>
       </c>
       <c r="O17" t="n">
+        <v>3.48</v>
+      </c>
+      <c r="P17" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.1</v>
       </c>
-      <c r="P17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.5</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V17" t="n">
-        <v>9</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>5</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>2.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="O18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.38</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.89</v>
-      </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>3.5</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>2.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.93</v>
+        <v>1.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.89</v>
+        <v>4.65</v>
       </c>
       <c r="AD18" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.32</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.94</v>
+        <v>1.5</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.73</v>
+        <v>5.5</v>
       </c>
       <c r="M19" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z19" t="n">
         <v>3.5</v>
       </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5.42</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.95</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AA19" t="n">
-        <v>2.03</v>
+        <v>1.96</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.81</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.38</v>
+        <v>3.18</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AH19" t="n">
-        <v>2.05</v>
+        <v>1.13</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,34 +2801,34 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="M20" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="O20" t="n">
         <v>3.3</v>
       </c>
-      <c r="N20" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.9</v>
-      </c>
       <c r="P20" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="R20" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S20" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
         <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
         <v>7.9</v>
@@ -2837,37 +2837,37 @@
         <v>1.02</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
         <v>1.28</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.05</v>
+        <v>1.94</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.92</v>
+        <v>2.06</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.57</v>
+        <v>1.36</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2923,7 +2923,7 @@
         <v>3.09</v>
       </c>
       <c r="M21" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
       <c r="N21" t="n">
         <v>2.38</v>
@@ -2935,43 +2935,43 @@
         <v>2.05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="T21" t="n">
         <v>3.15</v>
       </c>
       <c r="U21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
         <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z21" t="n">
         <v>2.76</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="AB21" t="n">
         <v>1.65</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="AD21" t="n">
         <v>1.19</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.75</v>
+        <v>2.36</v>
       </c>
       <c r="M22" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.46</v>
+        <v>1.7</v>
       </c>
       <c r="M23" t="n">
-        <v>3.04</v>
+        <v>3.7</v>
       </c>
       <c r="N23" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O23" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="P23" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.88</v>
+        <v>5.58</v>
       </c>
       <c r="R23" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.44</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U23" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.88</v>
+        <v>2.99</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.3</v>
+        <v>2.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
       <c r="AC23" t="n">
-        <v>4.5</v>
+        <v>3.7</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF23" t="n">
         <v>1.78</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.52</v>
+        <v>2.1</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.96</v>
+        <v>2.4</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.98</v>
       </c>
       <c r="O24" t="n">
-        <v>3.75</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>1.91</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="S24" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="Y24" t="n">
         <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.85</v>
+        <v>2.71</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.88</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.28</v>
+        <v>1.52</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3396,28 +3396,28 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>4.92</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="P25" t="n">
-        <v>2.21</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T25" t="n">
         <v>2.6</v>
@@ -3429,37 +3429,37 @@
         <v>6.25</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.44</v>
+        <v>3.54</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
         <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
         <v>2.12</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>3.97</v>
+        <v>2.62</v>
       </c>
       <c r="M26" t="n">
-        <v>3.92</v>
+        <v>3.32</v>
       </c>
       <c r="N26" t="n">
-        <v>1.78</v>
+        <v>2.59</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>3.02</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.77</v>
       </c>
       <c r="U26" t="n">
-        <v>1.61</v>
+        <v>1.44</v>
       </c>
       <c r="V26" t="n">
-        <v>5.5</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="X26" t="n">
         <v>1.04</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>3.55</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.53</v>
+        <v>1.87</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.45</v>
+        <v>1.87</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.25</v>
+        <v>3.14</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.35</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="N27" t="n">
-        <v>2.59</v>
+        <v>3.07</v>
       </c>
       <c r="O27" t="n">
-        <v>3.28</v>
+        <v>2.96</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.01</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.02</v>
+        <v>2.65</v>
       </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>2.99</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.34</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>7.9</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X27" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.55</v>
+        <v>3.08</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.14</v>
+        <v>3.5</v>
       </c>
       <c r="AD27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.35</v>
       </c>
-      <c r="AE27" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.47</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.41</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.67</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.13</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>5.05</v>
       </c>
       <c r="R28" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3.2</v>
+        <v>3.94</v>
       </c>
       <c r="T28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2.5</v>
       </c>
-      <c r="U28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V28" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,67 +3872,67 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.42</v>
+        <v>2.47</v>
       </c>
       <c r="M29" t="n">
-        <v>3.52</v>
+        <v>3.41</v>
       </c>
       <c r="N29" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="O29" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P29" t="n">
-        <v>2.15</v>
+        <v>2.13</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.32</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="S29" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="T29" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="U29" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>6</v>
+        <v>6.45</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="Z29" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB29" t="n">
         <v>2</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD29" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE29" t="n">
         <v>1.62</v>
       </c>
-      <c r="AE29" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AF29" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>1.26</v>
+        <v>2.42</v>
       </c>
       <c r="M30" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="N30" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O30" t="n">
+        <v>3</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V30" t="n">
         <v>6</v>
       </c>
-      <c r="N30" t="n">
-        <v>8.9</v>
-      </c>
-      <c r="O30" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="R30" t="n">
+      <c r="W30" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.19</v>
       </c>
-      <c r="S30" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="T30" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="V30" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.09</v>
-      </c>
       <c r="Z30" t="n">
-        <v>6.2</v>
+        <v>4</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.36</v>
+        <v>1.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.28</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.2</v>
+        <v>1.26</v>
       </c>
       <c r="M31" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="N31" t="n">
-        <v>2.85</v>
+        <v>8.9</v>
       </c>
       <c r="O31" t="n">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.01</v>
+        <v>2.8</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.85</v>
+        <v>7.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.42</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>2.65</v>
+        <v>4.45</v>
       </c>
       <c r="T31" t="n">
-        <v>2.7</v>
+        <v>1.97</v>
       </c>
       <c r="U31" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="V31" t="n">
-        <v>7.9</v>
+        <v>3.84</v>
       </c>
       <c r="W31" t="n">
-        <v>1.02</v>
+        <v>1.24</v>
       </c>
       <c r="X31" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.28</v>
+        <v>1.09</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.08</v>
+        <v>6.2</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.5</v>
+        <v>1.87</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.28</v>
+        <v>1.87</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="M33" t="n">
-        <v>4.3</v>
+        <v>3.92</v>
       </c>
       <c r="N33" t="n">
-        <v>5.2</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P33" t="n">
         <v>2.5</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.05</v>
+        <v>2.2</v>
       </c>
       <c r="R33" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="V33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>2</v>
+      </c>
+      <c r="AH33" t="n">
         <v>1.22</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V33" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.59</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1492,40 +1492,40 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="M9" t="n">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="N9" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="O9" t="n">
-        <v>5.2</v>
+        <v>4.32</v>
       </c>
       <c r="P9" t="n">
         <v>2.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.94</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.36</v>
+        <v>2.39</v>
       </c>
       <c r="U9" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="V9" t="n">
         <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1534,31 +1534,31 @@
         <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
         <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.44</v>
       </c>
       <c r="AE9" t="n">
         <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.08</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>1.85</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.03</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.03</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>6</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF12" t="n">
         <v>2.3</v>
       </c>
-      <c r="AF12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.68</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.17</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>4.21</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.63</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.9</v>
+        <v>6.5</v>
       </c>
       <c r="M14" t="n">
-        <v>5.6</v>
+        <v>6.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="O14" t="n">
         <v>5.5</v>
@@ -2111,7 +2111,7 @@
         <v>4.85</v>
       </c>
       <c r="T14" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="U14" t="n">
         <v>1.89</v>
@@ -2126,22 +2126,22 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>7</v>
+        <v>6.3</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.9</v>
+        <v>3.08</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE14" t="n">
         <v>1.5</v>
@@ -2150,10 +2150,10 @@
         <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>2.95</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N15" t="n">
-        <v>3.03</v>
+        <v>5</v>
       </c>
       <c r="O15" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>5.58</v>
       </c>
       <c r="R15" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V15" t="n">
         <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.08</v>
+        <v>2.99</v>
       </c>
       <c r="AA15" t="n">
         <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.54</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.22</v>
       </c>
-      <c r="AE15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.83</v>
+        <v>2.36</v>
       </c>
       <c r="M16" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="N16" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.78</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="M17" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="O17" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="P17" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S17" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T17" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U17" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V17" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X17" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>3.1</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>5.25</v>
       </c>
       <c r="P18" t="n">
-        <v>1.87</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.75</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="V18" t="n">
+        <v>7</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="Z18" t="n">
         <v>3.5</v>
       </c>
-      <c r="U18" t="n">
+      <c r="AA18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.24</v>
       </c>
-      <c r="V18" t="n">
-        <v>9</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.5</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>2.5</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>2.9</v>
       </c>
       <c r="N19" t="n">
-        <v>1.61</v>
+        <v>3.1</v>
       </c>
       <c r="O19" t="n">
-        <v>5.25</v>
+        <v>3.1</v>
       </c>
       <c r="P19" t="n">
-        <v>2.17</v>
+        <v>1.87</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.18</v>
+        <v>3.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="S19" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="U19" t="n">
-        <v>1.38</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="W19" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.07</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.27</v>
+        <v>1.51</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.96</v>
+        <v>2.65</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.81</v>
+        <v>1.44</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.18</v>
+        <v>4.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.92</v>
+        <v>2.05</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.79</v>
+        <v>1.68</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.13</v>
+        <v>1.5</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.75</v>
+        <v>1.67</v>
       </c>
       <c r="M20" t="n">
-        <v>3.13</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>5</v>
       </c>
       <c r="O20" t="n">
-        <v>3.3</v>
+        <v>2.22</v>
       </c>
       <c r="P20" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="R20" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.65</v>
+        <v>2.94</v>
       </c>
       <c r="T20" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="U20" t="n">
-        <v>1.34</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>7.9</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.76</v>
+        <v>1.98</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.36</v>
+        <v>2.12</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>3.09</v>
+        <v>2.85</v>
       </c>
       <c r="M21" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N21" t="n">
-        <v>2.38</v>
+        <v>2.45</v>
       </c>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>3.35</v>
       </c>
       <c r="P21" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>3.15</v>
+        <v>2.99</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X21" t="n">
         <v>1.04</v>
       </c>
-      <c r="X21" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y21" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.76</v>
+        <v>3.34</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.87</v>
+        <v>1.74</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.7</v>
+        <v>2.96</v>
       </c>
       <c r="M23" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N23" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="O23" t="n">
-        <v>2.25</v>
+        <v>3.48</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>5.58</v>
+        <v>2.8</v>
       </c>
       <c r="R23" t="n">
         <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.99</v>
+        <v>2.85</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.04</v>
+        <v>2.24</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.1</v>
+        <v>1.36</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="N24" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>2.38</v>
       </c>
       <c r="P24" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.6</v>
+        <v>4.78</v>
       </c>
       <c r="R24" t="n">
-        <v>1.48</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.6</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>1.42</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>6.25</v>
       </c>
       <c r="W24" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.71</v>
+        <v>3.54</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.58</v>
+        <v>1.95</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>2.89</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>1.32</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.78</v>
+        <v>1.98</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.35</v>
+        <v>1.2</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.52</v>
+        <v>1.94</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>3.09</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>2.38</v>
       </c>
       <c r="O25" t="n">
-        <v>2.22</v>
+        <v>4</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>2.85</v>
       </c>
       <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.35</v>
       </c>
-      <c r="S25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.45</v>
-      </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.35</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.54</v>
+        <v>2.76</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>2.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.98</v>
+        <v>1.65</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.36</v>
+        <v>1.19</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.87</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.12</v>
+        <v>1.33</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.62</v>
+        <v>4.03</v>
       </c>
       <c r="M26" t="n">
-        <v>3.32</v>
+        <v>3.96</v>
       </c>
       <c r="N26" t="n">
-        <v>2.59</v>
+        <v>1.79</v>
       </c>
       <c r="O26" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="S26" t="n">
-        <v>3.02</v>
+        <v>3.5</v>
       </c>
       <c r="T26" t="n">
-        <v>2.77</v>
+        <v>2.36</v>
       </c>
       <c r="U26" t="n">
-        <v>1.44</v>
+        <v>1.56</v>
       </c>
       <c r="V26" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W26" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="X26" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.14</v>
+        <v>2.49</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.35</v>
+        <v>1.55</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.68</v>
+        <v>1.53</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="N27" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O27" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="P27" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="R27" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S27" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U27" t="n">
         <v>1.35</v>
       </c>
-      <c r="S27" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V27" t="n">
-        <v>7.9</v>
+        <v>6.75</v>
       </c>
       <c r="W27" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB27" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC27" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF27" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>2.45</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>2.7</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.05</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="S28" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.45</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.58</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,67 +3872,67 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.47</v>
+        <v>2.64</v>
       </c>
       <c r="M29" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.8</v>
+        <v>3.28</v>
       </c>
       <c r="P29" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
         <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.2</v>
+        <v>2.95</v>
       </c>
       <c r="T29" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="V29" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X29" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.8</v>
+        <v>3.55</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AB29" t="n">
-        <v>2</v>
+        <v>1.84</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.62</v>
+        <v>1.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="M30" t="n">
-        <v>3.52</v>
+        <v>3.24</v>
       </c>
       <c r="N30" t="n">
-        <v>2.69</v>
+        <v>3.07</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.01</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.34</v>
       </c>
-      <c r="S30" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.51</v>
-      </c>
       <c r="V30" t="n">
-        <v>6</v>
+        <v>7.9</v>
       </c>
       <c r="W30" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X30" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.19</v>
+        <v>1.28</v>
       </c>
       <c r="Z30" t="n">
-        <v>4</v>
+        <v>3.08</v>
       </c>
       <c r="AA30" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB30" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB30" t="n">
-        <v>2</v>
-      </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.62</v>
+        <v>1.26</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.78</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4110,61 +4110,61 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="N31" t="n">
-        <v>8.9</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="P31" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>7.5</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
         <v>1.19</v>
       </c>
       <c r="S31" t="n">
-        <v>4.45</v>
+        <v>4.6</v>
       </c>
       <c r="T31" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>1.8</v>
+        <v>1.86</v>
       </c>
       <c r="V31" t="n">
-        <v>3.84</v>
+        <v>3.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X31" t="n">
         <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AB31" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="AC31" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.87</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="n">
         <v>1.65</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>1.58</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>4.4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.84</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>2.89</v>
+        <v>3.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.81</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
-        <v>6.75</v>
+        <v>4.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
         <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.4</v>
+        <v>5.45</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.82</v>
+        <v>1.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.3</v>
+        <v>2.17</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.33</v>
+        <v>1.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.75</v>
+        <v>1.52</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>2.54</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.26</v>
+        <v>2.4</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>3.97</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>1.78</v>
+        <v>2.75</v>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T33" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q33" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.36</v>
-      </c>
       <c r="U33" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
-        <v>5.5</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="X33" t="n">
         <v>1.04</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.6</v>
+        <v>3.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.35</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>3.68</v>
+        <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>6.99</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.08</v>
+        <v>2.45</v>
       </c>
       <c r="P10" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>1.47</v>
+        <v>1.3</v>
       </c>
       <c r="S10" t="n">
-        <v>2.41</v>
+        <v>3.1</v>
       </c>
       <c r="T10" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="U10" t="n">
-        <v>1.32</v>
+        <v>1.53</v>
       </c>
       <c r="V10" t="n">
-        <v>9.1</v>
+        <v>5.3</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="X10" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.45</v>
+        <v>1.18</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.34</v>
+        <v>1.65</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.55</v>
+        <v>2.1</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.4</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.5</v>
+        <v>1.53</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.45</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.44</v>
       </c>
       <c r="M11" t="n">
-        <v>2.8</v>
+        <v>3.68</v>
       </c>
       <c r="N11" t="n">
-        <v>3.1</v>
+        <v>6.99</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.08</v>
       </c>
       <c r="P11" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="R11" t="n">
-        <v>1.66</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.41</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>2.7</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>2.34</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>1.55</v>
       </c>
       <c r="AC11" t="n">
-        <v>6</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>2.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.68</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>4.17</v>
+        <v>2.8</v>
       </c>
       <c r="N13" t="n">
-        <v>4.21</v>
+        <v>3.1</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>2.85</v>
       </c>
       <c r="M15" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>2.45</v>
       </c>
       <c r="O15" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.58</v>
+        <v>3.1</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="S15" t="n">
         <v>2.65</v>
       </c>
       <c r="T15" t="n">
-        <v>2.94</v>
+        <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X15" t="n">
         <v>1.04</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.99</v>
+        <v>3.34</v>
       </c>
       <c r="AA15" t="n">
         <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AF15" t="n">
         <v>2</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>1.28</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="N16" t="n">
-        <v>2.9</v>
+        <v>2.98</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="M17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N17" t="n">
+        <v>5</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.3</v>
       </c>
-      <c r="M17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N17" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P17" t="n">
-        <v>2.03</v>
-      </c>
       <c r="Q17" t="n">
-        <v>3.78</v>
+        <v>5</v>
       </c>
       <c r="R17" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.69</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>2.99</v>
+        <v>2.6</v>
       </c>
       <c r="U17" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="V17" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.04</v>
+        <v>1.8</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.57</v>
+        <v>2.12</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.5</v>
+        <v>1.83</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>4.2</v>
       </c>
       <c r="O18" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="P18" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>4.78</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.89</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.18</v>
+        <v>2.89</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>1.73</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.79</v>
+        <v>1.98</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>1.94</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="M19" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N19" t="n">
         <v>2.9</v>
       </c>
-      <c r="N19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="O19" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.65</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.67</v>
+        <v>2.5</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>2.9</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
-        <v>2.22</v>
+        <v>3.1</v>
       </c>
       <c r="P20" t="n">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="Q20" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.5</v>
       </c>
       <c r="S20" t="n">
-        <v>2.94</v>
+        <v>2.38</v>
       </c>
       <c r="T20" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.24</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>9</v>
       </c>
       <c r="W20" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.07</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.51</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.54</v>
+        <v>2.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.8</v>
+        <v>2.65</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.98</v>
+        <v>1.44</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>4.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.12</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>2.05</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.12</v>
+        <v>1.5</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.85</v>
+        <v>5.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N21" t="n">
-        <v>2.45</v>
+        <v>1.61</v>
       </c>
       <c r="O21" t="n">
-        <v>3.35</v>
+        <v>5.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.06</v>
+        <v>2.17</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>2.18</v>
       </c>
       <c r="R21" t="n">
         <v>1.4</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>2.75</v>
       </c>
       <c r="T21" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W21" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="X21" t="n">
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.34</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.6</v>
+        <v>3.18</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.74</v>
+        <v>1.92</v>
       </c>
       <c r="AF21" t="n">
-        <v>2</v>
+        <v>1.79</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.28</v>
+        <v>1.13</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.4</v>
+        <v>3.09</v>
       </c>
       <c r="M22" t="n">
         <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.98</v>
+        <v>2.38</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>4</v>
       </c>
       <c r="P22" t="n">
-        <v>1.91</v>
+        <v>2.05</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>2.85</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.71</v>
+        <v>2.76</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.65</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.52</v>
+        <v>1.33</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.96</v>
+        <v>2.3</v>
       </c>
       <c r="M23" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="O23" t="n">
-        <v>3.48</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.8</v>
+        <v>3.78</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="T23" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="V23" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.85</v>
+        <v>3.08</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.24</v>
+        <v>2.04</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.36</v>
+        <v>1.57</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.83</v>
+        <v>2.96</v>
       </c>
       <c r="M24" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
       <c r="N24" t="n">
-        <v>4.2</v>
+        <v>2.4</v>
       </c>
       <c r="O24" t="n">
-        <v>2.38</v>
+        <v>3.48</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.78</v>
+        <v>2.8</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="T24" t="n">
-        <v>2.55</v>
+        <v>3.1</v>
       </c>
       <c r="U24" t="n">
-        <v>1.42</v>
+        <v>1.33</v>
       </c>
       <c r="V24" t="n">
-        <v>6.25</v>
+        <v>8.5</v>
       </c>
       <c r="W24" t="n">
         <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.54</v>
+        <v>2.85</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.83</v>
+        <v>2.24</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.95</v>
+        <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.89</v>
+        <v>3.9</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.73</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.98</v>
+        <v>1.91</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.94</v>
+        <v>1.36</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.09</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="N25" t="n">
-        <v>2.38</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>4</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.85</v>
+        <v>5.58</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.5</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>3.15</v>
+        <v>2.94</v>
       </c>
       <c r="U25" t="n">
         <v>1.35</v>
       </c>
       <c r="V25" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
         <v>1.04</v>
       </c>
       <c r="X25" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.76</v>
+        <v>2.99</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.17</v>
+        <v>2.04</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.33</v>
+        <v>2.1</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.03</v>
+        <v>2.31</v>
       </c>
       <c r="M26" t="n">
-        <v>3.96</v>
+        <v>3.24</v>
       </c>
       <c r="N26" t="n">
-        <v>1.79</v>
+        <v>3.07</v>
       </c>
       <c r="O26" t="n">
-        <v>4.1</v>
+        <v>2.96</v>
       </c>
       <c r="P26" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.2</v>
+        <v>3.55</v>
       </c>
       <c r="R26" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>3.5</v>
+        <v>2.65</v>
       </c>
       <c r="T26" t="n">
-        <v>2.36</v>
+        <v>2.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.56</v>
+        <v>1.34</v>
       </c>
       <c r="V26" t="n">
-        <v>5</v>
+        <v>7.9</v>
       </c>
       <c r="W26" t="n">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.6</v>
+        <v>3.08</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.61</v>
+        <v>2.04</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.33</v>
+        <v>1.75</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.49</v>
+        <v>3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.55</v>
+        <v>1.26</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.38</v>
+        <v>1.93</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>1.58</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,70 +3634,70 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4</v>
+        <v>4.03</v>
       </c>
       <c r="M27" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="N27" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.28</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S27" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>3.06</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.35</v>
+        <v>1.56</v>
       </c>
       <c r="V27" t="n">
-        <v>6.75</v>
+        <v>5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>1.61</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>2.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.35</v>
+        <v>2.49</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
         <v>1.25</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.45</v>
+        <v>1.58</v>
       </c>
       <c r="M28" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.7</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="T28" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH28" t="n">
         <v>2.4</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V28" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.72</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1.58</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.64</v>
+        <v>2.45</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="O29" t="n">
-        <v>3.28</v>
+        <v>3</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>2.21</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.29</v>
       </c>
       <c r="S29" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="T29" t="n">
-        <v>2.77</v>
+        <v>2.4</v>
       </c>
       <c r="U29" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="V29" t="n">
-        <v>6.25</v>
+        <v>5.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.91</v>
+        <v>1.79</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.84</v>
+        <v>2.12</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.17</v>
+        <v>2.72</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.43</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.28</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>1.58</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="M30" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="N30" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S30" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T30" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U30" t="n">
         <v>1.35</v>
       </c>
-      <c r="S30" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V30" t="n">
-        <v>7.9</v>
+        <v>6.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE30" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD30" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE30" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF30" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>2.45</v>
       </c>
       <c r="M31" t="n">
-        <v>6.2</v>
+        <v>3.5</v>
       </c>
       <c r="N31" t="n">
-        <v>8.720000000000001</v>
+        <v>2.75</v>
       </c>
       <c r="O31" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE31" t="n">
         <v>1.62</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
         <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="M32" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="O32" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="P32" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="T32" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="U32" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="V32" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="W32" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.17</v>
+        <v>3.17</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>1.27</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="N33" t="n">
-        <v>2.75</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>2.8</v>
+        <v>1.62</v>
       </c>
       <c r="P33" t="n">
-        <v>2.15</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.25</v>
+        <v>6.5</v>
       </c>
       <c r="R33" t="n">
-        <v>1.3</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>3.12</v>
+        <v>4.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="U33" t="n">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>6.45</v>
+        <v>3.8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.1</v>
+        <v>1.22</v>
       </c>
       <c r="X33" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
+        <v>1.08</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.8</v>
+        <v>6.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.79</v>
+        <v>1.33</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>2.98</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>1.91</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
         <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.5</v>
+        <v>3.6</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>4.17</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>4.21</v>
       </c>
       <c r="O10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.12</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1730,13 +1730,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>6.99</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
         <v>2.08</v>
@@ -1757,46 +1757,46 @@
         <v>3.25</v>
       </c>
       <c r="U11" t="n">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="V11" t="n">
         <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
         <v>1.45</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="AE11" t="n">
         <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
         <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.45</v>
+        <v>2.36</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>4.17</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>4.21</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1971,10 +1971,10 @@
         <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
         <v>3.2</v>
@@ -1986,16 +1986,16 @@
         <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2.07</v>
       </c>
       <c r="T13" t="n">
         <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
         <v>13</v>
@@ -2016,10 +2016,10 @@
         <v>2.88</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AC13" t="n">
-        <v>6</v>
+        <v>6.25</v>
       </c>
       <c r="AD13" t="n">
         <v>1.09</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="M15" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N15" t="n">
-        <v>2.45</v>
+        <v>3.03</v>
       </c>
       <c r="O15" t="n">
-        <v>3.35</v>
+        <v>2.88</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.03</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S15" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="T15" t="n">
         <v>2.99</v>
       </c>
       <c r="U15" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="V15" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.34</v>
+        <v>3.08</v>
       </c>
       <c r="AA15" t="n">
         <v>2.04</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AF15" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.28</v>
+        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="M16" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N16" t="n">
         <v>2.4</v>
       </c>
-      <c r="M16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N16" t="n">
-        <v>2.98</v>
-      </c>
       <c r="O16" t="n">
-        <v>2.95</v>
+        <v>3.48</v>
       </c>
       <c r="P16" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V16" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF16" t="n">
         <v>1.91</v>
       </c>
-      <c r="Q16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T16" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V16" t="n">
-        <v>8</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y16" t="n">
+      <c r="AG16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.36</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.52</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="O17" t="n">
-        <v>2.22</v>
+        <v>2.38</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="V17" t="n">
         <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X17" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
         <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.98</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.12</v>
+        <v>1.94</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>1.83</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="N18" t="n">
-        <v>4.2</v>
+        <v>1.61</v>
       </c>
       <c r="O18" t="n">
-        <v>2.38</v>
+        <v>5.25</v>
       </c>
       <c r="P18" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q18" t="n">
-        <v>4.78</v>
+        <v>2.18</v>
       </c>
       <c r="R18" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S18" t="n">
-        <v>2.89</v>
+        <v>2.75</v>
       </c>
       <c r="T18" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="U18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="V18" t="n">
-        <v>6.25</v>
+        <v>7</v>
       </c>
       <c r="W18" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.83</v>
+        <v>1.96</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="AC18" t="n">
-        <v>2.89</v>
+        <v>3.18</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.73</v>
+        <v>1.92</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.94</v>
+        <v>1.13</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="M19" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N19" t="n">
-        <v>2.9</v>
+        <v>5</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="M20" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q20" t="n">
         <v>3.1</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>3.75</v>
-      </c>
       <c r="R20" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.38</v>
+        <v>2.65</v>
       </c>
       <c r="T20" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="U20" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="V20" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W20" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X20" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="Z20" t="n">
-        <v>2.5</v>
+        <v>3.34</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.65</v>
+        <v>2.04</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.44</v>
+        <v>1.72</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.65</v>
+        <v>3.6</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.12</v>
+        <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>2.05</v>
+        <v>1.74</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.68</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.5</v>
+        <v>1.7</v>
       </c>
       <c r="M21" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="N21" t="n">
-        <v>1.61</v>
+        <v>5</v>
       </c>
       <c r="O21" t="n">
-        <v>5.25</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.18</v>
+        <v>5.58</v>
       </c>
       <c r="R21" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T21" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="U21" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="V21" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X21" t="n">
         <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>2.99</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.81</v>
+        <v>1.7</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.18</v>
+        <v>3.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.13</v>
+        <v>2.1</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.09</v>
+        <v>2.36</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="N22" t="n">
-        <v>2.38</v>
+        <v>2.9</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N23" t="n">
-        <v>3.03</v>
+        <v>2.98</v>
       </c>
       <c r="O23" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="P23" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="S23" t="n">
-        <v>2.69</v>
+        <v>2.6</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="W23" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X23" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.08</v>
+        <v>2.71</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.54</v>
+        <v>4.4</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="AE23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.78</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.93</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="M24" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="N24" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="O24" t="n">
-        <v>3.48</v>
+        <v>4</v>
       </c>
       <c r="P24" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="R24" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="T24" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="U24" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>8.5</v>
+        <v>7</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X24" t="n">
         <v>1.08</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.85</v>
+        <v>2.76</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="AB24" t="n">
         <v>1.65</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.7</v>
+        <v>2.9</v>
       </c>
       <c r="N25" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>1.87</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.58</v>
+        <v>3.75</v>
       </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V25" t="n">
+        <v>9</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.65</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V25" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.04</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.7</v>
+        <v>4.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.24</v>
+        <v>1.12</v>
       </c>
       <c r="AE25" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.78</v>
+        <v>1.68</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.31</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.24</v>
+        <v>3.58</v>
       </c>
       <c r="N26" t="n">
-        <v>3.07</v>
+        <v>1.88</v>
       </c>
       <c r="O26" t="n">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.01</v>
+        <v>2.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="R26" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="U26" t="n">
         <v>1.35</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.34</v>
-      </c>
       <c r="V26" t="n">
-        <v>7.9</v>
+        <v>6.75</v>
       </c>
       <c r="W26" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.04</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE26" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AF26" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.58</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>4.03</v>
+        <v>1.27</v>
       </c>
       <c r="M27" t="n">
-        <v>3.96</v>
+        <v>6.2</v>
       </c>
       <c r="N27" t="n">
-        <v>1.79</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>4.1</v>
+        <v>1.62</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.25</v>
+        <v>1.19</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
-        <v>1.56</v>
+        <v>1.86</v>
       </c>
       <c r="V27" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.22</v>
       </c>
       <c r="X27" t="n">
         <v>1.01</v>
       </c>
       <c r="Y27" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG27" t="n">
         <v>1.13</v>
       </c>
-      <c r="Z27" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.61</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH27" t="n">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.58</v>
+        <v>2.64</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>3.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.6</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.8</v>
+        <v>2.95</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.77</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>1.4</v>
       </c>
       <c r="V28" t="n">
-        <v>4.4</v>
+        <v>6.25</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.07</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.45</v>
+        <v>3.55</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.75</v>
+        <v>1.84</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.17</v>
+        <v>3.17</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.74</v>
+        <v>1.3</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.52</v>
+        <v>1.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.54</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>2.8</v>
       </c>
       <c r="P30" t="n">
-        <v>2.28</v>
+        <v>2.15</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>3.06</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.35</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>6.75</v>
+        <v>6.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.87</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.35</v>
+        <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.45</v>
+        <v>4.03</v>
       </c>
       <c r="M31" t="n">
+        <v>3.96</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S31" t="n">
         <v>3.5</v>
       </c>
-      <c r="N31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.12</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V31" t="n">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.8</v>
+        <v>4.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="AB31" t="n">
-        <v>2</v>
+        <v>2.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.9</v>
+        <v>2.49</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.15</v>
+        <v>2.38</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.64</v>
+        <v>1.58</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="N32" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="O32" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="P32" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S32" t="n">
-        <v>2.95</v>
+        <v>3.8</v>
       </c>
       <c r="T32" t="n">
-        <v>2.77</v>
+        <v>2.02</v>
       </c>
       <c r="U32" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="V32" t="n">
-        <v>6.25</v>
+        <v>4.4</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.55</v>
+        <v>5.45</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.91</v>
+        <v>1.44</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.84</v>
+        <v>2.75</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.17</v>
+        <v>2.17</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>1.74</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>1.52</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>2.54</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.27</v>
+        <v>2.31</v>
       </c>
       <c r="M33" t="n">
-        <v>6.2</v>
+        <v>3.24</v>
       </c>
       <c r="N33" t="n">
-        <v>8.720000000000001</v>
+        <v>3.07</v>
       </c>
       <c r="O33" t="n">
-        <v>1.62</v>
+        <v>2.96</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>2.01</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.35</v>
       </c>
       <c r="S33" t="n">
-        <v>4.6</v>
+        <v>2.65</v>
       </c>
       <c r="T33" t="n">
-        <v>1.98</v>
+        <v>2.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.86</v>
+        <v>1.34</v>
       </c>
       <c r="V33" t="n">
-        <v>3.8</v>
+        <v>7.9</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>1.02</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.33</v>
+        <v>2.04</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>1.26</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.15</v>
+        <v>1.93</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.13</v>
+        <v>1.35</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.6</v>
+        <v>1.58</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
         <v>4.32</v>
       </c>
       <c r="P9" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q9" t="n">
         <v>2.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.39</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
         <v>1.6</v>
@@ -1525,7 +1525,7 @@
         <v>5.5</v>
       </c>
       <c r="W9" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
@@ -1537,28 +1537,28 @@
         <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AB9" t="n">
         <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.44</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="n">
         <v>1.62</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.52083333334</v>
@@ -1739,16 +1739,16 @@
         <v>6.7</v>
       </c>
       <c r="O11" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
         <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>7</v>
+        <v>8.15</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S11" t="n">
         <v>2.41</v>
@@ -1763,10 +1763,10 @@
         <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Y11" t="n">
         <v>1.45</v>
@@ -1784,19 +1784,19 @@
         <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="AF11" t="n">
         <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O12" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="P12" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V12" t="n">
+        <v>13</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AE12" t="n">
         <v>2.3</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U12" t="n">
+      <c r="AF12" t="n">
         <v>1.53</v>
       </c>
-      <c r="V12" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="P13" t="n">
-        <v>1.87</v>
+        <v>2.3</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="S13" t="n">
-        <v>2.07</v>
+        <v>3.1</v>
       </c>
       <c r="T13" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.53</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>5.3</v>
       </c>
       <c r="W13" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="X13" t="n">
         <v>1.03</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>1.18</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>4</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>1.65</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.25</v>
+        <v>2.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="AE13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF13" t="n">
         <v>2.3</v>
       </c>
-      <c r="AF13" t="n">
-        <v>1.54</v>
-      </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.5</v>
+        <v>5.9</v>
       </c>
       <c r="M14" t="n">
-        <v>6.05</v>
+        <v>5.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="O14" t="n">
         <v>5.5</v>
@@ -2102,22 +2102,22 @@
         <v>3</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="R14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>4.85</v>
+        <v>4.9</v>
       </c>
       <c r="T14" t="n">
         <v>1.95</v>
       </c>
       <c r="U14" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="W14" t="n">
         <v>1.25</v>
@@ -2129,19 +2129,19 @@
         <v>1.06</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AE14" t="n">
         <v>1.5</v>
@@ -2150,10 +2150,10 @@
         <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.95</v>
+        <v>1.15</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.61458333334</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="M15" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.06</v>
+      </c>
+      <c r="O15" t="n">
         <v>3.4</v>
       </c>
-      <c r="N15" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.88</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.03</v>
+        <v>1.88</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>3.35</v>
       </c>
       <c r="R15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V15" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH15" t="n">
         <v>1.41</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.69</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.08</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>1.57</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.96</v>
+        <v>2.32</v>
       </c>
       <c r="M16" t="n">
-        <v>2.9</v>
+        <v>3.25</v>
       </c>
       <c r="N16" t="n">
-        <v>2.4</v>
+        <v>3.03</v>
       </c>
       <c r="O16" t="n">
-        <v>3.48</v>
+        <v>2.7</v>
       </c>
       <c r="P16" t="n">
         <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.8</v>
+        <v>4.12</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S16" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>2.89</v>
       </c>
       <c r="U16" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V16" t="n">
-        <v>8.5</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X16" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.85</v>
+        <v>3.18</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.24</v>
+        <v>2.03</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.9</v>
+        <v>3.38</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF16" t="n">
         <v>1.91</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.28</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="M17" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="N17" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.78</v>
+        <v>4.8</v>
       </c>
       <c r="R17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.89</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>2.55</v>
+        <v>2.68</v>
       </c>
       <c r="U17" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="V17" t="n">
         <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
         <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.95</v>
       </c>
-      <c r="AC17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AG17" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.94</v>
+        <v>2.15</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.5</v>
+        <v>2.75</v>
       </c>
       <c r="M18" t="n">
-        <v>3.9</v>
+        <v>3.13</v>
       </c>
       <c r="N18" t="n">
-        <v>1.61</v>
+        <v>2.29</v>
       </c>
       <c r="O18" t="n">
-        <v>5.25</v>
+        <v>3.35</v>
       </c>
       <c r="P18" t="n">
-        <v>2.17</v>
+        <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.18</v>
+        <v>3.08</v>
       </c>
       <c r="R18" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="S18" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="T18" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U18" t="n">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="V18" t="n">
-        <v>7</v>
+        <v>7.9</v>
       </c>
       <c r="W18" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X18" t="n">
         <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.96</v>
+        <v>1.94</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.81</v>
+        <v>1.76</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.18</v>
+        <v>3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.79</v>
+        <v>2</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.13</v>
+        <v>1.28</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="M19" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="O19" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S19" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB19" t="n">
         <v>1.67</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5</v>
-      </c>
-      <c r="O19" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>5</v>
-      </c>
-      <c r="R19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S19" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T19" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="U19" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y19" t="n">
+      <c r="AC19" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.22</v>
       </c>
-      <c r="Z19" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>1.83</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.23</v>
+        <v>1.67</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,55 +2801,55 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.85</v>
+        <v>3.16</v>
       </c>
       <c r="M20" t="n">
-        <v>3.25</v>
+        <v>3.16</v>
       </c>
       <c r="N20" t="n">
-        <v>2.45</v>
+        <v>2.29</v>
       </c>
       <c r="O20" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P20" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q20" t="n">
+        <v>3</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z20" t="n">
         <v>3.1</v>
       </c>
-      <c r="R20" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V20" t="n">
-        <v>8</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AA20" t="n">
-        <v>2.04</v>
+        <v>2.13</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC20" t="n">
         <v>3.6</v>
@@ -2858,16 +2858,16 @@
         <v>1.25</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>1.7</v>
+        <v>2.3</v>
       </c>
       <c r="M21" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="N21" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="O21" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3035,77 +3035,77 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.36</v>
+        <v>2.44</v>
       </c>
       <c r="M22" t="n">
-        <v>3.55</v>
+        <v>3.05</v>
       </c>
       <c r="N22" t="n">
-        <v>2.9</v>
+        <v>3.01</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="M23" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="N23" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="O23" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P23" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AC23" t="n">
         <v>3.2</v>
       </c>
-      <c r="N23" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="O23" t="n">
-        <v>2.95</v>
-      </c>
-      <c r="P23" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R23" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="S23" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T23" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="U23" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="V23" t="n">
-        <v>8</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.4</v>
-      </c>
       <c r="AD23" t="n">
-        <v>1.16</v>
+        <v>1.3</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.52</v>
+        <v>1.95</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>3.09</v>
+        <v>5.4</v>
       </c>
       <c r="M24" t="n">
-        <v>3.2</v>
+        <v>3.83</v>
       </c>
       <c r="N24" t="n">
-        <v>2.38</v>
+        <v>1.61</v>
       </c>
       <c r="O24" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P24" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q24" t="n">
         <v>2.05</v>
       </c>
-      <c r="Q24" t="n">
-        <v>2.85</v>
-      </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.88</v>
       </c>
       <c r="T24" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="U24" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="V24" t="n">
-        <v>7</v>
+        <v>6.25</v>
       </c>
       <c r="W24" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.04</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.76</v>
+        <v>3.45</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.17</v>
+        <v>1.91</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.65</v>
+        <v>1.83</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.1</v>
+        <v>2.94</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.19</v>
+        <v>1.33</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.33</v>
+        <v>1.12</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.5</v>
+        <v>1.67</v>
       </c>
       <c r="M25" t="n">
-        <v>2.9</v>
+        <v>3.65</v>
       </c>
       <c r="N25" t="n">
-        <v>3.1</v>
+        <v>5.1</v>
       </c>
       <c r="O25" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P25" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.75</v>
+        <v>5.82</v>
       </c>
       <c r="R25" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="S25" t="n">
-        <v>2.38</v>
+        <v>2.81</v>
       </c>
       <c r="T25" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
         <v>3.5</v>
       </c>
-      <c r="U25" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="V25" t="n">
-        <v>9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.5</v>
-      </c>
       <c r="AA25" t="n">
-        <v>2.65</v>
+        <v>1.98</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.44</v>
+        <v>1.77</v>
       </c>
       <c r="AC25" t="n">
-        <v>4.65</v>
+        <v>3.7</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.12</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.68</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.15</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.5</v>
+        <v>2.22</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>2.4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.58</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>1.88</v>
+        <v>2.98</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="P26" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V26" t="n">
+        <v>7</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG26" t="n">
         <v>1.36</v>
       </c>
-      <c r="S26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T26" t="n">
-        <v>3.06</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.27</v>
+        <v>2.62</v>
       </c>
       <c r="M27" t="n">
-        <v>6.2</v>
+        <v>3.32</v>
       </c>
       <c r="N27" t="n">
-        <v>8.720000000000001</v>
+        <v>2.59</v>
       </c>
       <c r="O27" t="n">
-        <v>1.62</v>
+        <v>3.28</v>
       </c>
       <c r="P27" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>4.6</v>
+        <v>3.02</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="V27" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.22</v>
+        <v>1.07</v>
       </c>
       <c r="X27" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.33</v>
+        <v>1.87</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.98</v>
+        <v>1.87</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.02</v>
+        <v>3.19</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.91</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.64</v>
+        <v>1.55</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="O28" t="n">
-        <v>3.28</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>2.95</v>
+        <v>3.94</v>
       </c>
       <c r="T28" t="n">
-        <v>2.77</v>
+        <v>2.02</v>
       </c>
       <c r="U28" t="n">
-        <v>1.4</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>6.25</v>
+        <v>4.35</v>
       </c>
       <c r="W28" t="n">
-        <v>1.07</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.55</v>
+        <v>5.5</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.91</v>
+        <v>1.58</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.84</v>
+        <v>2.38</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>2.45</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P29" t="n">
         <v>2.45</v>
       </c>
-      <c r="M29" t="n">
+      <c r="Q29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S29" t="n">
         <v>3.5</v>
       </c>
-      <c r="N29" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O29" t="n">
-        <v>3</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>3</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
       <c r="T29" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="U29" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V29" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="W29" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="Z29" t="n">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.79</v>
+        <v>1.53</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.72</v>
+        <v>2.25</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.43</v>
+        <v>1.65</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.28</v>
+        <v>2.38</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.49</v>
+        <v>1.25</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3991,25 +3991,25 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.41</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="O30" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
         <v>3.12</v>
@@ -4024,19 +4024,19 @@
         <v>6.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
         <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.8</v>
+        <v>3.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="AB30" t="n">
         <v>2</v>
@@ -4048,10 +4048,10 @@
         <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.03</v>
+        <v>2.42</v>
       </c>
       <c r="M31" t="n">
-        <v>3.96</v>
+        <v>3.52</v>
       </c>
       <c r="N31" t="n">
-        <v>1.79</v>
+        <v>2.69</v>
       </c>
       <c r="O31" t="n">
+        <v>3</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S31" t="n">
+        <v>3</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="V31" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z31" t="n">
         <v>4.1</v>
       </c>
-      <c r="P31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AA31" t="n">
-        <v>1.61</v>
+        <v>1.75</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.58</v>
+        <v>4</v>
       </c>
       <c r="M32" t="n">
-        <v>4.4</v>
+        <v>3.61</v>
       </c>
       <c r="N32" t="n">
-        <v>5.3</v>
+        <v>1.84</v>
       </c>
       <c r="O32" t="n">
+        <v>4</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V32" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AF32" t="n">
         <v>2</v>
       </c>
-      <c r="P32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V32" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>5.45</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AD32" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.54</v>
-      </c>
       <c r="AG32" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4312,7 +4312,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.31</v>
+        <v>1.26</v>
       </c>
       <c r="M33" t="n">
-        <v>3.24</v>
+        <v>6</v>
       </c>
       <c r="N33" t="n">
-        <v>3.07</v>
+        <v>8.9</v>
       </c>
       <c r="O33" t="n">
-        <v>2.96</v>
+        <v>1.65</v>
       </c>
       <c r="P33" t="n">
-        <v>2.01</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>6.75</v>
       </c>
       <c r="R33" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S33" t="n">
-        <v>2.65</v>
+        <v>4.6</v>
       </c>
       <c r="T33" t="n">
-        <v>2.99</v>
+        <v>1.99</v>
       </c>
       <c r="U33" t="n">
-        <v>1.34</v>
+        <v>1.86</v>
       </c>
       <c r="V33" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="W33" t="n">
-        <v>1.02</v>
+        <v>1.22</v>
       </c>
       <c r="X33" t="n">
         <v>1.01</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.28</v>
+        <v>1.1</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.08</v>
+        <v>6.5</v>
       </c>
       <c r="AA33" t="n">
-        <v>2.04</v>
+        <v>1.36</v>
       </c>
       <c r="AB33" t="n">
-        <v>1.75</v>
+        <v>3.1</v>
       </c>
       <c r="AC33" t="n">
-        <v>3.5</v>
+        <v>1.87</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.26</v>
+        <v>1.87</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.93</v>
+        <v>2.15</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.58</v>
+        <v>3.6</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1382,64 +1382,64 @@
         <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q8" t="n">
-        <v>6.35</v>
+        <v>5.5</v>
       </c>
       <c r="R8" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="S8" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="T8" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V8" t="n">
         <v>6.75</v>
       </c>
       <c r="W8" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.76</v>
+        <v>1.9</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.28</v>
+        <v>2.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.50347222222</v>
@@ -1611,13 +1611,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="M10" t="n">
-        <v>4.17</v>
+        <v>3.85</v>
       </c>
       <c r="N10" t="n">
-        <v>4.21</v>
+        <v>4.6</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1656,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>2.04</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="N11" t="n">
-        <v>6.7</v>
+        <v>3.31</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.15</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.41</v>
+        <v>2.82</v>
       </c>
       <c r="T11" t="n">
-        <v>3.25</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.09</v>
+        <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.45</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.66</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>1.82</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>1.97</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.3</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="O13" t="n">
-        <v>2.45</v>
+        <v>2.05</v>
       </c>
       <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>8.15</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AH13" t="n">
         <v>2.3</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T13" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V13" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>4</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.49</v>
+        <v>3.28</v>
       </c>
       <c r="M15" t="n">
-        <v>2.93</v>
+        <v>3.23</v>
       </c>
       <c r="N15" t="n">
-        <v>3.06</v>
+        <v>1.98</v>
       </c>
       <c r="O15" t="n">
-        <v>3.4</v>
+        <v>4.22</v>
       </c>
       <c r="P15" t="n">
-        <v>1.88</v>
+        <v>2.06</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="S15" t="n">
-        <v>2.48</v>
+        <v>2.62</v>
       </c>
       <c r="T15" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="U15" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="V15" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.65</v>
+        <v>2.07</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.8</v>
+        <v>3.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="M16" t="n">
-        <v>3.25</v>
+        <v>3.45</v>
       </c>
       <c r="N16" t="n">
-        <v>3.03</v>
+        <v>2.8</v>
       </c>
       <c r="O16" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.12</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>2.73</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.18</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.66</v>
+        <v>2.49</v>
       </c>
       <c r="M17" t="n">
-        <v>3.8</v>
+        <v>2.93</v>
       </c>
       <c r="N17" t="n">
-        <v>4.9</v>
+        <v>3.06</v>
       </c>
       <c r="O17" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V17" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AC17" t="n">
         <v>4.8</v>
       </c>
-      <c r="R17" t="n">
+      <c r="AD17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.35</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH17" t="n">
-        <v>2.15</v>
+        <v>1.41</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.75</v>
+        <v>2.32</v>
       </c>
       <c r="M18" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.29</v>
+        <v>3.03</v>
       </c>
       <c r="O18" t="n">
-        <v>3.35</v>
+        <v>2.7</v>
       </c>
       <c r="P18" t="n">
         <v>2.06</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.08</v>
+        <v>4.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.42</v>
+        <v>1.37</v>
       </c>
       <c r="S18" t="n">
-        <v>2.65</v>
+        <v>2.73</v>
       </c>
       <c r="T18" t="n">
-        <v>2.99</v>
+        <v>2.89</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="V18" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X18" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y18" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.28</v>
       </c>
-      <c r="Z18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA18" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AB18" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.26</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.28</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>3.28</v>
+        <v>5.4</v>
       </c>
       <c r="M19" t="n">
-        <v>3.23</v>
+        <v>3.83</v>
       </c>
       <c r="N19" t="n">
-        <v>1.98</v>
+        <v>1.61</v>
       </c>
       <c r="O19" t="n">
-        <v>4.22</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.8</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="T19" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V19" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.33</v>
-      </c>
-      <c r="V19" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.87</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.22</v>
       </c>
       <c r="AE19" t="n">
         <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.67</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.16</v>
+        <v>1.66</v>
       </c>
       <c r="M20" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="N20" t="n">
-        <v>2.29</v>
+        <v>4.9</v>
       </c>
       <c r="O20" t="n">
-        <v>3.44</v>
+        <v>2.15</v>
       </c>
       <c r="P20" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q20" t="n">
-        <v>3</v>
+        <v>4.8</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S20" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T20" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="U20" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W20" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X20" t="n">
         <v>1.04</v>
       </c>
-      <c r="X20" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.13</v>
+        <v>1.82</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.6</v>
+        <v>2.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF20" t="n">
         <v>1.95</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.44</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.3</v>
+        <v>1.67</v>
       </c>
       <c r="M21" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="N21" t="n">
-        <v>2.8</v>
+        <v>5.1</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.82</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.44</v>
+        <v>3.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.05</v>
+        <v>3.16</v>
       </c>
       <c r="N22" t="n">
-        <v>3.01</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>2.95</v>
+        <v>3.44</v>
       </c>
       <c r="P22" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.47</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="V22" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X22" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.72</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AC22" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.8</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>5.4</v>
+        <v>2.44</v>
       </c>
       <c r="M24" t="n">
-        <v>3.83</v>
+        <v>3.05</v>
       </c>
       <c r="N24" t="n">
-        <v>1.61</v>
+        <v>3.01</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>2.95</v>
       </c>
       <c r="P24" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="S24" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V24" t="n">
+        <v>8</v>
+      </c>
+      <c r="W24" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y24" t="n">
         <v>1.36</v>
       </c>
-      <c r="S24" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T24" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U24" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V24" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W24" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X24" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y24" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z24" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="AA24" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE24" t="n">
         <v>1.91</v>
       </c>
-      <c r="AB24" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC24" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD24" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE24" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF24" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="M25" t="n">
-        <v>3.65</v>
+        <v>3.13</v>
       </c>
       <c r="N25" t="n">
-        <v>5.1</v>
+        <v>2.29</v>
       </c>
       <c r="O25" t="n">
-        <v>2.25</v>
+        <v>3.35</v>
       </c>
       <c r="P25" t="n">
-        <v>2.15</v>
+        <v>2.06</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.82</v>
+        <v>3.08</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="T25" t="n">
-        <v>2.73</v>
+        <v>2.99</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X25" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.95</v>
+        <v>1.82</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.22</v>
+        <v>1.28</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.4</v>
+        <v>1.26</v>
       </c>
       <c r="M26" t="n">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="N26" t="n">
-        <v>2.98</v>
+        <v>8.9</v>
       </c>
       <c r="O26" t="n">
-        <v>2.78</v>
+        <v>1.65</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>3</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>6.75</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>4.6</v>
       </c>
       <c r="T26" t="n">
-        <v>2.79</v>
+        <v>1.99</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.86</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>3.8</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.22</v>
       </c>
       <c r="X26" t="n">
         <v>1.01</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.24</v>
+        <v>1.1</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.68</v>
+        <v>6.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.36</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.7</v>
+        <v>3.1</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.25</v>
+        <v>1.87</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.34</v>
+        <v>1.87</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>3.6</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.55</v>
+        <v>2.42</v>
       </c>
       <c r="M28" t="n">
-        <v>4.3</v>
+        <v>3.52</v>
       </c>
       <c r="N28" t="n">
-        <v>5.2</v>
+        <v>2.69</v>
       </c>
       <c r="O28" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P28" t="n">
-        <v>2.5</v>
+        <v>2.21</v>
       </c>
       <c r="Q28" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S28" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="T28" t="n">
-        <v>2.02</v>
+        <v>2.4</v>
       </c>
       <c r="U28" t="n">
-        <v>1.75</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>4.35</v>
+        <v>5.6</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z28" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.58</v>
+        <v>1.75</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="AD28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE28" t="n">
         <v>1.6</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AF28" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH28" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.97</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.92</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>1.78</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V29" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AF29" t="n">
         <v>2.45</v>
       </c>
-      <c r="Q29" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V29" t="n">
-        <v>5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="AG29" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH29" t="n">
-        <v>1.22</v>
+        <v>2.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.47</v>
+        <v>3.97</v>
       </c>
       <c r="M30" t="n">
-        <v>3.41</v>
+        <v>3.92</v>
       </c>
       <c r="N30" t="n">
-        <v>2.67</v>
+        <v>1.78</v>
       </c>
       <c r="O30" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="P30" t="n">
-        <v>2.17</v>
+        <v>2.45</v>
       </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3.5</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>5</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.03</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.84</v>
+        <v>4.6</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.45</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.9</v>
+        <v>2.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.65</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.52</v>
+        <v>3.15</v>
       </c>
       <c r="N31" t="n">
-        <v>2.69</v>
+        <v>2.98</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="P31" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="Q31" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R31" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="V31" t="n">
+        <v>7</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AD31" t="n">
         <v>1.34</v>
       </c>
-      <c r="S31" t="n">
-        <v>3</v>
-      </c>
-      <c r="T31" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V31" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE31" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.26</v>
+        <v>2.47</v>
       </c>
       <c r="M33" t="n">
-        <v>6</v>
+        <v>3.41</v>
       </c>
       <c r="N33" t="n">
-        <v>8.9</v>
+        <v>2.67</v>
       </c>
       <c r="O33" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="Q33" t="n">
         <v>3</v>
       </c>
-      <c r="Q33" t="n">
-        <v>6.75</v>
-      </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="S33" t="n">
-        <v>4.6</v>
+        <v>3.12</v>
       </c>
       <c r="T33" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
-        <v>3.8</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.36</v>
+        <v>1.8</v>
       </c>
       <c r="AB33" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>1.87</v>
+        <v>2.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.87</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.6</v>
+        <v>1.5</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1492,25 +1492,25 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="M9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="N9" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="O9" t="n">
         <v>4.6</v>
-      </c>
-      <c r="N9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="O9" t="n">
-        <v>4.32</v>
       </c>
       <c r="P9" t="n">
         <v>2.21</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.14</v>
+        <v>2.02</v>
       </c>
       <c r="R9" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="S9" t="n">
         <v>3.94</v>
@@ -1537,16 +1537,16 @@
         <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="AB9" t="n">
         <v>2.25</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.1</v>
+        <v>2.38</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AE9" t="n">
         <v>1.62</v>
@@ -1555,7 +1555,7 @@
         <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH9" t="n">
         <v>1.12</v>
@@ -2087,13 +2087,13 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.9</v>
+        <v>6.7</v>
       </c>
       <c r="M14" t="n">
-        <v>5.6</v>
+        <v>6.05</v>
       </c>
       <c r="N14" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="O14" t="n">
         <v>5.5</v>
@@ -2132,13 +2132,13 @@
         <v>6.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AD14" t="n">
         <v>1.87</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.28</v>
+        <v>1.67</v>
       </c>
       <c r="M15" t="n">
-        <v>3.23</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>1.98</v>
+        <v>4.9</v>
       </c>
       <c r="O15" t="n">
-        <v>4.22</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.8</v>
+        <v>5.83</v>
       </c>
       <c r="R15" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>3</v>
+        <v>2.73</v>
       </c>
       <c r="U15" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.07</v>
+        <v>1.89</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.67</v>
+        <v>1.91</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.87</v>
+        <v>3.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AF15" t="n">
         <v>1.85</v>
       </c>
-      <c r="AF15" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AG15" t="n">
-        <v>1.67</v>
+        <v>1.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>2.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2321,77 +2321,77 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.3</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>3.45</v>
+        <v>3.62</v>
       </c>
       <c r="N16" t="n">
-        <v>2.8</v>
+        <v>3.93</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>6.65</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.49</v>
+        <v>1.71</v>
       </c>
       <c r="M17" t="n">
-        <v>2.93</v>
+        <v>3.9</v>
       </c>
       <c r="N17" t="n">
-        <v>3.06</v>
+        <v>4.6</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>2.16</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2.18</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>4.35</v>
       </c>
       <c r="R17" t="n">
-        <v>1.5</v>
+        <v>1.35</v>
       </c>
       <c r="S17" t="n">
-        <v>2.48</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>3.4</v>
+        <v>2.68</v>
       </c>
       <c r="U17" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="V17" t="n">
-        <v>8.6</v>
+        <v>6.25</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="X17" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.4</v>
+        <v>3.54</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.35</v>
+        <v>1.79</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.8</v>
+        <v>2.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.34</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.32</v>
+        <v>5.5</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>4</v>
       </c>
       <c r="N18" t="n">
-        <v>3.03</v>
+        <v>1.6</v>
       </c>
       <c r="O18" t="n">
+        <v>6</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="T18" t="n">
         <v>2.7</v>
       </c>
-      <c r="P18" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>4.12</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S18" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.89</v>
-      </c>
       <c r="U18" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W18" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X18" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z18" t="n">
-        <v>3.18</v>
+        <v>3.45</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.03</v>
+        <v>1.97</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.72</v>
+        <v>1.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>3.38</v>
+        <v>2.94</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>1.12</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.4</v>
+        <v>2.76</v>
       </c>
       <c r="M19" t="n">
-        <v>3.83</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.61</v>
+        <v>2.52</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>3.44</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S19" t="n">
-        <v>2.88</v>
+        <v>2.62</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="U19" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="X19" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.91</v>
+        <v>2.17</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.83</v>
+        <v>1.75</v>
       </c>
       <c r="AC19" t="n">
-        <v>2.94</v>
+        <v>3.6</v>
       </c>
       <c r="AD19" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG19" t="n">
         <v>1.33</v>
       </c>
-      <c r="AE19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AH19" t="n">
-        <v>1.12</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.66</v>
+        <v>2.2</v>
       </c>
       <c r="M20" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="N20" t="n">
-        <v>4.9</v>
+        <v>3.1</v>
       </c>
       <c r="O20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.15</v>
       </c>
-      <c r="P20" t="n">
-        <v>2.3</v>
-      </c>
       <c r="Q20" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="R20" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.94</v>
+        <v>2.73</v>
       </c>
       <c r="T20" t="n">
-        <v>2.68</v>
+        <v>2.89</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="V20" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.54</v>
+        <v>3.18</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.92</v>
+        <v>1.8</v>
       </c>
       <c r="AC20" t="n">
-        <v>2.8</v>
+        <v>3.38</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.36</v>
+        <v>1.24</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="M21" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="N21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O21" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH21" t="n">
         <v>1.67</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="O21" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="P21" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>5.82</v>
-      </c>
-      <c r="R21" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S21" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z21" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA21" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB21" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AF21" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>2.22</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="M22" t="n">
-        <v>3.16</v>
+        <v>3.2</v>
       </c>
       <c r="N22" t="n">
-        <v>2.29</v>
+        <v>2.2</v>
       </c>
       <c r="O22" t="n">
-        <v>3.44</v>
+        <v>3.52</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q22" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V22" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z22" t="n">
         <v>3</v>
       </c>
-      <c r="R22" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="V22" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y22" t="n">
+      <c r="AA22" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG22" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z22" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA22" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF22" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG22" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH22" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="M23" t="n">
-        <v>3.55</v>
+        <v>3.13</v>
       </c>
       <c r="N23" t="n">
-        <v>4.1</v>
+        <v>2.29</v>
       </c>
       <c r="O23" t="n">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="P23" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q23" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="R23" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S23" t="n">
-        <v>3.03</v>
+        <v>2.65</v>
       </c>
       <c r="T23" t="n">
-        <v>2.55</v>
+        <v>2.99</v>
       </c>
       <c r="U23" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="V23" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="W23" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.83</v>
+        <v>1.94</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="AF23" t="n">
         <v>2</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.95</v>
+        <v>1.28</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.44</v>
+        <v>2.36</v>
       </c>
       <c r="M24" t="n">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>3.01</v>
+        <v>2.9</v>
       </c>
       <c r="O24" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W24" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="M25" t="n">
-        <v>3.13</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>2.29</v>
+        <v>2.7</v>
       </c>
       <c r="O25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q25" t="n">
         <v>3.35</v>
       </c>
-      <c r="P25" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q25" t="n">
-        <v>3.08</v>
-      </c>
       <c r="R25" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="S25" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V25" t="n">
+        <v>10</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AA25" t="n">
         <v>2.65</v>
       </c>
-      <c r="T25" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V25" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>1.94</v>
-      </c>
       <c r="AB25" t="n">
-        <v>1.76</v>
+        <v>1.5</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.82</v>
+        <v>1.98</v>
       </c>
       <c r="AF25" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.26</v>
+        <v>4.2</v>
       </c>
       <c r="M26" t="n">
-        <v>6</v>
+        <v>3.6</v>
       </c>
       <c r="N26" t="n">
-        <v>8.9</v>
+        <v>1.88</v>
       </c>
       <c r="O26" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>3</v>
+        <v>2.23</v>
       </c>
       <c r="Q26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S26" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V26" t="n">
         <v>6.75</v>
       </c>
-      <c r="R26" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S26" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="T26" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V26" t="n">
-        <v>3.8</v>
-      </c>
       <c r="W26" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.36</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>3.1</v>
+        <v>1.88</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.87</v>
+        <v>3.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.87</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>3.6</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,58 +3634,58 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.62</v>
+        <v>2.19</v>
       </c>
       <c r="M27" t="n">
-        <v>3.32</v>
+        <v>3.45</v>
       </c>
       <c r="N27" t="n">
-        <v>2.59</v>
+        <v>3.19</v>
       </c>
       <c r="O27" t="n">
-        <v>3.28</v>
+        <v>2.78</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S27" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="T27" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="U27" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="W27" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.87</v>
+        <v>2.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.19</v>
+        <v>3.25</v>
       </c>
       <c r="AD27" t="n">
         <v>1.3</v>
@@ -3697,10 +3697,10 @@
         <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.42</v>
+        <v>1.57</v>
       </c>
       <c r="M28" t="n">
-        <v>3.52</v>
+        <v>4.4</v>
       </c>
       <c r="N28" t="n">
-        <v>2.69</v>
+        <v>5.3</v>
       </c>
       <c r="O28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="P28" t="n">
-        <v>2.21</v>
+        <v>2.5</v>
       </c>
       <c r="Q28" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="R28" t="n">
-        <v>1.34</v>
+        <v>1.22</v>
       </c>
       <c r="S28" t="n">
-        <v>3</v>
+        <v>3.94</v>
       </c>
       <c r="T28" t="n">
-        <v>2.4</v>
+        <v>1.98</v>
       </c>
       <c r="U28" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="V28" t="n">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.09</v>
+        <v>1.18</v>
       </c>
       <c r="X28" t="n">
         <v>1.02</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.19</v>
+        <v>1.13</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.1</v>
+        <v>5.75</v>
       </c>
       <c r="AA28" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.75</v>
       </c>
-      <c r="AB28" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="V29" t="n">
+        <v>5</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="AD29" t="n">
         <v>1.55</v>
       </c>
-      <c r="M29" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="N29" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="AE29" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.22</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V29" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>2.4</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>3.97</v>
+        <v>2.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.78</v>
+        <v>2.64</v>
       </c>
       <c r="O30" t="n">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="S30" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="T30" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>5</v>
+        <v>6.45</v>
       </c>
       <c r="W30" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.6</v>
+        <v>3.84</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.53</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.25</v>
+        <v>2.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.65</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.53</v>
+        <v>1.59</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.25</v>
+        <v>1.44</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.22</v>
+        <v>1.54</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="M31" t="n">
-        <v>3.15</v>
+        <v>3.4</v>
       </c>
       <c r="N31" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S31" t="n">
         <v>2.98</v>
       </c>
-      <c r="O31" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.88</v>
-      </c>
       <c r="T31" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
         <v>1.39</v>
       </c>
       <c r="V31" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W31" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.68</v>
+        <v>3.55</v>
       </c>
       <c r="AA31" t="n">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="AE31" t="n">
         <v>1.7</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>4</v>
+        <v>1.25</v>
       </c>
       <c r="M32" t="n">
-        <v>3.61</v>
+        <v>6.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.84</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>4</v>
+        <v>1.65</v>
       </c>
       <c r="P32" t="n">
-        <v>2.23</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.48</v>
+        <v>6.5</v>
       </c>
       <c r="R32" t="n">
-        <v>1.41</v>
+        <v>1.19</v>
       </c>
       <c r="S32" t="n">
-        <v>2.89</v>
+        <v>4.4</v>
       </c>
       <c r="T32" t="n">
-        <v>2.81</v>
+        <v>1.99</v>
       </c>
       <c r="U32" t="n">
-        <v>1.43</v>
+        <v>1.86</v>
       </c>
       <c r="V32" t="n">
-        <v>6.8</v>
+        <v>3.8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.07</v>
+        <v>1.22</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.45</v>
+        <v>6.5</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.82</v>
+        <v>1.33</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.92</v>
+        <v>2.98</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.6</v>
+        <v>2.02</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.78</v>
+        <v>1.65</v>
       </c>
       <c r="AF32" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.25</v>
+        <v>3.5</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,70 +4348,70 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>3.41</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Q33" t="n">
         <v>3</v>
       </c>
       <c r="R33" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S33" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T33" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U33" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V33" t="n">
-        <v>6.45</v>
+        <v>5.6</v>
       </c>
       <c r="W33" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X33" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z33" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AB33" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="AH33" t="n">
         <v>1.5</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1385,7 +1385,7 @@
         <v>2.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.2</v>
+        <v>2.39</v>
       </c>
       <c r="Q8" t="n">
         <v>5.5</v>
@@ -1403,22 +1403,22 @@
         <v>1.42</v>
       </c>
       <c r="V8" t="n">
-        <v>6.75</v>
+        <v>6.1</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="Z8" t="n">
         <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
         <v>1.9</v>
@@ -1439,7 +1439,7 @@
         <v>1.14</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="AI8" s="3" t="n">
         <v>46042.50347222222</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="M10" t="n">
-        <v>3.85</v>
+        <v>3.5</v>
       </c>
       <c r="N10" t="n">
-        <v>4.6</v>
+        <v>6.7</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB10" t="n">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="M11" t="n">
-        <v>3.25</v>
+        <v>2.7</v>
       </c>
       <c r="N11" t="n">
-        <v>3.31</v>
+        <v>3.4</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.4</v>
+        <v>4.54</v>
       </c>
       <c r="R11" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>2.82</v>
+        <v>2.07</v>
       </c>
       <c r="T11" t="n">
-        <v>2.35</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>1.42</v>
+        <v>1.16</v>
       </c>
       <c r="V11" t="n">
+        <v>13</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC11" t="n">
         <v>6.25</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3</v>
-      </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.11</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.53</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>2.7</v>
+        <v>3.36</v>
       </c>
       <c r="N12" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
         <v>3.4</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AB12" t="n">
         <v>1.85</v>
       </c>
-      <c r="Q12" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="T12" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="V12" t="n">
-        <v>13</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y12" t="n">
+      <c r="AC12" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z12" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>3.5</v>
+        <v>4.2</v>
       </c>
       <c r="N13" t="n">
-        <v>6.7</v>
+        <v>4.39</v>
       </c>
       <c r="O13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>8.15</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
         <v>1.44</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V13" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1</v>
-      </c>
-      <c r="X13" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.35</v>
-      </c>
       <c r="AB13" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.67</v>
+        <v>3.18</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>4.9</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.15</v>
       </c>
-      <c r="P15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="V15" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD15" t="n">
+      <c r="AH15" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH15" t="n">
-        <v>2.22</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,61 +2325,61 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>2.75</v>
       </c>
       <c r="M16" t="n">
-        <v>3.62</v>
+        <v>3.13</v>
       </c>
       <c r="N16" t="n">
-        <v>3.93</v>
+        <v>2.29</v>
       </c>
       <c r="O16" t="n">
-        <v>2.38</v>
+        <v>3.35</v>
       </c>
       <c r="P16" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.4</v>
+        <v>3.08</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3</v>
+        <v>1.42</v>
       </c>
       <c r="S16" t="n">
-        <v>2.89</v>
+        <v>2.65</v>
       </c>
       <c r="T16" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V16" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE16" t="n">
         <v>1.82</v>
@@ -2388,10 +2388,10 @@
         <v>2</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.28</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.71</v>
+        <v>2.36</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="N17" t="n">
-        <v>4.6</v>
+        <v>2.9</v>
       </c>
       <c r="O17" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.35</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>2.68</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.76</v>
+        <v>1.71</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>3.9</v>
       </c>
       <c r="N19" t="n">
-        <v>2.52</v>
+        <v>4.6</v>
       </c>
       <c r="O19" t="n">
-        <v>3.44</v>
+        <v>2.16</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="Q19" t="n">
-        <v>3</v>
+        <v>4.35</v>
       </c>
       <c r="R19" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T19" t="n">
-        <v>2.94</v>
+        <v>2.68</v>
       </c>
       <c r="U19" t="n">
-        <v>1.35</v>
+        <v>1.45</v>
       </c>
       <c r="V19" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W19" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X19" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.54</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.17</v>
+        <v>1.79</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AE19" t="n">
         <v>1.75</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.8</v>
       </c>
       <c r="AF19" t="n">
         <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>2.1</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="M20" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.93</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="M20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O20" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q20" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="S20" t="n">
-        <v>2.73</v>
+        <v>2.89</v>
       </c>
       <c r="T20" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="U20" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="X20" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.38</v>
+        <v>3.15</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.24</v>
+        <v>1.3</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.18</v>
+        <v>2.2</v>
       </c>
       <c r="M22" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
       <c r="N22" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="O22" t="n">
-        <v>3.52</v>
+        <v>2.7</v>
       </c>
       <c r="P22" t="n">
-        <v>2.06</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="T22" t="n">
-        <v>3.04</v>
+        <v>2.89</v>
       </c>
       <c r="U22" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V22" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
         <v>1.03</v>
       </c>
       <c r="X22" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="Z22" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.15</v>
+        <v>1.98</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="AC22" t="n">
-        <v>3.87</v>
+        <v>3.38</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="M23" t="n">
-        <v>3.13</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.29</v>
+        <v>2.52</v>
       </c>
       <c r="O23" t="n">
-        <v>3.35</v>
+        <v>3.44</v>
       </c>
       <c r="P23" t="n">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="R23" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>2.99</v>
+        <v>2.94</v>
       </c>
       <c r="U23" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V23" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X23" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="n">
         <v>3.1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.94</v>
+        <v>2.17</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AC23" t="n">
         <v>3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="AE23" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.28</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3273,77 +3273,77 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.36</v>
+        <v>1.67</v>
       </c>
       <c r="M24" t="n">
-        <v>3.55</v>
+        <v>3.8</v>
       </c>
       <c r="N24" t="n">
-        <v>2.9</v>
+        <v>4.9</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>5.83</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.73</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4.2</v>
+        <v>2.19</v>
       </c>
       <c r="M26" t="n">
-        <v>3.6</v>
+        <v>3.45</v>
       </c>
       <c r="N26" t="n">
-        <v>1.88</v>
+        <v>3.19</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>2.78</v>
       </c>
       <c r="P26" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.45</v>
+        <v>3.1</v>
       </c>
       <c r="R26" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S26" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="T26" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="U26" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V26" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="X26" t="n">
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="AD26" t="n">
         <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.19</v>
+        <v>1.57</v>
       </c>
       <c r="M27" t="n">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="N27" t="n">
-        <v>3.19</v>
+        <v>5.3</v>
       </c>
       <c r="O27" t="n">
-        <v>2.78</v>
+        <v>2</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.22</v>
       </c>
       <c r="S27" t="n">
-        <v>2.88</v>
+        <v>3.94</v>
       </c>
       <c r="T27" t="n">
-        <v>2.79</v>
+        <v>1.98</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>4.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.04</v>
+        <v>1.18</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.24</v>
+        <v>1.13</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.5</v>
+        <v>5.75</v>
       </c>
       <c r="AA27" t="n">
-        <v>2.02</v>
+        <v>1.44</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>2.64</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.25</v>
+        <v>2.1</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.36</v>
+        <v>1.2</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.57</v>
+        <v>2.4</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="M28" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="N28" t="n">
-        <v>5.3</v>
+        <v>1.88</v>
       </c>
       <c r="O28" t="n">
+        <v>4</v>
+      </c>
+      <c r="P28" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S28" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V28" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF28" t="n">
         <v>2</v>
       </c>
-      <c r="P28" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T28" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V28" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>2.38</v>
-      </c>
       <c r="AG28" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>2.4</v>
+        <v>1.25</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3997,67 +3997,67 @@
         <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O30" t="n">
         <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V30" t="n">
-        <v>6.45</v>
+        <v>5.6</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
         <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>2.65</v>
+        <v>1.25</v>
       </c>
       <c r="M31" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="N31" t="n">
-        <v>2.63</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>3.28</v>
+        <v>1.65</v>
       </c>
       <c r="P31" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="R31" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="S31" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V31" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB31" t="n">
         <v>2.98</v>
       </c>
-      <c r="T31" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V31" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AC31" t="n">
-        <v>3.23</v>
+        <v>2.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.29</v>
+        <v>1.91</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.7</v>
+        <v>1.65</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>1.25</v>
+        <v>2.65</v>
       </c>
       <c r="M32" t="n">
-        <v>6.5</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>8.199999999999999</v>
+        <v>2.63</v>
       </c>
       <c r="O32" t="n">
-        <v>1.65</v>
+        <v>3.28</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>2.14</v>
       </c>
       <c r="Q32" t="n">
-        <v>6.5</v>
+        <v>3.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.19</v>
+        <v>1.38</v>
       </c>
       <c r="S32" t="n">
-        <v>4.4</v>
+        <v>2.98</v>
       </c>
       <c r="T32" t="n">
-        <v>1.99</v>
+        <v>2.81</v>
       </c>
       <c r="U32" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="V32" t="n">
-        <v>3.8</v>
+        <v>7.2</v>
       </c>
       <c r="W32" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="Z32" t="n">
-        <v>6.5</v>
+        <v>3.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.98</v>
+        <v>1.83</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.02</v>
+        <v>3.23</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.91</v>
+        <v>1.29</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>3.5</v>
+        <v>1.5</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4354,67 +4354,67 @@
         <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="O33" t="n">
         <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
-        <v>5.6</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>4.1</v>
+        <v>3.84</v>
       </c>
       <c r="AA33" t="n">
         <v>1.79</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.72</v>
+        <v>2.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="M2" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="N2" t="n">
-        <v>2.17</v>
+        <v>2.25</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="M3" t="n">
-        <v>2.95</v>
+        <v>2.86</v>
       </c>
       <c r="N3" t="n">
-        <v>3.65</v>
+        <v>3.56</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,13 +1016,13 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1061,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.85</v>
+        <v>3.35</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1385,13 +1385,13 @@
         <v>2.05</v>
       </c>
       <c r="P8" t="n">
-        <v>2.39</v>
+        <v>2.28</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="R8" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="S8" t="n">
         <v>2.91</v>
@@ -1400,10 +1400,10 @@
         <v>2.65</v>
       </c>
       <c r="U8" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="V8" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="W8" t="n">
         <v>1.06</v>
@@ -1412,13 +1412,13 @@
         <v>1.05</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="Z8" t="n">
         <v>3.6</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB8" t="n">
         <v>1.9</v>
@@ -1427,16 +1427,16 @@
         <v>2.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="AH8" t="n">
         <v>2.3</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.5</v>
       </c>
-      <c r="N10" t="n">
-        <v>6.7</v>
-      </c>
       <c r="O10" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB10" t="n">
         <v>2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>7</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>2.7</v>
+        <v>3.92</v>
       </c>
       <c r="N11" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.33</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N12" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="M12" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="N12" t="n">
-        <v>3.32</v>
-      </c>
-      <c r="O12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="T12" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="V12" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA12" t="n">
         <v>2.35</v>
       </c>
-      <c r="U12" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V12" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.5</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.21</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.36</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="M13" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>4.54</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="T13" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="V13" t="n">
+        <v>13</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y13" t="n">
         <v>1.62</v>
       </c>
-      <c r="M13" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="N13" t="n">
-        <v>4.39</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0</v>
-      </c>
-      <c r="T13" t="n">
-        <v>0</v>
-      </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="M15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z15" t="n">
         <v>3.18</v>
       </c>
-      <c r="M15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="N15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O15" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="P15" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3</v>
-      </c>
       <c r="AA15" t="n">
-        <v>2.15</v>
+        <v>1.99</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.87</v>
+        <v>3.38</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>1.67</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,73 +2325,73 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.75</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.13</v>
+        <v>4</v>
       </c>
       <c r="N16" t="n">
-        <v>2.29</v>
+        <v>1.58</v>
       </c>
       <c r="O16" t="n">
-        <v>3.35</v>
+        <v>6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.06</v>
+        <v>2.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.08</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.65</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.99</v>
+        <v>2.7</v>
       </c>
       <c r="U16" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="V16" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W16" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
         <v>1.04</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.1</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.94</v>
       </c>
-      <c r="AB16" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AF16" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.28</v>
+        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2440,77 +2440,77 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.36</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N17" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="O17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T17" t="n">
         <v>3.55</v>
       </c>
-      <c r="N17" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="M18" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>3.2</v>
       </c>
       <c r="O18" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="P18" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="R18" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V18" t="n">
+        <v>8</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y18" t="n">
         <v>1.36</v>
       </c>
-      <c r="S18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V18" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W18" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X18" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y18" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z18" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC18" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,61 +2682,61 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.71</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>3.9</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>4.6</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>4.35</v>
+        <v>3.08</v>
       </c>
       <c r="R19" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="S19" t="n">
-        <v>2.94</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.68</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="W19" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X19" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y19" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.22</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.34</v>
       </c>
       <c r="AE19" t="n">
         <v>1.75</v>
@@ -2745,10 +2745,10 @@
         <v>1.95</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.1</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.86</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>3.93</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>2.38</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>4.4</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V20" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG20" t="n">
         <v>1.3</v>
       </c>
-      <c r="S20" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V20" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AD20" t="n">
+      <c r="AH20" t="n">
         <v>1.3</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>2</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1.85</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>2.35</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.47</v>
       </c>
       <c r="N21" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="O21" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>2.47</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>3.1</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>2.7</v>
+        <v>2.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.15</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="S22" t="n">
-        <v>2.73</v>
+        <v>2.94</v>
       </c>
       <c r="T22" t="n">
-        <v>2.89</v>
+        <v>2.62</v>
       </c>
       <c r="U22" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.03</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.05</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.18</v>
+        <v>3.54</v>
       </c>
       <c r="AA22" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB22" t="n">
         <v>1.98</v>
       </c>
-      <c r="AB22" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AC22" t="n">
-        <v>3.38</v>
+        <v>2.83</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3158,22 +3158,22 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.76</v>
+        <v>2.69</v>
       </c>
       <c r="M23" t="n">
         <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="O23" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
         <v>1.43</v>
@@ -3200,7 +3200,7 @@
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>3.1</v>
+        <v>2.99</v>
       </c>
       <c r="AA23" t="n">
         <v>2.17</v>
@@ -3212,19 +3212,19 @@
         <v>3.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AE23" t="n">
         <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG23" t="n">
         <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="M24" t="n">
-        <v>3.8</v>
+        <v>3.69</v>
       </c>
       <c r="N24" t="n">
-        <v>4.9</v>
+        <v>3.93</v>
       </c>
       <c r="O24" t="n">
-        <v>2.15</v>
+        <v>2.51</v>
       </c>
       <c r="P24" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q24" t="n">
-        <v>5.83</v>
+        <v>4.2</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T24" t="n">
-        <v>2.73</v>
+        <v>2.84</v>
       </c>
       <c r="U24" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
         <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.7</v>
+        <v>3.12</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH24" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AG24" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AH24" t="n">
-        <v>2.22</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>2.8</v>
+        <v>1.58</v>
       </c>
       <c r="M25" t="n">
-        <v>3.1</v>
+        <v>3.98</v>
       </c>
       <c r="N25" t="n">
-        <v>2.7</v>
+        <v>5.37</v>
       </c>
       <c r="O25" t="n">
-        <v>3.4</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.88</v>
       </c>
-      <c r="Q25" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V25" t="n">
-        <v>10</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.5</v>
-      </c>
       <c r="AC25" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.19</v>
+        <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>3.19</v>
+        <v>2.64</v>
       </c>
       <c r="O26" t="n">
-        <v>2.78</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="R26" t="n">
-        <v>1.35</v>
+        <v>1.3</v>
       </c>
       <c r="S26" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="T26" t="n">
-        <v>2.79</v>
+        <v>2.5</v>
       </c>
       <c r="U26" t="n">
-        <v>1.39</v>
+        <v>1.49</v>
       </c>
       <c r="V26" t="n">
-        <v>7</v>
+        <v>6.45</v>
       </c>
       <c r="W26" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.24</v>
+        <v>1.21</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.25</v>
+        <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>1.59</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>2.24</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.57</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>5.3</v>
+        <v>2.7</v>
       </c>
       <c r="O27" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.5</v>
+        <v>2.36</v>
       </c>
       <c r="Q27" t="n">
-        <v>4.6</v>
+        <v>3</v>
       </c>
       <c r="R27" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="S27" t="n">
-        <v>3.94</v>
+        <v>3</v>
       </c>
       <c r="T27" t="n">
-        <v>1.98</v>
+        <v>2.4</v>
       </c>
       <c r="U27" t="n">
-        <v>1.75</v>
+        <v>1.51</v>
       </c>
       <c r="V27" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
       <c r="W27" t="n">
-        <v>1.18</v>
+        <v>1.09</v>
       </c>
       <c r="X27" t="n">
         <v>1.02</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.13</v>
+        <v>1.19</v>
       </c>
       <c r="Z27" t="n">
-        <v>5.75</v>
+        <v>4.1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.44</v>
+        <v>1.79</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.64</v>
+        <v>2.12</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.1</v>
+        <v>2.72</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.75</v>
+        <v>1.43</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.38</v>
+        <v>2.25</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.2</v>
+        <v>1.42</v>
       </c>
       <c r="AH27" t="n">
-        <v>2.4</v>
+        <v>1.5</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,37 +3753,37 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.2</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.88</v>
+        <v>2.63</v>
       </c>
       <c r="O28" t="n">
-        <v>4</v>
+        <v>3.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>2.89</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
         <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.43</v>
+        <v>1.39</v>
       </c>
       <c r="V28" t="n">
-        <v>6.75</v>
+        <v>7.2</v>
       </c>
       <c r="W28" t="n">
         <v>1.08</v>
@@ -3792,34 +3792,34 @@
         <v>1.05</v>
       </c>
       <c r="Y28" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="AD28" t="n">
         <v>1.29</v>
       </c>
-      <c r="Z28" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AE28" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
         <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>3.9</v>
+        <v>1.57</v>
       </c>
       <c r="M29" t="n">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.83</v>
+        <v>5.3</v>
       </c>
       <c r="O29" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="P29" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="S29" t="n">
-        <v>3.5</v>
+        <v>3.94</v>
       </c>
       <c r="T29" t="n">
-        <v>2.36</v>
+        <v>1.98</v>
       </c>
       <c r="U29" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="W29" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y29" t="n">
         <v>1.13</v>
       </c>
-      <c r="X29" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y29" t="n">
+      <c r="Z29" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AG29" t="n">
         <v>1.2</v>
       </c>
-      <c r="Z29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>2.4</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M30" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R30" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V30" t="n">
+        <v>7</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z30" t="n">
         <v>3.5</v>
       </c>
-      <c r="N30" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="O30" t="n">
-        <v>3</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="Q30" t="n">
-        <v>3</v>
-      </c>
-      <c r="R30" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="U30" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="V30" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>4.1</v>
-      </c>
       <c r="AA30" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.72</v>
+        <v>3.25</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.43</v>
+        <v>1.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O31" t="n">
+        <v>4</v>
+      </c>
+      <c r="P31" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V31" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH31" t="n">
         <v>1.25</v>
-      </c>
-      <c r="M31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N31" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P31" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S31" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T31" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V31" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X31" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y31" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE31" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF31" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N32" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="O32" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="P32" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R32" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="V32" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>1.25</v>
       </c>
       <c r="M33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N33" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P33" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S33" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V33" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH33" t="n">
         <v>3.5</v>
-      </c>
-      <c r="N33" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="O33" t="n">
-        <v>3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V33" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC33" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD33" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AE33" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AF33" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AG33" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AH33" t="n">
-        <v>1.54</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.45</v>
+        <v>2.12</v>
       </c>
       <c r="M2" t="n">
-        <v>2.75</v>
+        <v>2.86</v>
       </c>
       <c r="N2" t="n">
-        <v>2.25</v>
+        <v>3.56</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.12</v>
+        <v>3.45</v>
       </c>
       <c r="M3" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="N3" t="n">
-        <v>3.56</v>
+        <v>2.25</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -1135,7 +1135,7 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
         <v>3.3</v>
@@ -1147,22 +1147,22 @@
         <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
         <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
         <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>2.9</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
         <v>7.5</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="M10" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="N10" t="n">
-        <v>3.5</v>
+        <v>7.32</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="R10" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="T10" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="U10" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="V10" t="n">
-        <v>6.25</v>
+        <v>9.1</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X10" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="AB10" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC10" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="M11" t="n">
-        <v>3.92</v>
+        <v>2.64</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="M12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N12" t="n">
         <v>3.5</v>
       </c>
-      <c r="N12" t="n">
-        <v>6.7</v>
-      </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S12" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U12" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V12" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>7</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="S12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.53</v>
-      </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>2.9</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.25</v>
+        <v>1.62</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.36</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>3.92</v>
       </c>
       <c r="N13" t="n">
-        <v>3.4</v>
+        <v>4.33</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4.54</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.88</v>
+        <v>1.44</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.33</v>
+        <v>2.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.25</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.16</v>
+        <v>3.4</v>
       </c>
       <c r="M15" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.2</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>3.52</v>
       </c>
       <c r="P15" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V15" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA15" t="n">
         <v>2.15</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="U15" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="V15" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="AG15" t="n">
         <v>1.3</v>
       </c>
-      <c r="Z15" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE15" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG15" t="n">
-        <v>1.28</v>
-      </c>
       <c r="AH15" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>5.5</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>4</v>
+        <v>3.69</v>
       </c>
       <c r="N16" t="n">
-        <v>1.58</v>
+        <v>3.93</v>
       </c>
       <c r="O16" t="n">
-        <v>6</v>
+        <v>2.51</v>
       </c>
       <c r="P16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.05</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -2349,49 +2349,49 @@
         <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="U16" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>6.5</v>
+        <v>6.65</v>
       </c>
       <c r="W16" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X16" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AH16" t="n">
         <v>1.85</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>2.16</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>3.4</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>3.1</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>2.15</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R17" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.94</v>
       </c>
       <c r="T17" t="n">
-        <v>3.55</v>
+        <v>2.89</v>
       </c>
       <c r="U17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="V17" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="AD17" t="n">
         <v>1.24</v>
       </c>
-      <c r="V17" t="n">
-        <v>10</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.67</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.25</v>
+        <v>2.69</v>
       </c>
       <c r="M18" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>3.2</v>
+        <v>2.51</v>
       </c>
       <c r="O18" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.9</v>
+        <v>3.12</v>
       </c>
       <c r="R18" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
         <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.72</v>
+        <v>2.99</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.8</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.67</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.75</v>
+        <v>1.58</v>
       </c>
       <c r="M19" t="n">
-        <v>3.13</v>
+        <v>3.98</v>
       </c>
       <c r="N19" t="n">
-        <v>2.29</v>
+        <v>5.37</v>
       </c>
       <c r="O19" t="n">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="P19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.08</v>
+        <v>5.57</v>
       </c>
       <c r="R19" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>2.81</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.76</v>
+        <v>1.88</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.4</v>
+        <v>2.15</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.47</v>
       </c>
       <c r="N20" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="O20" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>2.74</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2916,77 +2916,77 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.47</v>
+        <v>3.14</v>
       </c>
       <c r="N21" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M23" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N23" t="n">
         <v>2.69</v>
       </c>
-      <c r="M23" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N23" t="n">
-        <v>2.51</v>
-      </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="AB23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC23" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE23" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF23" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.86</v>
+        <v>2.88</v>
       </c>
       <c r="M24" t="n">
-        <v>3.69</v>
+        <v>3.25</v>
       </c>
       <c r="N24" t="n">
-        <v>3.93</v>
+        <v>2.45</v>
       </c>
       <c r="O24" t="n">
-        <v>2.51</v>
+        <v>3.35</v>
       </c>
       <c r="P24" t="n">
-        <v>2.29</v>
+        <v>2.1</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R24" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S24" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T24" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="U24" t="n">
-        <v>1.39</v>
+        <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>6.65</v>
+        <v>7.9</v>
       </c>
       <c r="W24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X24" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.38</v>
+        <v>3.34</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.85</v>
+        <v>2.04</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AE24" t="n">
         <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.29</v>
+        <v>1.53</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.85</v>
+        <v>1.41</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,34 +3396,34 @@
         </is>
       </c>
       <c r="L25" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M25" t="n">
+        <v>4</v>
+      </c>
+      <c r="N25" t="n">
         <v>1.58</v>
       </c>
-      <c r="M25" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N25" t="n">
-        <v>5.37</v>
-      </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.57</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
         <v>6.5</v>
@@ -3432,37 +3432,37 @@
         <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF25" t="n">
         <v>1.85</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.15</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3521,67 +3521,67 @@
         <v>3.5</v>
       </c>
       <c r="N26" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R26" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="S26" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="U26" t="n">
-        <v>1.49</v>
+        <v>1.51</v>
       </c>
       <c r="V26" t="n">
-        <v>6.45</v>
+        <v>5.6</v>
       </c>
       <c r="W26" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X26" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.84</v>
+        <v>4.1</v>
       </c>
       <c r="AA26" t="n">
         <v>1.79</v>
       </c>
       <c r="AB26" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.9</v>
+        <v>2.72</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,70 +3634,70 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="M27" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="N27" t="n">
-        <v>2.7</v>
+        <v>2.63</v>
       </c>
       <c r="O27" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="P27" t="n">
-        <v>2.36</v>
+        <v>2.14</v>
       </c>
       <c r="Q27" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T27" t="n">
-        <v>2.4</v>
+        <v>2.81</v>
       </c>
       <c r="U27" t="n">
-        <v>1.51</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>5.6</v>
+        <v>7.2</v>
       </c>
       <c r="W27" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.1</v>
+        <v>3.55</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.79</v>
+        <v>1.92</v>
       </c>
       <c r="AB27" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AC27" t="n">
-        <v>2.72</v>
+        <v>3.23</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.42</v>
+        <v>1.3</v>
       </c>
       <c r="AH27" t="n">
         <v>1.5</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>3.95</v>
       </c>
       <c r="N28" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="O28" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S28" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T28" t="n">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="U28" t="n">
-        <v>1.39</v>
+        <v>1.56</v>
       </c>
       <c r="V28" t="n">
-        <v>7.2</v>
+        <v>5</v>
       </c>
       <c r="W28" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X28" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z28" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AB28" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.55</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="M29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O29" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P29" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S29" t="n">
         <v>4.4</v>
       </c>
-      <c r="N29" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O29" t="n">
-        <v>2</v>
-      </c>
-      <c r="P29" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V29" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W29" t="n">
         <v>1.22</v>
       </c>
-      <c r="S29" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="V29" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.18</v>
-      </c>
       <c r="X29" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z29" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB29" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="AC29" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.38</v>
+        <v>2.15</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AH29" t="n">
-        <v>2.4</v>
+        <v>3.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3955,7 +3955,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.18</v>
+        <v>4.2</v>
       </c>
       <c r="M30" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="N30" t="n">
-        <v>3.13</v>
+        <v>1.88</v>
       </c>
       <c r="O30" t="n">
-        <v>2.79</v>
+        <v>4</v>
       </c>
       <c r="P30" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.1</v>
+        <v>2.45</v>
       </c>
       <c r="R30" t="n">
-        <v>1.35</v>
+        <v>1.41</v>
       </c>
       <c r="S30" t="n">
-        <v>3.08</v>
+        <v>2.89</v>
       </c>
       <c r="T30" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U30" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V30" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="W30" t="n">
-        <v>1.05</v>
+        <v>1.08</v>
       </c>
       <c r="X30" t="n">
         <v>1.05</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.25</v>
+        <v>3.6</v>
       </c>
       <c r="AD30" t="n">
         <v>1.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.57</v>
+        <v>1.25</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4.2</v>
+        <v>1.57</v>
       </c>
       <c r="M31" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="N31" t="n">
-        <v>1.88</v>
+        <v>5.3</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P31" t="n">
-        <v>2.23</v>
+        <v>2.5</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.45</v>
+        <v>4.6</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.22</v>
       </c>
       <c r="S31" t="n">
-        <v>2.89</v>
+        <v>3.94</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>1.98</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="V31" t="n">
-        <v>6.75</v>
+        <v>4.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.18</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.13</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.45</v>
+        <v>5.75</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.88</v>
+        <v>1.44</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.88</v>
+        <v>2.64</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.6</v>
+        <v>2.1</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.3</v>
+        <v>1.75</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>2.4</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.9</v>
+        <v>2.18</v>
       </c>
       <c r="M32" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N32" t="n">
-        <v>1.83</v>
+        <v>3.13</v>
       </c>
       <c r="O32" t="n">
-        <v>4.1</v>
+        <v>2.79</v>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>2.2</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.35</v>
       </c>
       <c r="S32" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z32" t="n">
         <v>3.5</v>
       </c>
-      <c r="T32" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.6</v>
-      </c>
       <c r="AA32" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AB32" t="n">
-        <v>2.33</v>
+        <v>1.85</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.49</v>
+        <v>3.25</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.55</v>
+        <v>1.3</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.22</v>
+        <v>1.57</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.25</v>
+        <v>2.45</v>
       </c>
       <c r="M33" t="n">
-        <v>6.5</v>
+        <v>3.5</v>
       </c>
       <c r="N33" t="n">
-        <v>8.199999999999999</v>
+        <v>2.64</v>
       </c>
       <c r="O33" t="n">
-        <v>1.65</v>
+        <v>3</v>
       </c>
       <c r="P33" t="n">
-        <v>3</v>
+        <v>2.17</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.5</v>
+        <v>3.25</v>
       </c>
       <c r="R33" t="n">
-        <v>1.19</v>
+        <v>1.3</v>
       </c>
       <c r="S33" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="T33" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U33" t="n">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="V33" t="n">
-        <v>3.8</v>
+        <v>6.45</v>
       </c>
       <c r="W33" t="n">
-        <v>1.22</v>
+        <v>1.08</v>
       </c>
       <c r="X33" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z33" t="n">
-        <v>6.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA33" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AB33" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="AC33" t="n">
-        <v>2.02</v>
+        <v>2.9</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>1.4</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.65</v>
+        <v>1.59</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.15</v>
+        <v>2.24</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="AH33" t="n">
-        <v>3.5</v>
+        <v>1.54</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
-        <v>2.86</v>
+        <v>2.95</v>
       </c>
       <c r="N2" t="n">
-        <v>3.56</v>
+        <v>3.65</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="M3" t="n">
-        <v>2.75</v>
+        <v>2.85</v>
       </c>
       <c r="N3" t="n">
-        <v>2.25</v>
+        <v>2.17</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46042.41666666666</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N5" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1492,7 +1492,7 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.4</v>
+        <v>4.85</v>
       </c>
       <c r="M9" t="n">
         <v>4.33</v>
@@ -1504,10 +1504,10 @@
         <v>4.6</v>
       </c>
       <c r="P9" t="n">
-        <v>2.21</v>
+        <v>2.4</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
         <v>1.29</v>
@@ -1516,13 +1516,13 @@
         <v>3.94</v>
       </c>
       <c r="T9" t="n">
-        <v>2.3</v>
+        <v>2.49</v>
       </c>
       <c r="U9" t="n">
         <v>1.6</v>
       </c>
       <c r="V9" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="W9" t="n">
         <v>1.13</v>
@@ -1534,10 +1534,10 @@
         <v>1.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="AB9" t="n">
         <v>2.25</v>
@@ -1558,7 +1558,7 @@
         <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="M10" t="n">
-        <v>3.54</v>
+        <v>3.92</v>
       </c>
       <c r="N10" t="n">
-        <v>7.32</v>
+        <v>4.33</v>
       </c>
       <c r="O10" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
         <v>1.44</v>
       </c>
-      <c r="S10" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V10" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AB10" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>2.38</v>
+        <v>2.05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.64</v>
+        <v>3.4</v>
       </c>
       <c r="N11" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="P11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="R11" t="n">
-        <v>1.67</v>
+        <v>1.35</v>
       </c>
       <c r="S11" t="n">
-        <v>2.17</v>
+        <v>2.82</v>
       </c>
       <c r="T11" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="U11" t="n">
-        <v>1.2</v>
+        <v>1.41</v>
       </c>
       <c r="V11" t="n">
-        <v>13</v>
+        <v>6.25</v>
       </c>
       <c r="W11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>1.14</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.65</v>
+        <v>1.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.22</v>
+        <v>3.58</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>1.77</v>
       </c>
       <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD11" t="n">
         <v>1.33</v>
       </c>
-      <c r="AC11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>1.62</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2.05</v>
+        <v>1.47</v>
       </c>
       <c r="M12" t="n">
-        <v>3.4</v>
+        <v>3.54</v>
       </c>
       <c r="N12" t="n">
-        <v>3.5</v>
+        <v>7.32</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>2.06</v>
       </c>
       <c r="P12" t="n">
-        <v>2.2</v>
+        <v>1.99</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>7</v>
       </c>
       <c r="R12" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="S12" t="n">
-        <v>2.82</v>
+        <v>2.41</v>
       </c>
       <c r="T12" t="n">
-        <v>2.35</v>
+        <v>3.25</v>
       </c>
       <c r="U12" t="n">
-        <v>1.41</v>
+        <v>1.27</v>
       </c>
       <c r="V12" t="n">
-        <v>6.25</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="X12" t="n">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.58</v>
+        <v>2.63</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.77</v>
+        <v>2.34</v>
       </c>
       <c r="AB12" t="n">
-        <v>2</v>
+        <v>1.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.33</v>
+        <v>1.18</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.62</v>
+        <v>2.4</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>1.62</v>
+        <v>2.38</v>
       </c>
       <c r="M13" t="n">
-        <v>3.92</v>
+        <v>2.64</v>
       </c>
       <c r="N13" t="n">
-        <v>4.33</v>
+        <v>3.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AA13" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AG13" t="n">
         <v>1.44</v>
       </c>
-      <c r="AB13" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
-        <v>0</v>
-      </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2087,10 +2087,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="M14" t="n">
-        <v>6.05</v>
+        <v>6.06</v>
       </c>
       <c r="N14" t="n">
         <v>1.37</v>
@@ -2099,25 +2099,25 @@
         <v>5.5</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R14" t="n">
         <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="T14" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="U14" t="n">
         <v>1.9</v>
       </c>
       <c r="V14" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="W14" t="n">
         <v>1.25</v>
@@ -2138,7 +2138,7 @@
         <v>3.1</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AD14" t="n">
         <v>1.87</v>
@@ -2150,7 +2150,7 @@
         <v>2.4</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.15</v>
+        <v>2.9</v>
       </c>
       <c r="AH14" t="n">
         <v>1.13</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="M15" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N15" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3.52</v>
+        <v>2.15</v>
       </c>
       <c r="P15" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V15" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q15" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T15" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U15" t="n">
+      <c r="AC15" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.33</v>
       </c>
-      <c r="V15" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X15" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="M16" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="N16" t="n">
-        <v>3.93</v>
+        <v>3.1</v>
       </c>
       <c r="O16" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="P16" t="n">
-        <v>2.29</v>
+        <v>2.15</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>3.6</v>
       </c>
       <c r="R16" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="U16" t="n">
         <v>1.36</v>
       </c>
-      <c r="S16" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T16" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U16" t="n">
-        <v>1.39</v>
-      </c>
       <c r="V16" t="n">
-        <v>6.65</v>
+        <v>7.5</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
@@ -2364,34 +2364,34 @@
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="Z16" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC16" t="n">
         <v>3.38</v>
       </c>
-      <c r="AA16" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.12</v>
-      </c>
       <c r="AD16" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.28</v>
       </c>
-      <c r="AE16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,37 +2444,37 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M17" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="N17" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="O17" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="P17" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R17" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S17" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T17" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="U17" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V17" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="W17" t="n">
         <v>1.05</v>
@@ -2483,34 +2483,34 @@
         <v>1.05</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z17" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AB17" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE17" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC17" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF17" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="M18" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="N18" t="n">
         <v>2.69</v>
       </c>
-      <c r="M18" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N18" t="n">
-        <v>2.51</v>
-      </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.88</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.12</v>
+        <v>3.35</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.54</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>3.55</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>10</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1.1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.99</v>
+        <v>2.5</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.17</v>
+        <v>2.65</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF18" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.92</v>
-      </c>
       <c r="AG18" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,34 +2682,34 @@
         </is>
       </c>
       <c r="L19" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M19" t="n">
+        <v>4</v>
+      </c>
+      <c r="N19" t="n">
         <v>1.58</v>
       </c>
-      <c r="M19" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N19" t="n">
-        <v>5.37</v>
-      </c>
       <c r="O19" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="P19" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.57</v>
+        <v>2.05</v>
       </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T19" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V19" t="n">
         <v>6.5</v>
@@ -2718,37 +2718,37 @@
         <v>1.06</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF19" t="n">
         <v>1.85</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.15</v>
+        <v>1.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>1.58</v>
       </c>
       <c r="M21" t="n">
-        <v>3.14</v>
+        <v>3.98</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>5.37</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>2.15</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>5.57</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="S21" t="n">
-        <v>2.61</v>
+        <v>2.81</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>2.81</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>6.5</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>1.89</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.88</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>3.65</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,61 +3039,61 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>2.88</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>2.45</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>3.35</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S22" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="T22" t="n">
-        <v>2.62</v>
+        <v>2.99</v>
       </c>
       <c r="U22" t="n">
-        <v>1.43</v>
+        <v>1.34</v>
       </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>7.9</v>
       </c>
       <c r="W22" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="X22" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.32</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="AA22" t="n">
-        <v>1.8</v>
+        <v>2.04</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AC22" t="n">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="AE22" t="n">
         <v>1.75</v>
@@ -3102,10 +3102,10 @@
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.53</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.1</v>
+        <v>1.41</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="M23" t="n">
-        <v>2.97</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>2.69</v>
+        <v>2.51</v>
       </c>
       <c r="O23" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="P23" t="n">
-        <v>1.88</v>
+        <v>2.02</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.35</v>
+        <v>3.12</v>
       </c>
       <c r="R23" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.4</v>
+        <v>2.62</v>
       </c>
       <c r="T23" t="n">
-        <v>3.55</v>
+        <v>2.94</v>
       </c>
       <c r="U23" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V23" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD23" t="n">
         <v>1.24</v>
       </c>
-      <c r="V23" t="n">
-        <v>10</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AC23" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AD23" t="n">
-        <v>1.17</v>
-      </c>
       <c r="AE23" t="n">
-        <v>1.98</v>
+        <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.75</v>
+        <v>1.92</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>3.14</v>
       </c>
       <c r="N24" t="n">
-        <v>2.45</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>3.35</v>
+        <v>2.8</v>
       </c>
       <c r="P24" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.38</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>2.8</v>
+        <v>2.61</v>
       </c>
       <c r="T24" t="n">
-        <v>2.99</v>
+        <v>3.2</v>
       </c>
       <c r="U24" t="n">
         <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X24" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.34</v>
+        <v>2.72</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.04</v>
+        <v>2.25</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.75</v>
+        <v>1.91</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="N25" t="n">
-        <v>1.58</v>
+        <v>2.2</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>3.52</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>1.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>2.78</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.43</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>3.04</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7.4</v>
       </c>
       <c r="W25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X25" t="n">
         <v>1.06</v>
       </c>
-      <c r="X25" t="n">
-        <v>1.04</v>
-      </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AA25" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF25" t="n">
         <v>1.83</v>
       </c>
-      <c r="AB25" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE25" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF25" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.12</v>
+        <v>1.3</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3518,16 +3518,16 @@
         <v>2.45</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="N26" t="n">
-        <v>2.7</v>
+        <v>2.75</v>
       </c>
       <c r="O26" t="n">
         <v>3</v>
       </c>
       <c r="P26" t="n">
-        <v>2.36</v>
+        <v>2.21</v>
       </c>
       <c r="Q26" t="n">
         <v>3</v>
@@ -3539,13 +3539,13 @@
         <v>3</v>
       </c>
       <c r="T26" t="n">
-        <v>2.4</v>
+        <v>2.43</v>
       </c>
       <c r="U26" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="V26" t="n">
-        <v>5.6</v>
+        <v>6.15</v>
       </c>
       <c r="W26" t="n">
         <v>1.09</v>
@@ -3578,7 +3578,7 @@
         <v>2.25</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AH26" t="n">
         <v>1.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.65</v>
+        <v>3.9</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N27" t="n">
-        <v>2.63</v>
+        <v>1.83</v>
       </c>
       <c r="O27" t="n">
-        <v>3.28</v>
+        <v>4.1</v>
       </c>
       <c r="P27" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="R27" t="n">
-        <v>1.38</v>
+        <v>1.28</v>
       </c>
       <c r="S27" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T27" t="n">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="U27" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="V27" t="n">
-        <v>7.2</v>
+        <v>5.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X27" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="Z27" t="n">
-        <v>3.55</v>
+        <v>4.6</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.83</v>
+        <v>2.33</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.23</v>
+        <v>2.49</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.22</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>3.9</v>
+        <v>2.65</v>
       </c>
       <c r="M28" t="n">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="N28" t="n">
-        <v>1.83</v>
+        <v>2.6</v>
       </c>
       <c r="O28" t="n">
-        <v>4.1</v>
+        <v>3.28</v>
       </c>
       <c r="P28" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.2</v>
+        <v>3.2</v>
       </c>
       <c r="R28" t="n">
-        <v>1.28</v>
+        <v>1.38</v>
       </c>
       <c r="S28" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="T28" t="n">
-        <v>2.36</v>
+        <v>2.81</v>
       </c>
       <c r="U28" t="n">
-        <v>1.56</v>
+        <v>1.43</v>
       </c>
       <c r="V28" t="n">
-        <v>5</v>
+        <v>7.2</v>
       </c>
       <c r="W28" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="X28" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.2</v>
+        <v>1.32</v>
       </c>
       <c r="Z28" t="n">
-        <v>4.6</v>
+        <v>3.4</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.6</v>
+        <v>1.93</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.33</v>
+        <v>1.77</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.49</v>
+        <v>3.2</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.55</v>
+        <v>1.29</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.55</v>
+        <v>1.7</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
+        <v>4</v>
+      </c>
+      <c r="M29" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="N29" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="O29" t="n">
+        <v>4</v>
+      </c>
+      <c r="P29" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="R29" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S29" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="W29" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH29" t="n">
         <v>1.25</v>
-      </c>
-      <c r="M29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="N29" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="O29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="P29" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="R29" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S29" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="T29" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="U29" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="V29" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="W29" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X29" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y29" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="Z29" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="AA29" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="AC29" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AD29" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AE29" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AF29" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AG29" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>3.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.2</v>
+        <v>2.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="N30" t="n">
-        <v>1.88</v>
+        <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="P30" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="R30" t="n">
-        <v>1.41</v>
+        <v>1.36</v>
       </c>
       <c r="S30" t="n">
-        <v>2.89</v>
+        <v>3.12</v>
       </c>
       <c r="T30" t="n">
-        <v>2.81</v>
+        <v>2.5</v>
       </c>
       <c r="U30" t="n">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="V30" t="n">
-        <v>6.75</v>
+        <v>5.8</v>
       </c>
       <c r="W30" t="n">
         <v>1.08</v>
       </c>
       <c r="X30" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.29</v>
+        <v>1.21</v>
       </c>
       <c r="Z30" t="n">
-        <v>3.45</v>
+        <v>4.25</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.88</v>
+        <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AC30" t="n">
-        <v>3.6</v>
+        <v>2.83</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
         <v>1.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.57</v>
+        <v>1.27</v>
       </c>
       <c r="M31" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="N31" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="O31" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="P31" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S31" t="n">
         <v>4.4</v>
       </c>
-      <c r="N31" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2</v>
-      </c>
-      <c r="P31" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="S31" t="n">
-        <v>3.94</v>
-      </c>
       <c r="T31" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U31" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="V31" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="W31" t="n">
-        <v>1.18</v>
+        <v>1.24</v>
       </c>
       <c r="X31" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Z31" t="n">
-        <v>5.75</v>
+        <v>6.5</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.64</v>
+        <v>2.98</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.66</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.2</v>
+        <v>1.08</v>
       </c>
       <c r="AH31" t="n">
-        <v>2.4</v>
+        <v>3.35</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>2.45</v>
+        <v>1.55</v>
       </c>
       <c r="M33" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="N33" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="O33" t="n">
+        <v>2</v>
+      </c>
+      <c r="P33" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="R33" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S33" t="n">
+        <v>3.94</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="V33" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="W33" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AB33" t="n">
         <v>2.64</v>
       </c>
-      <c r="O33" t="n">
-        <v>3</v>
-      </c>
-      <c r="P33" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R33" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="S33" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="T33" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U33" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V33" t="n">
-        <v>6.45</v>
-      </c>
-      <c r="W33" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X33" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y33" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z33" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="AA33" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>2</v>
-      </c>
       <c r="AC33" t="n">
-        <v>2.9</v>
+        <v>2.12</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.4</v>
+        <v>1.74</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.59</v>
+        <v>1.53</v>
       </c>
       <c r="AF33" t="n">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="AG33" t="n">
-        <v>1.44</v>
+        <v>1.23</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.54</v>
+        <v>2.34</v>
       </c>
       <c r="AI33" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="M4" t="n">
         <v>3.1</v>
       </c>
       <c r="N4" t="n">
-        <v>1.73</v>
+        <v>1.65</v>
       </c>
       <c r="O4" t="n">
         <v>6.05</v>
@@ -936,10 +936,10 @@
         <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AA4" t="n">
         <v>2.62</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V10" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.62</v>
       </c>
-      <c r="M10" t="n">
-        <v>3.92</v>
-      </c>
-      <c r="N10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
-      <c r="U10" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" t="n">
-        <v>0</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>0</v>
-      </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="M11" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N11" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="O11" t="n">
         <v>2.05</v>
       </c>
-      <c r="M11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="S11" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V11" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="Z11" t="n">
         <v>2.6</v>
       </c>
-      <c r="P11" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S11" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T11" t="n">
+      <c r="AA11" t="n">
         <v>2.35</v>
       </c>
-      <c r="U11" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V11" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AB11" t="n">
-        <v>2</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.9</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.33</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.62</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.7</v>
+        <v>2.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.47</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.54</v>
+        <v>3.92</v>
       </c>
       <c r="N12" t="n">
-        <v>7.32</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
         <v>1.44</v>
       </c>
-      <c r="S12" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="V12" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.34</v>
-      </c>
       <c r="AB12" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1968,49 +1968,49 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="N13" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="P13" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="R13" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="S13" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="T13" t="n">
         <v>4.05</v>
       </c>
       <c r="U13" t="n">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="V13" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="W13" t="n">
         <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="AA13" t="n">
         <v>2.88</v>
@@ -2028,7 +2028,7 @@
         <v>2.3</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AG13" t="n">
         <v>1.44</v>
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2206,73 +2206,73 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.7</v>
+        <v>1.58</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.98</v>
       </c>
       <c r="N15" t="n">
-        <v>4.6</v>
+        <v>5.37</v>
       </c>
       <c r="O15" t="n">
         <v>2.15</v>
       </c>
       <c r="P15" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.8</v>
+        <v>5.57</v>
       </c>
       <c r="R15" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S15" t="n">
-        <v>2.94</v>
+        <v>2.81</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.81</v>
       </c>
       <c r="U15" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="V15" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.54</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.8</v>
+        <v>1.89</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.98</v>
+        <v>1.88</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.83</v>
+        <v>3.65</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.25</v>
+        <v>1.14</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,37 +2325,37 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.16</v>
+        <v>1.86</v>
       </c>
       <c r="M16" t="n">
-        <v>3.4</v>
+        <v>3.69</v>
       </c>
       <c r="N16" t="n">
-        <v>3.1</v>
+        <v>3.93</v>
       </c>
       <c r="O16" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="P16" t="n">
-        <v>2.15</v>
+        <v>2.29</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="R16" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S16" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="U16" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="V16" t="n">
-        <v>7.5</v>
+        <v>6.65</v>
       </c>
       <c r="W16" t="n">
         <v>1.05</v>
@@ -2364,34 +2364,34 @@
         <v>1.05</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.18</v>
+        <v>3.38</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="AB16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE16" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC16" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF16" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>1.86</v>
+        <v>2.8</v>
       </c>
       <c r="M17" t="n">
-        <v>3.69</v>
+        <v>2.97</v>
       </c>
       <c r="N17" t="n">
-        <v>3.93</v>
+        <v>2.69</v>
       </c>
       <c r="O17" t="n">
-        <v>2.51</v>
+        <v>3.4</v>
       </c>
       <c r="P17" t="n">
-        <v>2.29</v>
+        <v>1.88</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="R17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="V17" t="n">
+        <v>10</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AG17" t="n">
         <v>1.36</v>
       </c>
-      <c r="S17" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="V17" t="n">
-        <v>6.65</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.29</v>
-      </c>
       <c r="AH17" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.8</v>
+        <v>2.35</v>
       </c>
       <c r="M18" t="n">
-        <v>2.97</v>
+        <v>3.47</v>
       </c>
       <c r="N18" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="O18" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="M19" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N19" t="n">
-        <v>1.58</v>
+        <v>2.45</v>
       </c>
       <c r="O19" t="n">
-        <v>6</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="R19" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S19" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="T19" t="n">
-        <v>2.7</v>
+        <v>2.99</v>
       </c>
       <c r="U19" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V19" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AH19" t="n">
         <v>1.41</v>
-      </c>
-      <c r="V19" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W19" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X19" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>1.12</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2797,77 +2797,77 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L20" t="n">
-        <v>2.35</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.47</v>
+        <v>3.2</v>
       </c>
       <c r="N20" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,34 +2920,34 @@
         </is>
       </c>
       <c r="L21" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="M21" t="n">
+        <v>4</v>
+      </c>
+      <c r="N21" t="n">
         <v>1.58</v>
       </c>
-      <c r="M21" t="n">
-        <v>3.98</v>
-      </c>
-      <c r="N21" t="n">
-        <v>5.37</v>
-      </c>
       <c r="O21" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="P21" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.57</v>
+        <v>2.05</v>
       </c>
       <c r="R21" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.81</v>
+        <v>2.89</v>
       </c>
       <c r="T21" t="n">
-        <v>2.81</v>
+        <v>2.7</v>
       </c>
       <c r="U21" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="V21" t="n">
         <v>6.5</v>
@@ -2956,37 +2956,37 @@
         <v>1.06</v>
       </c>
       <c r="X21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.65</v>
+        <v>3.1</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.85</v>
+        <v>1.94</v>
       </c>
       <c r="AF21" t="n">
         <v>1.85</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH21" t="n">
-        <v>2.15</v>
+        <v>1.12</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3003,7 +3003,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,52 +3039,52 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="M22" t="n">
         <v>3.25</v>
       </c>
       <c r="N22" t="n">
-        <v>2.45</v>
+        <v>2.51</v>
       </c>
       <c r="O22" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="P22" t="n">
-        <v>2.1</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="R22" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S22" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="T22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="V22" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z22" t="n">
         <v>2.99</v>
       </c>
-      <c r="U22" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="V22" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="W22" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X22" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y22" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z22" t="n">
-        <v>3.34</v>
-      </c>
       <c r="AA22" t="n">
-        <v>2.04</v>
+        <v>2.17</v>
       </c>
       <c r="AB22" t="n">
         <v>1.75</v>
@@ -3093,16 +3093,16 @@
         <v>3.6</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.53</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
         <v>1.41</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,58 +3158,58 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.69</v>
+        <v>2.16</v>
       </c>
       <c r="M23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N23" t="n">
-        <v>2.51</v>
+        <v>3.1</v>
       </c>
       <c r="O23" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.12</v>
+        <v>3.6</v>
       </c>
       <c r="R23" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S23" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T23" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="U23" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="V23" t="n">
-        <v>6.5</v>
+        <v>7.5</v>
       </c>
       <c r="W23" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X23" t="n">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="Y23" t="n">
         <v>1.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>2.99</v>
+        <v>3.18</v>
       </c>
       <c r="AA23" t="n">
-        <v>2.17</v>
+        <v>1.99</v>
       </c>
       <c r="AB23" t="n">
         <v>1.75</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.6</v>
+        <v>3.38</v>
       </c>
       <c r="AD23" t="n">
         <v>1.24</v>
@@ -3218,13 +3218,13 @@
         <v>1.8</v>
       </c>
       <c r="AF23" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG23" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.41</v>
+        <v>1.67</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>3.4</v>
+        <v>1.7</v>
       </c>
       <c r="M25" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="N25" t="n">
-        <v>2.2</v>
+        <v>4.6</v>
       </c>
       <c r="O25" t="n">
-        <v>3.52</v>
+        <v>2.15</v>
       </c>
       <c r="P25" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="V25" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="W25" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AB25" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q25" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R25" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S25" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T25" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U25" t="n">
+      <c r="AC25" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD25" t="n">
         <v>1.33</v>
       </c>
-      <c r="V25" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W25" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X25" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y25" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z25" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA25" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AB25" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AC25" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="AD25" t="n">
-        <v>1.22</v>
-      </c>
       <c r="AE25" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,70 +3515,70 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.45</v>
+        <v>2.65</v>
       </c>
       <c r="M26" t="n">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="N26" t="n">
-        <v>2.75</v>
+        <v>2.6</v>
       </c>
       <c r="O26" t="n">
-        <v>3</v>
+        <v>3.28</v>
       </c>
       <c r="P26" t="n">
-        <v>2.21</v>
+        <v>2.14</v>
       </c>
       <c r="Q26" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R26" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="S26" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="T26" t="n">
-        <v>2.43</v>
+        <v>2.81</v>
       </c>
       <c r="U26" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>6.15</v>
+        <v>7.2</v>
       </c>
       <c r="W26" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="X26" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="Z26" t="n">
-        <v>4.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA26" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AB26" t="n">
-        <v>2.12</v>
+        <v>1.77</v>
       </c>
       <c r="AC26" t="n">
-        <v>2.72</v>
+        <v>3.2</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.43</v>
+        <v>1.29</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.25</v>
+        <v>2.05</v>
       </c>
       <c r="AG26" t="n">
-        <v>1.41</v>
+        <v>1.3</v>
       </c>
       <c r="AH26" t="n">
         <v>1.5</v>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="M27" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N27" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O27" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="P27" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R27" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T27" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V27" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W27" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X27" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z27" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA27" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE27" t="n">
         <v>1.6</v>
       </c>
-      <c r="AB27" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD27" t="n">
+      <c r="AF27" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH27" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>2.65</v>
+        <v>1.27</v>
       </c>
       <c r="M28" t="n">
-        <v>3.4</v>
+        <v>6.1</v>
       </c>
       <c r="N28" t="n">
-        <v>2.6</v>
+        <v>8.66</v>
       </c>
       <c r="O28" t="n">
-        <v>3.28</v>
+        <v>1.65</v>
       </c>
       <c r="P28" t="n">
-        <v>2.14</v>
+        <v>3</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.2</v>
+        <v>6.5</v>
       </c>
       <c r="R28" t="n">
-        <v>1.38</v>
+        <v>1.19</v>
       </c>
       <c r="S28" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U28" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="V28" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="W28" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB28" t="n">
         <v>2.98</v>
       </c>
-      <c r="T28" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U28" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V28" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="W28" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X28" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AC28" t="n">
-        <v>3.2</v>
+        <v>2.02</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.29</v>
+        <v>1.84</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.7</v>
+        <v>1.66</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AH28" t="n">
-        <v>1.5</v>
+        <v>3.35</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="M29" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>1.88</v>
+        <v>3.13</v>
       </c>
       <c r="O29" t="n">
-        <v>4</v>
+        <v>2.79</v>
       </c>
       <c r="P29" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.43</v>
+        <v>3.1</v>
       </c>
       <c r="R29" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="S29" t="n">
-        <v>2.89</v>
+        <v>3.08</v>
       </c>
       <c r="T29" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="V29" t="n">
-        <v>6.75</v>
+        <v>7</v>
       </c>
       <c r="W29" t="n">
-        <v>1.08</v>
+        <v>1.05</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="AA29" t="n">
         <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.65</v>
+        <v>3.25</v>
       </c>
       <c r="AD29" t="n">
         <v>1.3</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="AF29" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AG29" t="n">
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.25</v>
+        <v>1.57</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3994,67 +3994,67 @@
         <v>2.45</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="N30" t="n">
         <v>2.75</v>
       </c>
       <c r="O30" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="P30" t="n">
-        <v>2.17</v>
+        <v>2.21</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="R30" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="S30" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="T30" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="U30" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="V30" t="n">
-        <v>5.8</v>
+        <v>6.15</v>
       </c>
       <c r="W30" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="X30" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="Z30" t="n">
-        <v>4.25</v>
+        <v>4.1</v>
       </c>
       <c r="AA30" t="n">
         <v>1.79</v>
       </c>
       <c r="AB30" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.83</v>
+        <v>2.72</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="AE30" t="n">
         <v>1.6</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.3</v>
+        <v>1.41</v>
       </c>
       <c r="AH30" t="n">
         <v>1.5</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>1.27</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>6.1</v>
+        <v>3.56</v>
       </c>
       <c r="N31" t="n">
-        <v>8.66</v>
+        <v>1.88</v>
       </c>
       <c r="O31" t="n">
-        <v>1.65</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>6.5</v>
+        <v>2.43</v>
       </c>
       <c r="R31" t="n">
-        <v>1.19</v>
+        <v>1.41</v>
       </c>
       <c r="S31" t="n">
-        <v>4.4</v>
+        <v>2.89</v>
       </c>
       <c r="T31" t="n">
-        <v>1.99</v>
+        <v>2.81</v>
       </c>
       <c r="U31" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="V31" t="n">
-        <v>3.8</v>
+        <v>6.75</v>
       </c>
       <c r="W31" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.1</v>
+        <v>1.29</v>
       </c>
       <c r="Z31" t="n">
-        <v>6.5</v>
+        <v>3.45</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.98</v>
+        <v>1.89</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.02</v>
+        <v>3.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.84</v>
+        <v>1.3</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.66</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH31" t="n">
-        <v>3.35</v>
+        <v>1.25</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.18</v>
+        <v>3.9</v>
       </c>
       <c r="M32" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="N32" t="n">
-        <v>3.13</v>
+        <v>1.83</v>
       </c>
       <c r="O32" t="n">
-        <v>2.79</v>
+        <v>4.1</v>
       </c>
       <c r="P32" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="Q32" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q32" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R32" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="S32" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="T32" t="n">
-        <v>2.79</v>
+        <v>2.36</v>
       </c>
       <c r="U32" t="n">
-        <v>1.42</v>
+        <v>1.61</v>
       </c>
       <c r="V32" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="W32" t="n">
-        <v>1.05</v>
+        <v>1.13</v>
       </c>
       <c r="X32" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="Z32" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
       <c r="AA32" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.85</v>
+        <v>2.33</v>
       </c>
       <c r="AC32" t="n">
-        <v>3.25</v>
+        <v>2.49</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG32" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Fasil Ketema</t>
+          <t>Welayta Dicha</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Hadiya Hosaena</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>3.35</v>
       </c>
       <c r="M2" t="n">
-        <v>2.95</v>
+        <v>2.85</v>
       </c>
       <c r="N2" t="n">
-        <v>3.65</v>
+        <v>2.17</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -698,10 +698,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Welayta Dicha</t>
+          <t>Fasil Ketema</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Hadiya Hosaena</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>3.35</v>
+        <v>2</v>
       </c>
       <c r="M3" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="N3" t="n">
-        <v>2.17</v>
+        <v>3.65</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -980,7 +980,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Jordan Jordanian Pro League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -990,12 +990,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Al Wihdat</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Al Buqa'a</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1016,73 +1016,73 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>7.5</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46042.5</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jordan Jordanian Pro League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Wihdat</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Buqa'a</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M11" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="N11" t="n">
-        <v>6.7</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="M12" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N12" t="n">
-        <v>4.33</v>
+        <v>6.7</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB12" t="n">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2170,7 +2170,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2180,12 +2180,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2202,77 +2202,77 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.58</v>
+        <v>2.35</v>
       </c>
       <c r="M15" t="n">
-        <v>3.98</v>
+        <v>3.47</v>
       </c>
       <c r="N15" t="n">
-        <v>5.37</v>
+        <v>2.7</v>
       </c>
       <c r="O15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.57</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
       <c r="M17" t="n">
-        <v>2.97</v>
+        <v>3.2</v>
       </c>
       <c r="N17" t="n">
-        <v>2.69</v>
+        <v>2.2</v>
       </c>
       <c r="O17" t="n">
-        <v>3.4</v>
+        <v>3.52</v>
       </c>
       <c r="P17" t="n">
-        <v>1.88</v>
+        <v>1.98</v>
       </c>
       <c r="Q17" t="n">
-        <v>3.35</v>
+        <v>2.78</v>
       </c>
       <c r="R17" t="n">
-        <v>1.54</v>
+        <v>1.43</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="T17" t="n">
-        <v>3.55</v>
+        <v>3.04</v>
       </c>
       <c r="U17" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="V17" t="n">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="W17" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X17" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.44</v>
+        <v>1.33</v>
       </c>
       <c r="Z17" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AA17" t="n">
-        <v>2.65</v>
+        <v>2.15</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.8</v>
+        <v>3.8</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2527,7 +2527,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2559,77 +2559,77 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.35</v>
+        <v>2.69</v>
       </c>
       <c r="M18" t="n">
-        <v>3.47</v>
+        <v>3.25</v>
       </c>
       <c r="N18" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="M19" t="n">
-        <v>3.25</v>
+        <v>2.97</v>
       </c>
       <c r="N19" t="n">
-        <v>2.45</v>
+        <v>2.69</v>
       </c>
       <c r="O19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="Q19" t="n">
         <v>3.35</v>
       </c>
-      <c r="P19" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R19" t="n">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="S19" t="n">
-        <v>2.8</v>
+        <v>2.4</v>
       </c>
       <c r="T19" t="n">
-        <v>2.99</v>
+        <v>3.55</v>
       </c>
       <c r="U19" t="n">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="V19" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="W19" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X19" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.34</v>
+        <v>2.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.04</v>
+        <v>2.65</v>
       </c>
       <c r="AB19" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AF19" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF19" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AG19" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>3.4</v>
+        <v>1.58</v>
       </c>
       <c r="M20" t="n">
-        <v>3.2</v>
+        <v>3.98</v>
       </c>
       <c r="N20" t="n">
+        <v>5.37</v>
+      </c>
+      <c r="O20" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="P20" t="n">
         <v>2.2</v>
       </c>
-      <c r="O20" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.98</v>
-      </c>
       <c r="Q20" t="n">
-        <v>2.78</v>
+        <v>5.57</v>
       </c>
       <c r="R20" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="S20" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="T20" t="n">
-        <v>3.04</v>
+        <v>2.81</v>
       </c>
       <c r="U20" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="V20" t="n">
-        <v>7.4</v>
+        <v>6.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X20" t="n">
         <v>1.06</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="Z20" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="AA20" t="n">
-        <v>2.15</v>
+        <v>1.89</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.7</v>
+        <v>1.88</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="AE20" t="n">
         <v>1.85</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.3</v>
+        <v>1.14</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="M21" t="n">
-        <v>4</v>
+        <v>3.14</v>
       </c>
       <c r="N21" t="n">
-        <v>1.58</v>
+        <v>3.2</v>
       </c>
       <c r="O21" t="n">
-        <v>6</v>
+        <v>2.8</v>
       </c>
       <c r="P21" t="n">
-        <v>2.3</v>
+        <v>1.93</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.05</v>
+        <v>3.9</v>
       </c>
       <c r="R21" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="V21" t="n">
+        <v>8</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y21" t="n">
         <v>1.36</v>
       </c>
-      <c r="S21" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T21" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="U21" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="V21" t="n">
-        <v>6.5</v>
-      </c>
-      <c r="W21" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X21" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y21" t="n">
-        <v>1.24</v>
-      </c>
       <c r="Z21" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.83</v>
+        <v>2.25</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.85</v>
+        <v>1.62</v>
       </c>
       <c r="AC21" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG21" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>2.69</v>
+        <v>1.7</v>
       </c>
       <c r="M22" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N22" t="n">
-        <v>2.51</v>
+        <v>4.6</v>
       </c>
       <c r="O22" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="P22" t="n">
-        <v>2.02</v>
+        <v>2.3</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.12</v>
+        <v>4.8</v>
       </c>
       <c r="R22" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.43</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.35</v>
-      </c>
       <c r="V22" t="n">
-        <v>6.5</v>
+        <v>6.25</v>
       </c>
       <c r="W22" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X22" t="n">
-        <v>1.07</v>
+        <v>1.03</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="Z22" t="n">
-        <v>2.99</v>
+        <v>3.54</v>
       </c>
       <c r="AA22" t="n">
-        <v>2.17</v>
+        <v>1.8</v>
       </c>
       <c r="AB22" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.8</v>
-      </c>
       <c r="AF22" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,73 +3277,73 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="M24" t="n">
-        <v>3.14</v>
+        <v>3.13</v>
       </c>
       <c r="N24" t="n">
-        <v>3.2</v>
+        <v>2.29</v>
       </c>
       <c r="O24" t="n">
-        <v>2.8</v>
+        <v>3.35</v>
       </c>
       <c r="P24" t="n">
-        <v>1.93</v>
+        <v>2.01</v>
       </c>
       <c r="Q24" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="R24" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="T24" t="n">
-        <v>3.2</v>
+        <v>3.03</v>
       </c>
       <c r="U24" t="n">
         <v>1.34</v>
       </c>
       <c r="V24" t="n">
-        <v>8</v>
+        <v>6.1</v>
       </c>
       <c r="W24" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X24" t="n">
         <v>1.01</v>
       </c>
-      <c r="X24" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y24" t="n">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.72</v>
+        <v>3.08</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.25</v>
+        <v>1.94</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.62</v>
+        <v>1.76</v>
       </c>
       <c r="AC24" t="n">
-        <v>4.4</v>
+        <v>3.64</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE24" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AF24" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.7</v>
+        <v>5.5</v>
       </c>
       <c r="M25" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="N25" t="n">
-        <v>4.6</v>
+        <v>1.58</v>
       </c>
       <c r="O25" t="n">
-        <v>2.15</v>
+        <v>6</v>
       </c>
       <c r="P25" t="n">
         <v>2.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.8</v>
+        <v>2.05</v>
       </c>
       <c r="R25" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S25" t="n">
-        <v>2.94</v>
+        <v>2.89</v>
       </c>
       <c r="T25" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="U25" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="V25" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W25" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="X25" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.54</v>
+        <v>3.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AC25" t="n">
-        <v>2.83</v>
+        <v>3.1</v>
       </c>
       <c r="AD25" t="n">
         <v>1.33</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.75</v>
+        <v>1.94</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AG25" t="n">
         <v>1.25</v>
       </c>
       <c r="AH25" t="n">
-        <v>2.1</v>
+        <v>1.12</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.65</v>
+        <v>4</v>
       </c>
       <c r="M26" t="n">
-        <v>3.4</v>
+        <v>3.56</v>
       </c>
       <c r="N26" t="n">
-        <v>2.6</v>
+        <v>1.88</v>
       </c>
       <c r="O26" t="n">
-        <v>3.28</v>
+        <v>4</v>
       </c>
       <c r="P26" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.2</v>
+        <v>2.43</v>
       </c>
       <c r="R26" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S26" t="n">
-        <v>2.98</v>
+        <v>2.89</v>
       </c>
       <c r="T26" t="n">
         <v>2.81</v>
@@ -3545,43 +3545,43 @@
         <v>1.43</v>
       </c>
       <c r="V26" t="n">
-        <v>7.2</v>
+        <v>6.75</v>
       </c>
       <c r="W26" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="X26" t="n">
         <v>1.05</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="Z26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="AA26" t="n">
         <v>1.93</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.77</v>
+        <v>1.89</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="AD26" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="AF26" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AG26" t="n">
         <v>1.3</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.5</v>
+        <v>1.25</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Europe UEFA Champions League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3634,73 +3634,73 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.45</v>
+        <v>2.18</v>
       </c>
       <c r="M27" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N27" t="n">
+        <v>3.13</v>
+      </c>
+      <c r="O27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="V27" t="n">
+        <v>7</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="Z27" t="n">
         <v>3.5</v>
       </c>
-      <c r="N27" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="O27" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="P27" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="Q27" t="n">
+      <c r="AA27" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AC27" t="n">
         <v>3.25</v>
       </c>
-      <c r="R27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S27" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T27" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V27" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AD27" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="AE27" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="AF27" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG27" t="n">
         <v>1.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AI27" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3836,7 +3836,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Europe UEFA Champions League</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,61 +3872,61 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.18</v>
+        <v>2.65</v>
       </c>
       <c r="M29" t="n">
         <v>3.4</v>
       </c>
       <c r="N29" t="n">
-        <v>3.13</v>
+        <v>2.6</v>
       </c>
       <c r="O29" t="n">
-        <v>2.79</v>
+        <v>3.28</v>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>2.14</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="S29" t="n">
-        <v>3.08</v>
+        <v>2.98</v>
       </c>
       <c r="T29" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="U29" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="V29" t="n">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="W29" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X29" t="n">
         <v>1.05</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA29" t="n">
         <v>1.93</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.85</v>
+        <v>1.77</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE29" t="n">
         <v>1.7</v>
@@ -3938,7 +3938,7 @@
         <v>1.3</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M31" t="n">
-        <v>3.56</v>
+        <v>3.9</v>
       </c>
       <c r="N31" t="n">
-        <v>1.88</v>
+        <v>1.83</v>
       </c>
       <c r="O31" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="P31" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.43</v>
+        <v>2.2</v>
       </c>
       <c r="R31" t="n">
-        <v>1.41</v>
+        <v>1.28</v>
       </c>
       <c r="S31" t="n">
-        <v>2.89</v>
+        <v>3.5</v>
       </c>
       <c r="T31" t="n">
-        <v>2.81</v>
+        <v>2.36</v>
       </c>
       <c r="U31" t="n">
-        <v>1.43</v>
+        <v>1.61</v>
       </c>
       <c r="V31" t="n">
-        <v>6.75</v>
+        <v>5.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.08</v>
+        <v>1.13</v>
       </c>
       <c r="X31" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="Z31" t="n">
-        <v>3.45</v>
+        <v>4.6</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.93</v>
+        <v>1.6</v>
       </c>
       <c r="AB31" t="n">
-        <v>1.89</v>
+        <v>2.33</v>
       </c>
       <c r="AC31" t="n">
-        <v>3.65</v>
+        <v>2.49</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.75</v>
+        <v>1.53</v>
       </c>
       <c r="AF31" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AG31" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,73 +4229,73 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>3.9</v>
+        <v>2.45</v>
       </c>
       <c r="M32" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="N32" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O32" t="n">
-        <v>4.1</v>
+        <v>3.14</v>
       </c>
       <c r="P32" t="n">
-        <v>2.45</v>
+        <v>2.17</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="R32" t="n">
-        <v>1.28</v>
+        <v>1.36</v>
       </c>
       <c r="S32" t="n">
-        <v>3.5</v>
+        <v>3.12</v>
       </c>
       <c r="T32" t="n">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="U32" t="n">
-        <v>1.61</v>
+        <v>1.49</v>
       </c>
       <c r="V32" t="n">
-        <v>5.5</v>
+        <v>5.8</v>
       </c>
       <c r="W32" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X32" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y32" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Z32" t="n">
-        <v>4.6</v>
+        <v>4.25</v>
       </c>
       <c r="AA32" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE32" t="n">
         <v>1.6</v>
       </c>
-      <c r="AB32" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="AD32" t="n">
+      <c r="AF32" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH32" t="n">
         <v>1.5</v>
-      </c>
-      <c r="AE32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AF32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AG32" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH32" t="n">
-        <v>1.22</v>
       </c>
       <c r="AI32" s="3" t="n">
         <v>46042.70833333334</v>

--- a/jogos_2026-01-20.xlsx
+++ b/jogos_2026-01-20.xlsx
@@ -668,34 +668,34 @@
         <v>2.17</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y2" t="n">
         <v>1.6</v>
@@ -704,28 +704,28 @@
         <v>2.2</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>6.05</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46042.375</v>
@@ -787,34 +787,34 @@
         <v>3.65</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>4.74</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.82</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y3" t="n">
         <v>1.55</v>
@@ -823,28 +823,28 @@
         <v>2.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.65</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46042.375</v>
@@ -918,7 +918,7 @@
         <v>1.56</v>
       </c>
       <c r="S4" t="n">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="T4" t="n">
         <v>3.58</v>
@@ -942,10 +942,10 @@
         <v>2.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="AC4" t="n">
         <v>5</v>
@@ -954,10 +954,10 @@
         <v>1.1</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="AF4" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="AG4" t="n">
         <v>1.27</v>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Mekelle Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rijeka</t>
+          <t>Mebrat Hayl</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.25</v>
+        <v>2.85</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3</v>
+        <v>2.95</v>
       </c>
       <c r="N6" t="n">
-        <v>2.02</v>
+        <v>2.35</v>
       </c>
       <c r="O6" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="P6" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.5</v>
+        <v>3.18</v>
       </c>
       <c r="R6" t="n">
-        <v>1.36</v>
+        <v>1.49</v>
       </c>
       <c r="S6" t="n">
-        <v>2.5</v>
+        <v>2.34</v>
       </c>
       <c r="T6" t="n">
-        <v>2.65</v>
+        <v>3.42</v>
       </c>
       <c r="U6" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="V6" t="n">
-        <v>7.5</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X6" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.3</v>
+        <v>1.46</v>
       </c>
       <c r="Z6" t="n">
-        <v>3</v>
+        <v>2.48</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
       <c r="AB6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.7</v>
       </c>
-      <c r="AC6" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.89</v>
-      </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46042.5</v>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Mekelle Kenema</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mebrat Hayl</t>
+          <t>Rijeka</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.85</v>
+        <v>3.25</v>
       </c>
       <c r="M7" t="n">
-        <v>2.95</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2.02</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.4</v>
+        <v>2.1</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46042.5</v>
@@ -1492,19 +1492,19 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>4.85</v>
+        <v>4.7</v>
       </c>
       <c r="M9" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="N9" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="O9" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="P9" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q9" t="n">
         <v>2.1</v>
@@ -1513,52 +1513,52 @@
         <v>1.29</v>
       </c>
       <c r="S9" t="n">
-        <v>3.94</v>
+        <v>3.3</v>
       </c>
       <c r="T9" t="n">
-        <v>2.49</v>
+        <v>2.3</v>
       </c>
       <c r="U9" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V9" t="n">
         <v>5.4</v>
       </c>
       <c r="W9" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X9" t="n">
         <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.62</v>
+        <v>1.53</v>
       </c>
       <c r="AB9" t="n">
-        <v>2.25</v>
+        <v>2.33</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.38</v>
+        <v>2.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="AG9" t="n">
         <v>1.2</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" s="3" t="n">
         <v>46042.52083333334</v>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1585,12 +1585,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Fateh</t>
+          <t>Sekhukhune United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Stellenbosch</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1611,73 +1611,73 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.4</v>
       </c>
-      <c r="N10" t="n">
-        <v>3.5</v>
-      </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
       <c r="P10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="S10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="V10" t="n">
+        <v>9</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE10" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="AF10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AG10" t="n">
         <v>1.41</v>
       </c>
-      <c r="V10" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AH10" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AI10" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>South Africa Premier Soccer League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1704,12 +1704,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kaizer Chiefs</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Al Khaleej</t>
+          <t>Golden Arrows</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1730,73 +1730,73 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="M11" t="n">
-        <v>3.92</v>
+        <v>3.5</v>
       </c>
       <c r="N11" t="n">
-        <v>4.33</v>
+        <v>6.7</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>7.58</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>9.1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.44</v>
+        <v>2.35</v>
       </c>
       <c r="AB11" t="n">
-        <v>2.62</v>
+        <v>1.53</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AI11" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1823,12 +1823,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaizer Chiefs</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Golden Arrows</t>
+          <t>Al Khaleej</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1849,73 +1849,73 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="M12" t="n">
-        <v>3.5</v>
+        <v>3.92</v>
       </c>
       <c r="N12" t="n">
-        <v>6.7</v>
+        <v>4.33</v>
       </c>
       <c r="O12" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>7.58</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>9.1</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.35</v>
+        <v>1.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.53</v>
+        <v>2.62</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="3" t="n">
         <v>46042.60416666666</v>
@@ -1932,7 +1932,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>South Africa Premier Soccer League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sekhukhune United</t>
+          <t>Al Fateh</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Stellenbosch</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1968,73 +1968,73 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="M13" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="N13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q13" t="n">
         <v>3.4</v>
       </c>
-      <c r="O13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="P13" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>4.1</v>
-      </c>
       <c r="R13" t="n">
-        <v>1.65</v>
+        <v>1.35</v>
       </c>
       <c r="S13" t="n">
-        <v>2.2</v>
+        <v>2.82</v>
       </c>
       <c r="T13" t="n">
-        <v>4.05</v>
+        <v>2.35</v>
       </c>
       <c r="U13" t="n">
-        <v>1.16</v>
+        <v>1.41</v>
       </c>
       <c r="V13" t="n">
-        <v>9</v>
+        <v>6.25</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
-        <v>1.13</v>
+        <v>1.04</v>
       </c>
       <c r="Y13" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.62</v>
       </c>
-      <c r="Z13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>2.3</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.44</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" s="3" t="n">
         <v>46042.60416666666</v>
@@ -2087,37 +2087,37 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>6.3</v>
+        <v>5.9</v>
       </c>
       <c r="M14" t="n">
-        <v>6.06</v>
+        <v>5.6</v>
       </c>
       <c r="N14" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="O14" t="n">
-        <v>5.5</v>
+        <v>4.94</v>
       </c>
       <c r="P14" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="R14" t="n">
         <v>1.17</v>
       </c>
       <c r="S14" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="T14" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="U14" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="V14" t="n">
-        <v>4</v>
+        <v>3.75</v>
       </c>
       <c r="W14" t="n">
         <v>1.25</v>
@@ -2126,34 +2126,34 @@
         <v>1.01</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="Z14" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AB14" t="n">
-        <v>3.1</v>
+        <v>3.21</v>
       </c>
       <c r="AC14" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="AD14" t="n">
         <v>1.87</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="AG14" t="n">
-        <v>2.9</v>
+        <v>1.14</v>
       </c>
       <c r="AH14" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AI14" s="3" t="n">
         <v>46042.61458333334</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>2.35</v>
+        <v>2.45</v>
       </c>
       <c r="M15" t="n">
-        <v>3.47</v>
+        <v>3.65</v>
       </c>
       <c r="N15" t="n">
         <v>2.7</v>
@@ -2299,12 +2299,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2325,22 +2325,22 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>1.86</v>
+        <v>5.4</v>
       </c>
       <c r="M16" t="n">
-        <v>3.69</v>
+        <v>3.83</v>
       </c>
       <c r="N16" t="n">
-        <v>3.93</v>
+        <v>1.61</v>
       </c>
       <c r="O16" t="n">
-        <v>2.51</v>
+        <v>6.25</v>
       </c>
       <c r="P16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.2</v>
+        <v>2.05</v>
       </c>
       <c r="R16" t="n">
         <v>1.36</v>
@@ -2349,49 +2349,49 @@
         <v>2.89</v>
       </c>
       <c r="T16" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="U16" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="V16" t="n">
-        <v>6.65</v>
+        <v>6.15</v>
       </c>
       <c r="W16" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X16" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AC16" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.75</v>
+        <v>1.96</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.96</v>
+        <v>1.82</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.29</v>
+        <v>2.51</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.85</v>
+        <v>1.11</v>
       </c>
       <c r="AI16" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2408,7 +2408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2418,12 +2418,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Stevenage</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Bristol City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2444,73 +2444,73 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>3.4</v>
+        <v>1.67</v>
       </c>
       <c r="M17" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="N17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="P17" t="n">
         <v>2.2</v>
       </c>
-      <c r="O17" t="n">
-        <v>3.52</v>
-      </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA17" t="n">
         <v>1.98</v>
       </c>
-      <c r="Q17" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="R17" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S17" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="V17" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X17" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.15</v>
-      </c>
       <c r="AB17" t="n">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="AC17" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AE17" t="n">
         <v>1.85</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AH17" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
       <c r="AI17" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2537,12 +2537,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2563,73 +2563,73 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>2.69</v>
+        <v>1.66</v>
       </c>
       <c r="M18" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="N18" t="n">
-        <v>2.51</v>
+        <v>4.9</v>
       </c>
       <c r="O18" t="n">
-        <v>3.1</v>
+        <v>2.15</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="Q18" t="n">
-        <v>3.12</v>
+        <v>5.25</v>
       </c>
       <c r="R18" t="n">
-        <v>1.43</v>
+        <v>1.35</v>
       </c>
       <c r="S18" t="n">
-        <v>2.62</v>
+        <v>2.94</v>
       </c>
       <c r="T18" t="n">
-        <v>2.94</v>
+        <v>2.59</v>
       </c>
       <c r="U18" t="n">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>6.5</v>
+        <v>5.95</v>
       </c>
       <c r="W18" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X18" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="Z18" t="n">
-        <v>2.99</v>
+        <v>3.88</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.17</v>
+        <v>1.82</v>
       </c>
       <c r="AB18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AE18" t="n">
         <v>1.75</v>
       </c>
-      <c r="AC18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AD18" t="n">
+      <c r="AF18" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG18" t="n">
         <v>1.24</v>
       </c>
-      <c r="AE18" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AF18" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>1.33</v>
-      </c>
       <c r="AH18" t="n">
-        <v>1.41</v>
+        <v>2.1</v>
       </c>
       <c r="AI18" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2646,7 +2646,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2656,12 +2656,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Derby County</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2682,73 +2682,73 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="M19" t="n">
-        <v>2.97</v>
+        <v>3.13</v>
       </c>
       <c r="N19" t="n">
-        <v>2.69</v>
+        <v>2.29</v>
       </c>
       <c r="O19" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="P19" t="n">
-        <v>1.88</v>
+        <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.35</v>
+        <v>3</v>
       </c>
       <c r="R19" t="n">
-        <v>1.54</v>
+        <v>1.36</v>
       </c>
       <c r="S19" t="n">
-        <v>2.4</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>3.55</v>
+        <v>3.03</v>
       </c>
       <c r="U19" t="n">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>10</v>
+        <v>6.1</v>
       </c>
       <c r="W19" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X19" t="n">
         <v>1.01</v>
       </c>
-      <c r="X19" t="n">
-        <v>1.1</v>
-      </c>
       <c r="Y19" t="n">
-        <v>1.44</v>
+        <v>1.28</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.5</v>
+        <v>3.08</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.65</v>
+        <v>1.94</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.5</v>
+        <v>1.76</v>
       </c>
       <c r="AC19" t="n">
-        <v>4.8</v>
+        <v>3.64</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="AE19" t="n">
-        <v>1.98</v>
+        <v>1.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>1.75</v>
+        <v>2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AI19" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2775,12 +2775,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bristol City</t>
+          <t>Derby County</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2801,73 +2801,73 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>1.58</v>
+        <v>2.49</v>
       </c>
       <c r="M20" t="n">
-        <v>3.98</v>
+        <v>2.93</v>
       </c>
       <c r="N20" t="n">
-        <v>5.37</v>
+        <v>3.06</v>
       </c>
       <c r="O20" t="n">
-        <v>2.15</v>
+        <v>3.4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.2</v>
+        <v>1.89</v>
       </c>
       <c r="Q20" t="n">
-        <v>5.57</v>
+        <v>3.4</v>
       </c>
       <c r="R20" t="n">
-        <v>1.38</v>
+        <v>1.52</v>
       </c>
       <c r="S20" t="n">
-        <v>2.81</v>
+        <v>2.48</v>
       </c>
       <c r="T20" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="U20" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="V20" t="n">
-        <v>6.5</v>
+        <v>8.5</v>
       </c>
       <c r="W20" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="X20" t="n">
-        <v>1.06</v>
+        <v>1.1</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="Z20" t="n">
-        <v>3.3</v>
+        <v>2.4</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.89</v>
+        <v>2.38</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.88</v>
+        <v>1.54</v>
       </c>
       <c r="AC20" t="n">
-        <v>3.65</v>
+        <v>4.8</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.29</v>
+        <v>1.14</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AG20" t="n">
-        <v>1.14</v>
+        <v>1.36</v>
       </c>
       <c r="AH20" t="n">
-        <v>2.15</v>
+        <v>1.44</v>
       </c>
       <c r="AI20" s="3" t="n">
         <v>46042.69791666666</v>
@@ -2884,7 +2884,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2894,12 +2894,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Stevenage</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blackburn Rovers</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2920,73 +2920,73 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.25</v>
+        <v>3.28</v>
       </c>
       <c r="M21" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="N21" t="n">
-        <v>3.2</v>
+        <v>1.98</v>
       </c>
       <c r="O21" t="n">
-        <v>2.8</v>
+        <v>3.65</v>
       </c>
       <c r="P21" t="n">
-        <v>1.93</v>
+        <v>2.03</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>2.63</v>
       </c>
       <c r="R21" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="S21" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="T21" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="V21" t="n">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="W21" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X21" t="n">
-        <v>1.07</v>
+        <v>1.02</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="AA21" t="n">
-        <v>2.25</v>
+        <v>2.07</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.2</v>
+        <v>1.25</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AG21" t="n">
         <v>1.3</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.67</v>
+        <v>1.3</v>
       </c>
       <c r="AI21" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3013,12 +3013,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3039,73 +3039,73 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>1.7</v>
+        <v>3.16</v>
       </c>
       <c r="M22" t="n">
-        <v>3.8</v>
+        <v>3.16</v>
       </c>
       <c r="N22" t="n">
-        <v>4.6</v>
+        <v>2.29</v>
       </c>
       <c r="O22" t="n">
-        <v>2.15</v>
+        <v>3.43</v>
       </c>
       <c r="P22" t="n">
-        <v>2.3</v>
+        <v>2.02</v>
       </c>
       <c r="Q22" t="n">
-        <v>4.8</v>
+        <v>2.95</v>
       </c>
       <c r="R22" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
         <v>1.35</v>
       </c>
-      <c r="S22" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1.43</v>
-      </c>
       <c r="V22" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="W22" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X22" t="n">
         <v>1.07</v>
       </c>
-      <c r="X22" t="n">
-        <v>1.03</v>
-      </c>
       <c r="Y22" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>3.54</v>
+        <v>3.1</v>
       </c>
       <c r="AA22" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AE22" t="n">
         <v>1.8</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AC22" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AD22" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>1.75</v>
       </c>
       <c r="AF22" t="n">
         <v>1.95</v>
       </c>
       <c r="AG22" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH22" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="AI22" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3132,12 +3132,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Blackburn Rovers</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3158,73 +3158,73 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>2.16</v>
+        <v>2.44</v>
       </c>
       <c r="M23" t="n">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="N23" t="n">
-        <v>3.1</v>
+        <v>3.01</v>
       </c>
       <c r="O23" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="P23" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.6</v>
+        <v>3.95</v>
       </c>
       <c r="R23" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="S23" t="n">
-        <v>2.94</v>
+        <v>2.47</v>
       </c>
       <c r="T23" t="n">
-        <v>2.89</v>
+        <v>3.2</v>
       </c>
       <c r="U23" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="V23" t="n">
+        <v>9</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y23" t="n">
         <v>1.36</v>
       </c>
-      <c r="V23" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X23" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>1.3</v>
-      </c>
       <c r="Z23" t="n">
-        <v>3.18</v>
+        <v>2.88</v>
       </c>
       <c r="AA23" t="n">
-        <v>1.99</v>
+        <v>2.23</v>
       </c>
       <c r="AB23" t="n">
-        <v>1.75</v>
+        <v>1.58</v>
       </c>
       <c r="AC23" t="n">
-        <v>3.38</v>
+        <v>4.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="AE23" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AF23" t="n">
         <v>1.8</v>
       </c>
-      <c r="AF23" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AG23" t="n">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="AH23" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="AI23" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3277,61 +3277,61 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="M24" t="n">
-        <v>3.13</v>
+        <v>3.55</v>
       </c>
       <c r="N24" t="n">
-        <v>2.29</v>
+        <v>4.1</v>
       </c>
       <c r="O24" t="n">
-        <v>3.35</v>
+        <v>2.32</v>
       </c>
       <c r="P24" t="n">
-        <v>2.01</v>
+        <v>2.15</v>
       </c>
       <c r="Q24" t="n">
-        <v>3</v>
+        <v>4.63</v>
       </c>
       <c r="R24" t="n">
         <v>1.36</v>
       </c>
       <c r="S24" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T24" t="n">
-        <v>3.03</v>
+        <v>2.77</v>
       </c>
       <c r="U24" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="V24" t="n">
-        <v>6.1</v>
+        <v>6.65</v>
       </c>
       <c r="W24" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="X24" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="Z24" t="n">
-        <v>3.08</v>
+        <v>3.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.76</v>
+        <v>1.91</v>
       </c>
       <c r="AC24" t="n">
-        <v>3.64</v>
+        <v>3.2</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE24" t="n">
         <v>1.75</v>
@@ -3340,10 +3340,10 @@
         <v>2</v>
       </c>
       <c r="AG24" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="AI24" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3370,12 +3370,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3396,73 +3396,73 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>5.5</v>
+        <v>2.32</v>
       </c>
       <c r="M25" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="N25" t="n">
-        <v>1.58</v>
+        <v>3.03</v>
       </c>
       <c r="O25" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="P25" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.05</v>
+        <v>3.94</v>
       </c>
       <c r="R25" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S25" t="n">
-        <v>2.89</v>
+        <v>2.73</v>
       </c>
       <c r="T25" t="n">
-        <v>2.7</v>
+        <v>2.94</v>
       </c>
       <c r="U25" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="V25" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="W25" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="X25" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="Z25" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA25" t="n">
-        <v>1.83</v>
+        <v>2.03</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="AC25" t="n">
-        <v>3.1</v>
+        <v>3.47</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.94</v>
+        <v>1.8</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AG25" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="AH25" t="n">
-        <v>1.12</v>
+        <v>1.67</v>
       </c>
       <c r="AI25" s="3" t="n">
         <v>46042.69791666666</v>
@@ -3489,12 +3489,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>København</t>
+          <t>Olympiakos Piraeus</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3515,73 +3515,73 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>4</v>
+        <v>2.42</v>
       </c>
       <c r="M26" t="n">
-        <v>3.56</v>
+        <v>3.52</v>
       </c>
       <c r="N26" t="n">
-        <v>1.88</v>
+        <v>2.69</v>
       </c>
       <c r="O26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P26" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>3</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="V26" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AF26" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q26" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="R26" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S26" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="V26" t="n">
-        <v>6.75</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X26" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>2</v>
-      </c>
       <c r="AG26" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="AI26" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3634,61 +3634,61 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>2.18</v>
+        <v>2.4</v>
       </c>
       <c r="M27" t="n">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="N27" t="n">
-        <v>3.13</v>
+        <v>2.98</v>
       </c>
       <c r="O27" t="n">
-        <v>2.79</v>
+        <v>3</v>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="R27" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S27" t="n">
-        <v>3.08</v>
+        <v>2.85</v>
       </c>
       <c r="T27" t="n">
-        <v>2.79</v>
+        <v>2.77</v>
       </c>
       <c r="U27" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="V27" t="n">
-        <v>7</v>
+        <v>6.5</v>
       </c>
       <c r="W27" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X27" t="n">
         <v>1.05</v>
       </c>
       <c r="Y27" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="Z27" t="n">
         <v>3.5</v>
       </c>
       <c r="AA27" t="n">
-        <v>1.93</v>
+        <v>2.02</v>
       </c>
       <c r="AB27" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="AC27" t="n">
-        <v>3.25</v>
+        <v>3.12</v>
       </c>
       <c r="AD27" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AE27" t="n">
         <v>1.7</v>
@@ -3697,7 +3697,7 @@
         <v>2.05</v>
       </c>
       <c r="AG27" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="AH27" t="n">
         <v>1.57</v>
@@ -3727,12 +3727,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Monaco</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -3753,73 +3753,73 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>1.27</v>
+        <v>2.47</v>
       </c>
       <c r="M28" t="n">
-        <v>6.1</v>
+        <v>3.41</v>
       </c>
       <c r="N28" t="n">
-        <v>8.66</v>
+        <v>2.67</v>
       </c>
       <c r="O28" t="n">
-        <v>1.65</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
-        <v>3</v>
+        <v>2.25</v>
       </c>
       <c r="Q28" t="n">
-        <v>6.5</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="S28" t="n">
-        <v>4.4</v>
+        <v>3.12</v>
       </c>
       <c r="T28" t="n">
-        <v>1.99</v>
+        <v>2.5</v>
       </c>
       <c r="U28" t="n">
-        <v>1.86</v>
+        <v>1.49</v>
       </c>
       <c r="V28" t="n">
-        <v>3.8</v>
+        <v>5.75</v>
       </c>
       <c r="W28" t="n">
-        <v>1.24</v>
+        <v>1.08</v>
       </c>
       <c r="X28" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.1</v>
+        <v>1.21</v>
       </c>
       <c r="Z28" t="n">
-        <v>6.5</v>
+        <v>3.84</v>
       </c>
       <c r="AA28" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB28" t="n">
-        <v>2.98</v>
+        <v>2</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.02</v>
+        <v>2.95</v>
       </c>
       <c r="AD28" t="n">
-        <v>1.84</v>
+        <v>1.4</v>
       </c>
       <c r="AE28" t="n">
-        <v>1.66</v>
+        <v>1.59</v>
       </c>
       <c r="AF28" t="n">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="AG28" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AH28" t="n">
-        <v>3.35</v>
+        <v>1.44</v>
       </c>
       <c r="AI28" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3846,12 +3846,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Inter Milan</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Ajax</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -3872,73 +3872,73 @@
         </is>
       </c>
       <c r="L29" t="n">
-        <v>2.65</v>
+        <v>1.55</v>
       </c>
       <c r="M29" t="n">
-        <v>3.4</v>
+        <v>4.3</v>
       </c>
       <c r="N29" t="n">
-        <v>2.6</v>
+        <v>5.2</v>
       </c>
       <c r="O29" t="n">
-        <v>3.28</v>
+        <v>1.98</v>
       </c>
       <c r="P29" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.2</v>
+        <v>4.6</v>
       </c>
       <c r="R29" t="n">
-        <v>1.38</v>
+        <v>1.2</v>
       </c>
       <c r="S29" t="n">
-        <v>2.98</v>
+        <v>3.9</v>
       </c>
       <c r="T29" t="n">
-        <v>2.81</v>
+        <v>2.05</v>
       </c>
       <c r="U29" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="V29" t="n">
-        <v>7.2</v>
+        <v>4.6</v>
       </c>
       <c r="W29" t="n">
-        <v>1.06</v>
+        <v>1.18</v>
       </c>
       <c r="X29" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="Y29" t="n">
-        <v>1.32</v>
+        <v>1.14</v>
       </c>
       <c r="Z29" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA29" t="n">
-        <v>1.93</v>
+        <v>1.58</v>
       </c>
       <c r="AB29" t="n">
-        <v>1.77</v>
+        <v>2.38</v>
       </c>
       <c r="AC29" t="n">
-        <v>3.2</v>
+        <v>2.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>1.29</v>
+        <v>1.6</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.7</v>
+        <v>1.53</v>
       </c>
       <c r="AF29" t="n">
-        <v>2.05</v>
+        <v>2.38</v>
       </c>
       <c r="AG29" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
       <c r="AH29" t="n">
-        <v>1.5</v>
+        <v>2.46</v>
       </c>
       <c r="AI29" s="3" t="n">
         <v>46042.70833333334</v>
@@ -3965,12 +3965,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Olympiakos Piraeus</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Monaco</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -3991,73 +3991,73 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>2.45</v>
+        <v>1.26</v>
       </c>
       <c r="M30" t="n">
-        <v>3.52</v>
+        <v>6</v>
       </c>
       <c r="N30" t="n">
-        <v>2.75</v>
+        <v>8.9</v>
       </c>
       <c r="O30" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="P30" t="n">
         <v>3</v>
       </c>
-      <c r="P30" t="n">
-        <v>2.21</v>
-      </c>
       <c r="Q30" t="n">
-        <v>3</v>
+        <v>7.26</v>
       </c>
       <c r="R30" t="n">
-        <v>1.34</v>
+        <v>1.19</v>
       </c>
       <c r="S30" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="T30" t="n">
-        <v>2.43</v>
+        <v>2.02</v>
       </c>
       <c r="U30" t="n">
-        <v>1.5</v>
+        <v>1.86</v>
       </c>
       <c r="V30" t="n">
-        <v>6.15</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y30" t="n">
         <v>1.09</v>
       </c>
-      <c r="X30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.19</v>
-      </c>
       <c r="Z30" t="n">
-        <v>4.1</v>
+        <v>6.1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1.79</v>
+        <v>1.35</v>
       </c>
       <c r="AB30" t="n">
-        <v>2.12</v>
+        <v>3.04</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.72</v>
+        <v>1.87</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.43</v>
+        <v>1.87</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AF30" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AG30" t="n">
-        <v>1.41</v>
+        <v>1.14</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.5</v>
+        <v>3.5</v>
       </c>
       <c r="AI30" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4084,12 +4084,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sporting CP</t>
+          <t>København</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>PSG</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4110,73 +4110,73 @@
         </is>
       </c>
       <c r="L31" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="M31" t="n">
-        <v>3.9</v>
+        <v>3.61</v>
       </c>
       <c r="N31" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="O31" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.2</v>
+        <v>2.43</v>
       </c>
       <c r="R31" t="n">
-        <v>1.28</v>
+        <v>1.4</v>
       </c>
       <c r="S31" t="n">
-        <v>3.5</v>
+        <v>2.84</v>
       </c>
       <c r="T31" t="n">
-        <v>2.36</v>
+        <v>3.12</v>
       </c>
       <c r="U31" t="n">
-        <v>1.61</v>
+        <v>1.4</v>
       </c>
       <c r="V31" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="W31" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="X31" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="Z31" t="n">
-        <v>4.6</v>
+        <v>3.3</v>
       </c>
       <c r="AA31" t="n">
-        <v>1.6</v>
+        <v>1.82</v>
       </c>
       <c r="AB31" t="n">
-        <v>2.33</v>
+        <v>1.92</v>
       </c>
       <c r="AC31" t="n">
-        <v>2.49</v>
+        <v>3.65</v>
       </c>
       <c r="AD31" t="n">
-        <v>1.5</v>
+        <v>1.27</v>
       </c>
       <c r="AE31" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="AF31" t="n">
-        <v>2.38</v>
+        <v>1.95</v>
       </c>
       <c r="AG31" t="n">
         <v>1.25</v>
       </c>
       <c r="AH31" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="AI31" s="3" t="n">
         <v>46042.70833333334</v>
@@ -4203,12 +4203,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Inter Milan</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4229,67 +4229,67 @@
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.45</v>
+        <v>2.62</v>
       </c>
       <c r="M32" t="n">
-        <v>3.5</v>
+        <v>3.32</v>
       </c>
       <c r="N32" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="O32" t="n">
-        <v>3.14</v>
+        <v>3.34</v>
       </c>
       <c r="P32" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="Q32" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="S32" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="V32" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AC32" t="n">
         <v>3.25</v>
       </c>
-      <c r="R32" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S32" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="T32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U32" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V32" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="X32" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y32" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="Z32" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="AA32" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AB32" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC32" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AD32" t="n">
-        <v>1.4</v>
+        <v>1.28</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="AF32" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG32" t="n">
         <v>1.3</v>
@@ -4322,12 +4322,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Sporting CP</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ajax</t>
+          <t>PSG</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4348,73 +4348,73 @@
         </is>
       </c>
       <c r="L33" t="n">
-        <v>1.55</v>
+        <v>3.97</v>
       </c>
       <c r="M33" t="n">
-        <v>4.4</v>
+        <v>3.92</v>
       </c>
       <c r="N33" t="n">
-        <v>5.3</v>
+        <v>1.78</v>
       </c>
       <c r="O33" t="n">
-        <v>2</v>
+        <v>4.25</v>
       </c>
       <c r="P33" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.17</v>
+        <v>2.23</v>
       </c>
       <c r="R33" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="S33" t="n">
-        <v>3.94</v>
+        <v>3.58</v>
       </c>
       <c r="T33" t="n">
-       